--- a/radio_capture/relatorio_anuncios.xlsx
+++ b/radio_capture/relatorio_anuncios.xlsx
@@ -42,7 +42,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +62,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,6 +115,180 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -494,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -544,261 +723,2370 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>06/03/2026 12:38:54</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:00:14</t>
+        </is>
+      </c>
+      <c r="B2" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C2" s="67" t="inlineStr">
+        <is>
+          <t>Casa dos Construtores</t>
+        </is>
+      </c>
+      <c r="D2" s="67" t="inlineStr">
+        <is>
+          <t>espaços para casas</t>
+        </is>
+      </c>
+      <c r="E2" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Mas em como se vive? O tempo bem vivido é feito de escolhas, de detalhes que permanecem, de casas que acolhem, de memórias que resistem. Há 65 anos, criamos espaços para que cada instante não apenas p</t>
+        </is>
+      </c>
+      <c r="G2" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Casa_dos_Construtores__espacos_para_casas__09-03-2026_09-00-14__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:00:15</t>
+        </is>
+      </c>
+      <c r="B3" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C3" s="67" t="inlineStr">
+        <is>
+          <t>Ótica Fabriley</t>
+        </is>
+      </c>
+      <c r="D3" s="67" t="inlineStr">
+        <is>
+          <t>serviços de ótica</t>
+        </is>
+      </c>
+      <c r="E3" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Mas em como se vive? O tempo bem vivido é feito de escolhas, de detalhes que permanecem, de casas que acolhem, de memórias que resistem. Há 65 anos, criamos espaços para que cada instante não apenas p</t>
+        </is>
+      </c>
+      <c r="G3" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Otica_Fabriley__servicos_de_otica__09-03-2026_09-00-15__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:00:31</t>
+        </is>
+      </c>
+      <c r="B4" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C4" s="67" t="inlineStr">
+        <is>
+          <t>ótica FabriLen</t>
+        </is>
+      </c>
+      <c r="D4" s="67" t="inlineStr">
+        <is>
+          <t>lentes</t>
+        </is>
+      </c>
+      <c r="E4" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Cada instante, não apenas passe, mas fique. Casa dos Construtores, o melhor tempo na sua casa. Quando o assunto é visão, a ótica FabriLen é referência. Atendimento diferenciado com profissionais prepa</t>
+        </is>
+      </c>
+      <c r="G4" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__otica_FabriLen__lentes__09-03-2026_09-00-30.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:00:33</t>
+        </is>
+      </c>
+      <c r="B5" s="67" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C5" s="67" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D5" s="67" t="inlineStr">
+        <is>
+          <t>Chocolate</t>
+        </is>
+      </c>
+      <c r="E5" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Viu? Bob Sinclair na programação número 1 do seu rádio, vocês viram aí, aliás, ouviram, né? Vai, Tassonzão! Tonsera, né, pra gente curtir aqui na programação. Jovem Pan, daqui a pouquinho, depois de i</t>
+        </is>
+      </c>
+      <c r="G5" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Cacau_Show__Chocolate__09-03-2026_09-00-33.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:00:48</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C6" s="67" t="inlineStr">
+        <is>
+          <t>Noblen</t>
+        </is>
+      </c>
+      <c r="D6" s="67" t="inlineStr">
+        <is>
+          <t>lentes multifocais digitais e lentes de visão simples</t>
+        </is>
+      </c>
+      <c r="E6" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Preparados para orientar você com atenção e confiança. As lentes são produzidas com alta tecnologia, garantindo precisão e conforto para o dia a dia. E tem promoção especial. Na compra do primeiro par</t>
+        </is>
+      </c>
+      <c r="G6" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Noblen__lentes_multifocais_digitais_e_lentes_de_visao_simples__09-03-2026_09-00-48.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:00:50</t>
+        </is>
+      </c>
+      <c r="B7" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C7" s="67" t="inlineStr">
+        <is>
+          <t>Cacau Show</t>
+        </is>
+      </c>
+      <c r="D7" s="67" t="inlineStr">
         <is>
           <t>chocolate</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>A loja cacau show catanduva no insta e comente eu quero no post oficial Páscoa com muito chocolate É na número 1 do Brasil Jovem Pan Estamos de volta aqui na programação da Jovem Pan para todo o Brasi</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>Jovem_Pan__Cacau_Show__chocolate__06-03-2026_12-38-53.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>06/03/2026 12:53:11</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="E7" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Número 1 do Brasil e... e... e... Cacau Show! Aquele chocolate maravilhoso, aquele chocolate refinado, aquele sabor... Hummm... já vai dando assim o negócio, é de louco, né? Quer levar pra casa? Então</t>
+        </is>
+      </c>
+      <c r="G7" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Cacau_Show__chocolate__09-03-2026_09-00-50.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:01:04</t>
+        </is>
+      </c>
+      <c r="B8" s="67" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Bazar da Pechincha</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>roupas, calçados e utilidades domésticas</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preço baixo e pipoca e algodão doce pra alegrar a criançada. Vem conferir. Um a noventa e nove. Quem economiza pode mais. Bazar da Pechincha. Nesta sexta-feira, dia seis de março, acontece o Bazar da </t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Bazar_da_Pechincha__roupas__calcados_e_utilidades_domesticas__06-03-2026_12-53-11.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>06/03/2026 13:05:54</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="C8" s="67" t="inlineStr">
+        <is>
+          <t>Óticas FabriLem</t>
+        </is>
+      </c>
+      <c r="D8" s="67" t="inlineStr">
+        <is>
+          <t>lentes de visão simples com antirreflexo e filtro de luz azul</t>
+        </is>
+      </c>
+      <c r="E8" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>digitais noblem com antirreflexo, o segundo par é grátis. E mais, lentes de visão simples com antirreflexo e filtro de luz azul em até dez vezes de dezoito e noventa. Visite a loja na Rua Brasil Esqui</t>
+        </is>
+      </c>
+      <c r="G8" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Oticas_FabriLem__lentes_de_visao_simples_com_antirreflexo_e_filtro_de_luz_azu__09-03-2026_09-01-04__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="62" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:01:04</t>
+        </is>
+      </c>
+      <c r="B9" s="62" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Bazar da Pechincha</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>roupas, calçados, utilidades domésticas</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>da Pechincha. Nesta sexta-feira, dia seis de março, acontece o Bazar da Pechincha da Associação Espírita Morigaridade. Roupas masculinas, femininas, infantis, calçados e utilidades domésticas a preços</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Bazar_da_Pechincha__roupas__calcados__utilidades_domesticas__06-03-2026_13-05-54.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>06/03/2026 13:15:43</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
+        <is>
+          <t>Amaral Centro Automotivo Multimarcas</t>
+        </is>
+      </c>
+      <c r="D9" s="62" t="inlineStr">
+        <is>
+          <t>serviços automotivos</t>
+        </is>
+      </c>
+      <c r="E9" s="62" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>digitais noblem com antirreflexo, o segundo par é grátis. E mais, lentes de visão simples com antirreflexo e filtro de luz azul em até dez vezes de dezoito e noventa. Visite a loja na Rua Brasil Esqui</t>
+        </is>
+      </c>
+      <c r="G9" s="62" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Amaral_Centro_Automotivo_Multimarcas__servicos_automotivos__09-03-2026_09-01-04__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:01:21</t>
+        </is>
+      </c>
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>FabriLem</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>óculos de grau</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Aço, das nove às dezessete horas, na Rua Sergipe, quatrocentos e dez, no centro, em Catanduba. Participe e colabore. Quando o assunto é visão, a ótica FabriLem é referência. Atendimento diferenciado c</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__FabriLem__oculos_de_grau__06-03-2026_13-15-43.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>06/03/2026 13:27:20</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="C10" s="67" t="inlineStr">
+        <is>
+          <t>Amaral Centro Automotivo Multimarcas</t>
+        </is>
+      </c>
+      <c r="D10" s="67" t="inlineStr">
+        <is>
+          <t>serviços automotivos</t>
+        </is>
+      </c>
+      <c r="E10" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>FabriLem, a fábrica da sua lente. Amaral Centro Automotivo Multimarcas agradece a todos o carinho e a confiança no trabalho realizado com sua equipe de profissionais. Hoje estamos em novo endereço par</t>
+        </is>
+      </c>
+      <c r="G10" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Amaral_Centro_Automotivo_Multimarcas__servicos_automotivos__09-03-2026_09-01-21.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:02:10</t>
+        </is>
+      </c>
+      <c r="B11" s="67" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Noblen</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>lentes multifocais digitais, lentes de visão simples com antirreflexo e filtro de luz azul</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">para orientar você com atenção e confiança. As lentes são produzidas com alta tecnologia, garantindo precisão e conforto para o dia a dia. E tem promoção especial. Na compra do primeiro par de lentes </t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Noblen__lentes_multifocais_digitais__lentes_de_visao_simples_com_ant__06-03-2026_13-27-20.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>06/03/2026 13:37:57</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="C11" s="67" t="inlineStr">
+        <is>
+          <t>Unifipa</t>
+        </is>
+      </c>
+      <c r="D11" s="67" t="inlineStr">
+        <is>
+          <t>Cursos de graduação</t>
+        </is>
+      </c>
+      <c r="E11" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>São onze opções de cursos de graduação na instituição que tem mais de cinquenta e cinco anos de tradição e é sinônimo de excelência em ensino com nota máxima na avaliação do MEC. Venha ser Unifipa. In</t>
+        </is>
+      </c>
+      <c r="G11" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Unifipa__Cursos_de_graduacao__09-03-2026_09-02-10__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:02:10</t>
+        </is>
+      </c>
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Óticas FabriLem</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>lentes de visão com antirreflexo e filtro de luz azul</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>com antirreflexo, o segundo par é grátis. E mais, lentes de visão simples com antirreflexo e filtro de luz azul em até 10x de R$ 18,90. Visite a loja na Rua Brasil Esquina com a Cuiabá em Catanduva. Ó</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Oticas_FabriLem__lentes_de_visao_com_antirreflexo_e_filtro_de_luz_azul__06-03-2026_13-37-57.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>06/03/2026 13:48:56</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="C12" s="62" t="inlineStr">
+        <is>
+          <t>Nagatela</t>
+        </is>
+      </c>
+      <c r="D12" s="62" t="inlineStr">
+        <is>
+          <t>Poupança premiada</t>
+        </is>
+      </c>
+      <c r="E12" s="62" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>São onze opções de cursos de graduação na instituição que tem mais de cinquenta e cinco anos de tradição e é sinônimo de excelência em ensino com nota máxima na avaliação do MEC. Venha ser Unifipa. In</t>
+        </is>
+      </c>
+      <c r="G12" s="62" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Nagatela__Poupanca_premiada__09-03-2026_09-02-10__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:02:27</t>
+        </is>
+      </c>
+      <c r="B13" s="67" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C13" s="67" t="inlineStr">
+        <is>
+          <t>Cicred</t>
+        </is>
+      </c>
+      <c r="D13" s="67" t="inlineStr">
+        <is>
+          <t>Poupança premiada</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>A Unipipa, referência que transforma vidas. Aqui é a Nagacela, é hora de sonhar alto. A poupança premiada Cicred tá aí. Cicred, poupança é premiada Pra fazer tudo o que você sonhava Tem milhões em ben</t>
+        </is>
+      </c>
+      <c r="G13" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Cicred__Poupanca_premiada__09-03-2026_09-02-27.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:02:43</t>
+        </is>
+      </c>
+      <c r="B14" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C14" s="67" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Variedade de produtos de supermercado (filé de frango, óleo, arroz, café, Omo, Skol)</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>A fábrica da sua lente. Para tudo, chegou o dia M no Max. Vem aproveitar os melhores preços do Atacarejo. É o preço mais fácil de que tanto. Filé de frango, treze e noventa e sete o quilo. Óleo só e n</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Max__Variedade_de_produtos_de_supermercado__file_de_frango__oleo___06-03-2026_13-48-56.mp3</t>
+      <c r="D14" s="67" t="inlineStr">
+        <is>
+          <t>Produtos para Páscoa (chocolate, ovo de Páscoa, peixe, etc.)</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>São mais de 600 ganhadores, 5 milhões em prêmios em dinheiro. Volte no Cicred e concorra! O Baré Show, olha onde eu tô! Corre para conferir os preços imperdíveis do Max e garanta sua Páscoa! Olha, tem</t>
+        </is>
+      </c>
+      <c r="G14" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Max__Produtos_para_Pascoa__chocolate__ovo_de_Pascoa__peixe__etc__09-03-2026_09-02-43__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:02:43</t>
+        </is>
+      </c>
+      <c r="B15" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C15" s="67" t="inlineStr">
+        <is>
+          <t>Cicred</t>
+        </is>
+      </c>
+      <c r="D15" s="67" t="inlineStr">
+        <is>
+          <t>Concurso com prêmios em dinheiro</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>São mais de 600 ganhadores, 5 milhões em prêmios em dinheiro. Volte no Cicred e concorra! O Baré Show, olha onde eu tô! Corre para conferir os preços imperdíveis do Max e garanta sua Páscoa! Olha, tem</t>
+        </is>
+      </c>
+      <c r="G15" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Cicred__Concurso_com_premios_em_dinheiro__09-03-2026_09-02-43__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:03:00</t>
+        </is>
+      </c>
+      <c r="B16" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C16" s="67" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D16" s="67" t="inlineStr">
+        <is>
+          <t>Produtos para Páscoa (chocolate, ovo de Páscoa, peixe, etc.)</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Corre para conferir os preços imperdíveis do Max e garanta sua Páscoa. Olha, tem chocolate, ovo de Páscoa, peixe e muito mais. Tudo com preço baixinho pra você aproveitar. Filé de peito lá no quilo 14</t>
+        </is>
+      </c>
+      <c r="G16" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Max__Produtos_para_Pascoa__chocolate__ovo_de_Pascoa__peixe__etc__09-03-2026_09-03-00.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:03:14</t>
+        </is>
+      </c>
+      <c r="B17" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C17" s="67" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="D17" s="67" t="inlineStr">
+        <is>
+          <t>BTS The Comeback Live</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uma delas é o trailer do especial da Netflix, BTS The Comeback Live, que chega à plataforma no próximo dia 20. O filme faz parte da poderosa campanha promocional do álbum I Run dos reis do K-Pop. Pra </t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Netflix__BTS_The_Comeback_Live__09-03-2026_09-03-14.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:03:16</t>
+        </is>
+      </c>
+      <c r="B18" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C18" s="67" t="inlineStr">
+        <is>
+          <t>Sete Farinha Globo</t>
+        </is>
+      </c>
+      <c r="D18" s="67" t="inlineStr">
+        <is>
+          <t>Farinha</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>sete farinha globo, um quilo, dois e quarenta e sete. Tó de trezentos e setenta gramas, sete e noventa e nove. Mussarela a partir de vinte e seis e noventa um quilo. Papel Supra, vinte e nove e novent</t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Sete_Farinha_Globo__Farinha__09-03-2026_09-03-16__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:03:16</t>
+        </is>
+      </c>
+      <c r="B19" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C19" s="67" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D19" s="67" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>sete farinha globo, um quilo, dois e quarenta e sete. Tó de trezentos e setenta gramas, sete e noventa e nove. Mussarela a partir de vinte e seis e noventa um quilo. Papel Supra, vinte e nove e novent</t>
+        </is>
+      </c>
+      <c r="G19" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Max__Pasta__09-03-2026_09-03-16__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:03:16</t>
+        </is>
+      </c>
+      <c r="B20" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C20" s="67" t="inlineStr">
+        <is>
+          <t>Drogaria Total Popular</t>
+        </is>
+      </c>
+      <c r="D20" s="67" t="inlineStr">
+        <is>
+          <t>Remédios</t>
+        </is>
+      </c>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>sete farinha globo, um quilo, dois e quarenta e sete. Tó de trezentos e setenta gramas, sete e noventa e nove. Mussarela a partir de vinte e seis e noventa um quilo. Papel Supra, vinte e nove e novent</t>
+        </is>
+      </c>
+      <c r="G20" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Drogaria_Total_Popular__Remedios__09-03-2026_09-03-16__ad3.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:03:32</t>
+        </is>
+      </c>
+      <c r="B21" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="inlineStr">
+        <is>
+          <t>Doutor Alex Baraldo Portes</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="inlineStr">
+        <is>
+          <t>Serviços de Otorrino Laringologista</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jovem Pan. Jovem Pan Brasil. Você está ouvindo. Manhã Pan. Catanduva. Oferecimento. Doutor Alex Baraldo Portes. Otorrino Laringologista. RQE 64202. Vive em empreendimentos. Municipa Catanduva. Doutor </t>
+        </is>
+      </c>
+      <c r="G21" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_Otorrino_Laringologista__09-03-2026_09-03-32__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:03:32</t>
+        </is>
+      </c>
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C22" s="67" t="inlineStr">
+        <is>
+          <t>IGA Proteção Veicular</t>
+        </is>
+      </c>
+      <c r="D22" s="67" t="inlineStr">
+        <is>
+          <t>Proteção Veicular</t>
+        </is>
+      </c>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jovem Pan. Jovem Pan Brasil. Você está ouvindo. Manhã Pan. Catanduva. Oferecimento. Doutor Alex Baraldo Portes. Otorrino Laringologista. RQE 64202. Vive em empreendimentos. Municipa Catanduva. Doutor </t>
+        </is>
+      </c>
+      <c r="G22" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__IGA_Protecao_Veicular__Protecao_Veicular__09-03-2026_09-03-32__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:03:50</t>
+        </is>
+      </c>
+      <c r="B23" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C23" s="67" t="inlineStr">
+        <is>
+          <t>Doutor Alex Baraldo Portes</t>
+        </is>
+      </c>
+      <c r="D23" s="67" t="inlineStr">
+        <is>
+          <t>Serviços de otorrino laringologista</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Municipal, município de Catanduva, doutor Cristiano Herrera e GA Proteção Veicular. Nariz entupido, incômodos no ouvido, nariz ou garganta? Sua saúde pode estar precisando de atenção. Quando você sent</t>
+        </is>
+      </c>
+      <c r="G23" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_otorrino_laringologista__09-03-2026_09-03-50.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:04:08</t>
+        </is>
+      </c>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>Doutor Alex Baraldo Portes</t>
+        </is>
+      </c>
+      <c r="D24" s="67" t="inlineStr">
+        <is>
+          <t>Serviços de otorrino-laringologia</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Cuida do nariz, ouvido e garganta. Não perca o foco da sua saúde. Essa é uma mensagem do doutor Alex Baraldo Portes, que é otorrino-laringologista. CRM 137582, RQE 64202. Lá no Instagram do doutor Ale</t>
+        </is>
+      </c>
+      <c r="G24" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_otorrino-laringologia__09-03-2026_09-04-08__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:04:08</t>
+        </is>
+      </c>
+      <c r="B25" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C25" s="67" t="inlineStr">
+        <is>
+          <t>Unifipa Catanduva</t>
+        </is>
+      </c>
+      <c r="D25" s="67" t="inlineStr">
+        <is>
+          <t>Vestibular continuado 2026</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Cuida do nariz, ouvido e garganta. Não perca o foco da sua saúde. Essa é uma mensagem do doutor Alex Baraldo Portes, que é otorrino-laringologista. CRM 137582, RQE 64202. Lá no Instagram do doutor Ale</t>
+        </is>
+      </c>
+      <c r="G25" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Unifipa_Catanduva__Vestibular_continuado_2026__09-03-2026_09-04-08__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:04:22</t>
+        </is>
+      </c>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="D26" s="67" t="inlineStr">
+        <is>
+          <t>Serviço de streaming</t>
+        </is>
+      </c>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Ligue agora ou mande um zap, dezessete três um cinco um mil, ou acesse NetflixBR.com. É Netflix! A FM da gente, Ondas Verde! A sua manhã fica completa na Ondas Verdes.</t>
+        </is>
+      </c>
+      <c r="G26" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Netflix__Servico_de_streaming__09-03-2026_09-04-22.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:04:44</t>
+        </is>
+      </c>
+      <c r="B27" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C27" s="67" t="inlineStr">
+        <is>
+          <t>Unifipa</t>
+        </is>
+      </c>
+      <c r="D27" s="67" t="inlineStr">
+        <is>
+          <t>Inscrições e provas online</t>
+        </is>
+      </c>
+      <c r="E27" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>é que venha ser Unifipa, inscrições e provas online em unifipa.com.br barra vestibular. Unifipa, referência que transforma vidas. A clínica do doutor Cristiano Herrera, gente, atenção, é referência na</t>
+        </is>
+      </c>
+      <c r="G27" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Unifipa__Inscricoes_e_provas_online__09-03-2026_09-04-44__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:04:45</t>
+        </is>
+      </c>
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C28" s="67" t="inlineStr">
+        <is>
+          <t>Clínica do Doutor Cristiano Herrera</t>
+        </is>
+      </c>
+      <c r="D28" s="67" t="inlineStr">
+        <is>
+          <t>Serviços de psicologia, neuropsicologia e psicopedagogia</t>
+        </is>
+      </c>
+      <c r="E28" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>é que venha ser Unifipa, inscrições e provas online em unifipa.com.br barra vestibular. Unifipa, referência que transforma vidas. A clínica do doutor Cristiano Herrera, gente, atenção, é referência na</t>
+        </is>
+      </c>
+      <c r="G28" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Clinica_do_Doutor_Cristiano_Herrera__Servicos_de_psicologia__neuropsicologia_e_psicopedagogia__09-03-2026_09-04-45__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:05:02</t>
+        </is>
+      </c>
+      <c r="B29" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C29" s="67" t="inlineStr">
+        <is>
+          <t>Doutor Cristiano Herrera</t>
+        </is>
+      </c>
+      <c r="D29" s="67" t="inlineStr">
+        <is>
+          <t>Serviços de psicopedagogia e neuropsicologia</t>
+        </is>
+      </c>
+      <c r="E29" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Psicopedagogia, através da avaliação neuropsicológica com a equipe multidisciplinar, que você vai encontrar lá, pessoal maravilhoso, o doutor Cristiano Herrera, ele utiliza testes em escalas mais efet</t>
+        </is>
+      </c>
+      <c r="G29" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Doutor_Cristiano_Herrera__Servicos_de_psicopedagogia_e_neuropsicologia__09-03-2026_09-05-02__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:05:03</t>
+        </is>
+      </c>
+      <c r="B30" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C30" s="67" t="inlineStr">
+        <is>
+          <t>Doutor Cristian Aranjeira</t>
+        </is>
+      </c>
+      <c r="D30" s="67" t="inlineStr">
+        <is>
+          <t>Serviços de psicologia e neuropsicologia</t>
+        </is>
+      </c>
+      <c r="E30" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Psicopedagogia, através da avaliação neuropsicológica com a equipe multidisciplinar, que você vai encontrar lá, pessoal maravilhoso, o doutor Cristiano Herrera, ele utiliza testes em escalas mais efet</t>
+        </is>
+      </c>
+      <c r="G30" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Doutor_Cristian_Aranjeira__Servicos_de_psicologia_e_neuropsicologia__09-03-2026_09-05-03__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:05:21</t>
+        </is>
+      </c>
+      <c r="B31" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C31" s="67" t="inlineStr">
+        <is>
+          <t>Clínica do Dr. Cristiano Herrera</t>
+        </is>
+      </c>
+      <c r="D31" s="67" t="inlineStr">
+        <is>
+          <t>Serviços de psicologia e neuroreabilitação</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>inclusive os tratamentos não medicamentosos, por exemplo, como neuromodulação e biofeedback. O doutor Cristiano Herrera, ele é psicólogo, neuropsicólogo formado pela USP, especialista em neuroreabilit</t>
+        </is>
+      </c>
+      <c r="G31" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Clinica_do_Dr__Cristiano_Herrera__Servicos_de_psicologia_e_neuroreabilitacao__09-03-2026_09-05-21.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:05:39</t>
+        </is>
+      </c>
+      <c r="B32" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C32" s="67" t="inlineStr">
+        <is>
+          <t>Antunes Mais</t>
+        </is>
+      </c>
+      <c r="D32" s="67" t="inlineStr">
+        <is>
+          <t>Arroz seleto e feijão carioca</t>
+        </is>
+      </c>
+      <c r="E32" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O segundo andar, então acesse arroba DR Cristiano Herrera no Instagram. Liga a fã no Instagram, arroba jovem fã Catanduba. Comece a semana com mais economia no Antunes Mais. Confira arroz seleto tipo </t>
+        </is>
+      </c>
+      <c r="G32" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Antunes_Mais__Arroz_seleto_e_feijao_carioca__09-03-2026_09-05-39__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:05:39</t>
+        </is>
+      </c>
+      <c r="B33" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C33" s="67" t="inlineStr">
+        <is>
+          <t>Clube do Precinho</t>
+        </is>
+      </c>
+      <c r="D33" s="67" t="inlineStr">
+        <is>
+          <t>Músculo bovino e cortes de carne</t>
+        </is>
+      </c>
+      <c r="E33" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O segundo andar, então acesse arroba DR Cristiano Herrera no Instagram. Liga a fã no Instagram, arroba jovem fã Catanduba. Comece a semana com mais economia no Antunes Mais. Confira arroz seleto tipo </t>
+        </is>
+      </c>
+      <c r="G33" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Clube_do_Precinho__Musculo_bovino_e_cortes_de_carne__09-03-2026_09-05-39__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:05:57</t>
+        </is>
+      </c>
+      <c r="B34" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C34" s="67" t="inlineStr">
+        <is>
+          <t>Antunes Mais</t>
+        </is>
+      </c>
+      <c r="D34" s="67" t="inlineStr">
+        <is>
+          <t>Produtos variados (feijão, carne, detergente, etc.)</t>
+        </is>
+      </c>
+      <c r="E34" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>onze e noventa e nove, feijão carioca seleto, pacote um quilo, seis e noventa e nove, tem também as ofertas do Clube do Precinho, acenho, músculo bovino, trinta e quatro e noventa e cinco quilo, colch</t>
+        </is>
+      </c>
+      <c r="G34" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Antunes_Mais__Produtos_variados__feijao__carne__detergente__etc__09-03-2026_09-05-57.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:06:15</t>
+        </is>
+      </c>
+      <c r="B35" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C35" s="67" t="inlineStr">
+        <is>
+          <t>Antunes Mais</t>
+        </is>
+      </c>
+      <c r="D35" s="67" t="inlineStr">
+        <is>
+          <t>Produtos com descontos</t>
+        </is>
+      </c>
+      <c r="E35" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>O Festas Válidas, até dia onze, no Antunes Mais. As melhores lojas de Catanduva, reunidas em um único lugar, com até setenta por cento off. Você já sabe de qual evento estamos falando? Bazar chique, é</t>
+        </is>
+      </c>
+      <c r="G35" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Antunes_Mais__Produtos_com_descontos__09-03-2026_09-06-15__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:06:15</t>
+        </is>
+      </c>
+      <c r="B36" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C36" s="67" t="inlineStr">
+        <is>
+          <t>Bazar Chique</t>
+        </is>
+      </c>
+      <c r="D36" s="67" t="inlineStr">
+        <is>
+          <t>Roupas, acessórios, calçados, óticas</t>
+        </is>
+      </c>
+      <c r="E36" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>O Festas Válidas, até dia onze, no Antunes Mais. As melhores lojas de Catanduva, reunidas em um único lugar, com até setenta por cento off. Você já sabe de qual evento estamos falando? Bazar chique, é</t>
+        </is>
+      </c>
+      <c r="G36" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Bazar_Chique__Roupas__acessorios__calcados__oticas__09-03-2026_09-06-15__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:06:33</t>
+        </is>
+      </c>
+      <c r="B37" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="inlineStr">
+        <is>
+          <t>SimComércio e Vive Empre</t>
+        </is>
+      </c>
+      <c r="D37" s="67" t="inlineStr">
+        <is>
+          <t>Feira ou evento de vendas</t>
+        </is>
+      </c>
+      <c r="E37" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>e muito mais com preços imperdíveis. Dias 19, 20 e 21 de março, na sede do SimComércio, Avenida Benedito Zancaner, 720, quinta e sexta, das nove às vinte e duas horas. Sábado, das nove às dezessete ho</t>
+        </is>
+      </c>
+      <c r="G37" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__SimComercio_e_Vive_Empre__Feira_ou_evento_de_vendas__09-03-2026_09-06-33.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:06:52</t>
+        </is>
+      </c>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>Vive Empreendimentos</t>
+        </is>
+      </c>
+      <c r="D38" s="67" t="inlineStr">
+        <is>
+          <t>empreendimentos imobiliários</t>
+        </is>
+      </c>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Olha, se tem uma empresa que vem transformando o jeito de viver dos últimos anos, essa empresa seguramente é a Vive Empreendimentos. Nascida em Catanduva, a Vive hoje está presente em quatro estados d</t>
+        </is>
+      </c>
+      <c r="G38" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Vive_Empreendimentos__empreendimentos_imobiliarios__09-03-2026_09-06-52.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:07:08</t>
+        </is>
+      </c>
+      <c r="B39" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C39" s="67" t="inlineStr">
+        <is>
+          <t>Vive</t>
+        </is>
+      </c>
+      <c r="D39" s="67" t="inlineStr">
+        <is>
+          <t>Loteamentos e espaços planejados</t>
+        </is>
+      </c>
+      <c r="E39" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Atenção, São Paulo, Mato Grosso do Sul, Minas Gerais e Goiás. Sempre levando desempenho com responsabilidade, sustentabilidade e muita inovação. Quem conhece os projetos da Vive sabe, não são apenas l</t>
+        </is>
+      </c>
+      <c r="G39" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Vive__Loteamentos_e_espacos_planejados__09-03-2026_09-07-08.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:07:26</t>
+        </is>
+      </c>
+      <c r="B40" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C40" s="67" t="inlineStr">
+        <is>
+          <t>VIB</t>
+        </is>
+      </c>
+      <c r="D40" s="67" t="inlineStr">
+        <is>
+          <t>empreendimentos imobiliários</t>
+        </is>
+      </c>
+      <c r="E40" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>para oferecer mais qualidade de vida, contato com a natureza e toda a infraestrutura que as famílias procuram para viver bem. E tem mais, como coligada no grupo Serradinho, a VIB carrega a credibilida</t>
+        </is>
+      </c>
+      <c r="G40" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__VIB__empreendimentos_imobiliarios__09-03-2026_09-07-26.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:07:44</t>
+        </is>
+      </c>
+      <c r="B41" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C41" s="67" t="inlineStr">
+        <is>
+          <t>Oralfai Catanduva</t>
+        </is>
+      </c>
+      <c r="D41" s="67" t="inlineStr">
+        <is>
+          <t>tratamentos odontológicos</t>
+        </is>
+      </c>
+      <c r="E41" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visão de futuro e compromisso com as cidades onde atua, vive empreendimentos conectando pessoas, criando novas formas de viver e mudando o futuro. Jovem Pan Olá, eu sou o doutor Guilherme Pelegrin da </t>
+        </is>
+      </c>
+      <c r="G41" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Oralfai_Catanduva__tratamentos_odontologicos__09-03-2026_09-07-44.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:08:38</t>
+        </is>
+      </c>
+      <c r="B42" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C42" s="67" t="inlineStr">
+        <is>
+          <t>Cacau Show</t>
+        </is>
+      </c>
+      <c r="D42" s="67" t="inlineStr">
+        <is>
+          <t>Ovos de Páscoa e tabletes</t>
+        </is>
+      </c>
+      <c r="E42" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>E nos momentos em memórias que ficam para sempre. E quando o assunto é celebrar com sabor, a escolha é uma só. Cacau Show. Ovos de Páscoa encantadores. Tabletes irresistíveis. Presentes que emocionam.</t>
+        </is>
+      </c>
+      <c r="G42" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Cacau_Show__Ovos_de_Pascoa_e_tabletes__09-03-2026_09-08-38.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:09:51</t>
+        </is>
+      </c>
+      <c r="B43" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C43" s="67" t="inlineStr">
+        <is>
+          <t>Jovem Pan</t>
+        </is>
+      </c>
+      <c r="D43" s="67" t="inlineStr">
+        <is>
+          <t>Cobertura da Copa do Mundo</t>
+        </is>
+      </c>
+      <c r="E43" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Agora é dois mil e vinte e seis. Estados Unidos, México e Canadá. Desde sempre, a Jovem Pan está presente nas Copas do Mundo com equipe completa, informação em tempo real, opinião forte e a energia de</t>
+        </is>
+      </c>
+      <c r="G43" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Jovem_Pan__Cobertura_da_Copa_do_Mundo__09-03-2026_09-09-51.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:14:02</t>
+        </is>
+      </c>
+      <c r="B44" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C44" s="67" t="inlineStr">
+        <is>
+          <t>Cacau Show</t>
+        </is>
+      </c>
+      <c r="D44" s="67" t="inlineStr">
+        <is>
+          <t>Ovo de Páscoa</t>
+        </is>
+      </c>
+      <c r="E44" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>porque ele tá dando mau exemplo do programa, eu acho que ele tá muito besteirento, ô Babu, você tá muito besteirento, Babu, para de falar, tá falando muita besteira e ainda tá causando esse alvoroço n</t>
+        </is>
+      </c>
+      <c r="G44" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Cacau_Show__Ovo_de_Pascoa__09-03-2026_09-14-02.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:14:20</t>
+        </is>
+      </c>
+      <c r="B45" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C45" s="67" t="inlineStr">
+        <is>
+          <t>Jovem Pan</t>
+        </is>
+      </c>
+      <c r="D45" s="67" t="inlineStr">
+        <is>
+          <t>Ovo de Páscoa Cacau Show</t>
+        </is>
+      </c>
+      <c r="E45" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E nas redes sociais, a hashtag tá lá, Babu Expulso, o que que cê acha? Conta aí que eu quero saber, no finalzinho, da hora do Manhã Pan. Fique ligado porque tem o ovo de páscoa cacau show, tá rolando </t>
+        </is>
+      </c>
+      <c r="G45" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Jovem_Pan__Ovo_de_Pascoa_Cacau_Show__09-03-2026_09-14-20.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:14:24</t>
+        </is>
+      </c>
+      <c r="B46" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C46" s="67" t="inlineStr">
+        <is>
+          <t>Sotintas</t>
+        </is>
+      </c>
+      <c r="D46" s="67" t="inlineStr">
+        <is>
+          <t>loja de produtos</t>
+        </is>
+      </c>
+      <c r="E46" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Música Não saia daí, já já tem muito mais músicas aqui na Band FM Música Conheça a nova loja da Sotintas em Catanduva, na avenida Berendito Zancaner 1481 Um novo, moderno e amplo espaço para você conh</t>
+        </is>
+      </c>
+      <c r="G46" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM__Sotintas__loja_de_produtos__09-03-2026_09-14-24__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="62" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:14:24</t>
+        </is>
+      </c>
+      <c r="B47" s="62" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C47" s="62" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
+      <c r="D47" s="62" t="inlineStr">
+        <is>
+          <t>linha de produtos</t>
+        </is>
+      </c>
+      <c r="E47" s="62" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Música Não saia daí, já já tem muito mais músicas aqui na Band FM Música Conheça a nova loja da Sotintas em Catanduva, na avenida Berendito Zancaner 1481 Um novo, moderno e amplo espaço para você conh</t>
+        </is>
+      </c>
+      <c r="G47" s="62" t="inlineStr">
+        <is>
+          <t>Band_FM__Lufthansa__linha_de_produtos__09-03-2026_09-14-24__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:15:00</t>
+        </is>
+      </c>
+      <c r="B48" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C48" s="67" t="inlineStr">
+        <is>
+          <t>Tatinho Veículos</t>
+        </is>
+      </c>
+      <c r="D48" s="67" t="inlineStr">
+        <is>
+          <t>Veículos</t>
+        </is>
+      </c>
+      <c r="E48" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>José Nelson Machado, mil trezentos e setenta e nove, e agora também, na Avenida Benedito Zancanet, mil quatrocentos e oitenta e um, ao lado do Proença Supermercados. Só tintas, tudo em tintas, pra com</t>
+        </is>
+      </c>
+      <c r="G48" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM__Tatinho_Veiculos__Veiculos__09-03-2026_09-15-00.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="62" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:17:16</t>
+        </is>
+      </c>
+      <c r="B49" s="62" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C49" s="62" t="inlineStr">
+        <is>
+          <t>Procuro, mora, esquete, supermercados</t>
+        </is>
+      </c>
+      <c r="D49" s="62" t="inlineStr">
+        <is>
+          <t>Produtos de supermercado</t>
+        </is>
+      </c>
+      <c r="E49" s="62" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Filos folha dupla, vinte metros, com doze unidades, doze e noventa e nove. Refrigerante, roler cola pet, dois litros, seis e noventa e nove. Procuro, mora, esquete, supermercados, qualidade, confiança</t>
+        </is>
+      </c>
+      <c r="G49" s="62" t="inlineStr">
+        <is>
+          <t>Band_FM__Procuro__mora__esquete__supermercados__Produtos_de_supermercado__09-03-2026_09-17-15__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:17:16</t>
+        </is>
+      </c>
+      <c r="B50" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C50" s="67" t="inlineStr">
+        <is>
+          <t>Alto Posto Campeão</t>
+        </is>
+      </c>
+      <c r="D50" s="67" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+      <c r="E50" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Filos folha dupla, vinte metros, com doze unidades, doze e noventa e nove. Refrigerante, roler cola pet, dois litros, seis e noventa e nove. Procuro, mora, esquete, supermercados, qualidade, confiança</t>
+        </is>
+      </c>
+      <c r="G50" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM__Alto_Posto_Campeao__Combustivel__09-03-2026_09-17-16__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:17:33</t>
+        </is>
+      </c>
+      <c r="B51" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C51" s="67" t="inlineStr">
+        <is>
+          <t>Bande FM</t>
+        </is>
+      </c>
+      <c r="D51" s="67" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="E51" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>É bem melhor, é Bande FM.</t>
+        </is>
+      </c>
+      <c r="G51" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM__Bande_FM__Radio__09-03-2026_09-17-33.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:30:51</t>
+        </is>
+      </c>
+      <c r="B52" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C52" s="67" t="inlineStr">
+        <is>
+          <t>Traia Veia</t>
+        </is>
+      </c>
+      <c r="D52" s="67" t="inlineStr">
+        <is>
+          <t>Evento (show)</t>
+        </is>
+      </c>
+      <c r="E52" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Primeira vez na região, Traia Veia! E em palco, 360! Mesas, open pool de open bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br Seu moço e Traia Veia! Dia 20 de</t>
+        </is>
+      </c>
+      <c r="G52" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Traia_Veia__Evento__show__09-03-2026_09-30-51__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="62" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:30:51</t>
+        </is>
+      </c>
+      <c r="B53" s="62" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C53" s="62" t="inlineStr">
+        <is>
+          <t>Clube de Tênis Catanduva</t>
+        </is>
+      </c>
+      <c r="D53" s="62" t="inlineStr">
+        <is>
+          <t>Espaço para eventos</t>
+        </is>
+      </c>
+      <c r="E53" s="62" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Primeira vez na região, Traia Veia! E em palco, 360! Mesas, open pool de open bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br Seu moço e Traia Veia! Dia 20 de</t>
+        </is>
+      </c>
+      <c r="G53" s="62" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Clube_de_Tenis_Catanduva__Espaco_para_eventos__09-03-2026_09-30-51__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:30:51</t>
+        </is>
+      </c>
+      <c r="B54" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C54" s="67" t="inlineStr">
+        <is>
+          <t>Quero Dois Ingressos</t>
+        </is>
+      </c>
+      <c r="D54" s="67" t="inlineStr">
+        <is>
+          <t>Serviço de venda de ingressos</t>
+        </is>
+      </c>
+      <c r="E54" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Primeira vez na região, Traia Veia! E em palco, 360! Mesas, open pool de open bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br Seu moço e Traia Veia! Dia 20 de</t>
+        </is>
+      </c>
+      <c r="G54" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Quero_Dois_Ingressos__Servico_de_venda_de_ingressos__09-03-2026_09-30-51__ad3.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:31:07</t>
+        </is>
+      </c>
+      <c r="B55" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C55" s="67" t="inlineStr">
+        <is>
+          <t>Clube de Tênis Catanduva</t>
+        </is>
+      </c>
+      <c r="D55" s="67" t="inlineStr">
+        <is>
+          <t>Ingressos</t>
+        </is>
+      </c>
+      <c r="E55" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>A venda na Secretaria do Clube ou quero dois ingressos ponto com ponto BR. Seu moço e praia velha, dia vinte de março no Clube de Tênis Catanduva. Na vida, os imprevistos são comuns. Aquela viagem ine</t>
+        </is>
+      </c>
+      <c r="G55" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Clube_de_Tenis_Catanduva__Ingressos__09-03-2026_09-31-07.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:31:56</t>
+        </is>
+      </c>
+      <c r="B56" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C56" s="67" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D56" s="67" t="inlineStr">
+        <is>
+          <t>Produtos alimentícios (peixe, camarão, farinha, queijo, papel)</t>
+        </is>
+      </c>
+      <c r="E56" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Peixe e muito mais, tudo com preço baixinho pra você aproveitar. Filé de peito laro, 1,1497. Camarão palimara, 180 gramas, 1,1497. Farinha globo, 1,247. Tó de 370 gramas, 7,99. Mussarela a partir de 2</t>
+        </is>
+      </c>
+      <c r="G56" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Mar__Produtos_alimenticios__peixe__camarao__farinha__queijo__pape__09-03-2026_09-31-56.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:32:13</t>
+        </is>
+      </c>
+      <c r="B57" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C57" s="67" t="inlineStr">
+        <is>
+          <t>Atacarejo Mar</t>
+        </is>
+      </c>
+      <c r="D57" s="67" t="inlineStr">
+        <is>
+          <t>Páscoa</t>
+        </is>
+      </c>
+      <c r="E57" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tocando Papel Supra, vinte e nove e noventa. A maior páscoa do atacarejo é no mar. De voltar aqui na Ondas Verdes, nove e trinta e um agora. Alô, Toninha, bom dia, cê tá boa? Eu sou bem abençoado pra </t>
+        </is>
+      </c>
+      <c r="G57" s="67" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Atacarejo_Mar__Pascoa__09-03-2026_09-32-13.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="62" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:34:10</t>
+        </is>
+      </c>
+      <c r="B58" s="62" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C58" s="62" t="inlineStr">
+        <is>
+          <t>Desconhecido</t>
+        </is>
+      </c>
+      <c r="D58" s="62" t="inlineStr">
+        <is>
+          <t>Promoção</t>
+        </is>
+      </c>
+      <c r="E58" s="62" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>O barulho que eu vou causar Peguei o meu carro, comprei mega fone É hoje que cê escuta a minha saudade de longe Olha o carro do ex passando na sua porta Olha o beijo docinho, abraço quentinho, a pegad</t>
+        </is>
+      </c>
+      <c r="G58" s="62" t="inlineStr">
+        <is>
+          <t>Band_FM__Desconhecido__Promocao__09-03-2026_09-34-10.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="62" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:35:03</t>
+        </is>
+      </c>
+      <c r="B59" s="62" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C59" s="62" t="inlineStr">
+        <is>
+          <t>Desconhecido</t>
+        </is>
+      </c>
+      <c r="D59" s="62" t="inlineStr">
+        <is>
+          <t>Produto ou serviço desconhecido</t>
+        </is>
+      </c>
+      <c r="E59" s="62" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>O carro comprei, megafone, é hoje que você escuta a minha saudade hoje Olha o carro do ex, olha o beijo docinho, abraço, minha pegada gostosa Olha o carro do ex parando aqui na frente, aproveita a pro</t>
+        </is>
+      </c>
+      <c r="G59" s="62" t="inlineStr">
+        <is>
+          <t>Band_FM__Desconhecido__Produto_ou_servico_desconhecido__09-03-2026_09-35-03.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:35:56</t>
+        </is>
+      </c>
+      <c r="B60" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C60" s="67" t="inlineStr">
+        <is>
+          <t>Rede Móveis Casa Vende</t>
+        </is>
+      </c>
+      <c r="D60" s="67" t="inlineStr">
+        <is>
+          <t>Produtos para renovar a casa</t>
+        </is>
+      </c>
+      <c r="E60" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Não saia daí, já já tem muito mais músicas aqui na Band FM. Band FM Atenção Catanduva e região, é aniversário da Rede Móveis Casa Vende. Com ofertas especiais para renovar a sua casa. Produtos selecio</t>
+        </is>
+      </c>
+      <c r="G60" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM__Rede_Moveis_Casa_Vende__Produtos_para_renovar_a_casa__09-03-2026_09-35-56.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:36:33</t>
+        </is>
+      </c>
+      <c r="B61" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C61" s="67" t="inlineStr">
+        <is>
+          <t>Cressol</t>
+        </is>
+      </c>
+      <c r="D61" s="67" t="inlineStr">
+        <is>
+          <t>Promoção Operar é Ganhar</t>
+        </is>
+      </c>
+      <c r="E61" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dá pra contar com a sorte, né? Mas se a sorte te ajudar, você ainda pode ganhar 12 milhões em prêmios com a promoção Operar é Ganhar. Invista com a Cressol, gere números da sorte e concorra. Você vai </t>
+        </is>
+      </c>
+      <c r="G61" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM__Cressol__Promocao_Operar_e_Ganhar__09-03-2026_09-36-33__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:36:33</t>
+        </is>
+      </c>
+      <c r="B62" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C62" s="67" t="inlineStr">
+        <is>
+          <t>Alto Posto Campeão</t>
+        </is>
+      </c>
+      <c r="D62" s="67" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
+      <c r="E62" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dá pra contar com a sorte, né? Mas se a sorte te ajudar, você ainda pode ganhar 12 milhões em prêmios com a promoção Operar é Ganhar. Invista com a Cressol, gere números da sorte e concorra. Você vai </t>
+        </is>
+      </c>
+      <c r="G62" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM__Alto_Posto_Campeao__Combustivel__09-03-2026_09-36-33__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:36:50</t>
+        </is>
+      </c>
+      <c r="B63" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C63" s="67" t="inlineStr">
+        <is>
+          <t>Alto Posto Campeão</t>
+        </is>
+      </c>
+      <c r="D63" s="67" t="inlineStr">
+        <is>
+          <t>Combustível e conveniência</t>
+        </is>
+      </c>
+      <c r="E63" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Só poderá é ganhar Certificado de autorização SPAME, número 04047374 Alto Posto Campeão, o seu destino de qualidade em combustível Vá conhecer o Alto Posto Campeão, onde qualidade e preço campeão anda</t>
+        </is>
+      </c>
+      <c r="G63" s="67" t="inlineStr">
+        <is>
+          <t>Band_FM__Alto_Posto_Campeao__Combustivel_e_conveniencia__09-03-2026_09-36-50.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="67" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:37:08</t>
+        </is>
+      </c>
+      <c r="B64" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C64" s="67" t="inlineStr">
+        <is>
+          <t>UOL</t>
+        </is>
+      </c>
+      <c r="D64" s="67" t="inlineStr">
+        <is>
+          <t>Enquete do Big Brother 26</t>
+        </is>
+      </c>
+      <c r="E64" s="67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Rafa, que negócio do Babu, hein? Babu, eu vou te falar, hein, Babu? O Paulo mandou pra gente aqui, o nosso ouvinte, ele falou assim Ô Rafa, cola no site do UOL Vai lá no UOL que tem a enquete A enquet</t>
+        </is>
+      </c>
+      <c r="G64" s="67" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__UOL__Enquete_do_Big_Brother_26__09-03-2026_09-37-08.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="68" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:39:48</t>
+        </is>
+      </c>
+      <c r="B65" s="68" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C65" s="68" t="inlineStr">
+        <is>
+          <t>Grupo Moresque</t>
+        </is>
+      </c>
+      <c r="D65" s="68" t="inlineStr">
+        <is>
+          <t>Carnes e arroz</t>
+        </is>
+      </c>
+      <c r="E65" s="68" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>o mundo. Atenção para algumas das grandes ofertas do Grupo Moresque válidas até dia nove de março. Alcatra com a minha bovina quilo quarenta e três e noventa e nove contra filé bovino quilo quarenta e</t>
+        </is>
+      </c>
+      <c r="G65" s="68" t="inlineStr">
+        <is>
+          <t>Band_FM__Grupo_Moresque__Carnes_e_arroz__09-03-2026_09-39-48.mp3</t>
         </is>
       </c>
     </row>
@@ -813,7 +3101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,30 +3124,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jovem_Pan</t>
+          <t>Ondas_Verdes</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06/03/2026 12:38:54</t>
+          <t>09/03/2026 09:32:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ondas_Verdes</t>
+          <t>Jovem_Pan</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06/03/2026 13:48:56</t>
+          <t>09/03/2026 09:37:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:39:48</t>
         </is>
       </c>
     </row>

--- a/radio_capture/relatorio_anuncios.xlsx
+++ b/radio_capture/relatorio_anuncios.xlsx
@@ -42,7 +42,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -303,6 +308,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -673,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -723,27 +746,27 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:14</t>
         </is>
       </c>
-      <c r="B2" s="67" t="inlineStr">
+      <c r="B2" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C2" s="67" t="inlineStr">
+      <c r="C2" s="72" t="inlineStr">
         <is>
           <t>Casa dos Construtores</t>
         </is>
       </c>
-      <c r="D2" s="67" t="inlineStr">
+      <c r="D2" s="72" t="inlineStr">
         <is>
           <t>espaços para casas</t>
         </is>
       </c>
-      <c r="E2" s="67" t="inlineStr">
+      <c r="E2" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -753,34 +776,34 @@
           <t>Mas em como se vive? O tempo bem vivido é feito de escolhas, de detalhes que permanecem, de casas que acolhem, de memórias que resistem. Há 65 anos, criamos espaços para que cada instante não apenas p</t>
         </is>
       </c>
-      <c r="G2" s="67" t="inlineStr">
+      <c r="G2" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Casa_dos_Construtores__espacos_para_casas__09-03-2026_09-00-14__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:15</t>
         </is>
       </c>
-      <c r="B3" s="67" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C3" s="67" t="inlineStr">
+      <c r="C3" s="72" t="inlineStr">
         <is>
           <t>Ótica Fabriley</t>
         </is>
       </c>
-      <c r="D3" s="67" t="inlineStr">
+      <c r="D3" s="72" t="inlineStr">
         <is>
           <t>serviços de ótica</t>
         </is>
       </c>
-      <c r="E3" s="67" t="inlineStr">
+      <c r="E3" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -790,34 +813,34 @@
           <t>Mas em como se vive? O tempo bem vivido é feito de escolhas, de detalhes que permanecem, de casas que acolhem, de memórias que resistem. Há 65 anos, criamos espaços para que cada instante não apenas p</t>
         </is>
       </c>
-      <c r="G3" s="67" t="inlineStr">
+      <c r="G3" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Otica_Fabriley__servicos_de_otica__09-03-2026_09-00-15__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:31</t>
         </is>
       </c>
-      <c r="B4" s="67" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C4" s="67" t="inlineStr">
+      <c r="C4" s="72" t="inlineStr">
         <is>
           <t>ótica FabriLen</t>
         </is>
       </c>
-      <c r="D4" s="67" t="inlineStr">
+      <c r="D4" s="72" t="inlineStr">
         <is>
           <t>lentes</t>
         </is>
       </c>
-      <c r="E4" s="67" t="inlineStr">
+      <c r="E4" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -827,34 +850,34 @@
           <t>Cada instante, não apenas passe, mas fique. Casa dos Construtores, o melhor tempo na sua casa. Quando o assunto é visão, a ótica FabriLen é referência. Atendimento diferenciado com profissionais prepa</t>
         </is>
       </c>
-      <c r="G4" s="67" t="inlineStr">
+      <c r="G4" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__otica_FabriLen__lentes__09-03-2026_09-00-30.mp3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:33</t>
         </is>
       </c>
-      <c r="B5" s="67" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C5" s="67" t="inlineStr">
+      <c r="C5" s="72" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D5" s="67" t="inlineStr">
+      <c r="D5" s="72" t="inlineStr">
         <is>
           <t>Chocolate</t>
         </is>
       </c>
-      <c r="E5" s="67" t="inlineStr">
+      <c r="E5" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -864,34 +887,34 @@
           <t>Viu? Bob Sinclair na programação número 1 do seu rádio, vocês viram aí, aliás, ouviram, né? Vai, Tassonzão! Tonsera, né, pra gente curtir aqui na programação. Jovem Pan, daqui a pouquinho, depois de i</t>
         </is>
       </c>
-      <c r="G5" s="67" t="inlineStr">
+      <c r="G5" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show__Chocolate__09-03-2026_09-00-33.mp3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:48</t>
         </is>
       </c>
-      <c r="B6" s="67" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="C6" s="72" t="inlineStr">
         <is>
           <t>Noblen</t>
         </is>
       </c>
-      <c r="D6" s="67" t="inlineStr">
+      <c r="D6" s="72" t="inlineStr">
         <is>
           <t>lentes multifocais digitais e lentes de visão simples</t>
         </is>
       </c>
-      <c r="E6" s="67" t="inlineStr">
+      <c r="E6" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -901,34 +924,34 @@
           <t>Preparados para orientar você com atenção e confiança. As lentes são produzidas com alta tecnologia, garantindo precisão e conforto para o dia a dia. E tem promoção especial. Na compra do primeiro par</t>
         </is>
       </c>
-      <c r="G6" s="67" t="inlineStr">
+      <c r="G6" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Noblen__lentes_multifocais_digitais_e_lentes_de_visao_simples__09-03-2026_09-00-48.mp3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:50</t>
         </is>
       </c>
-      <c r="B7" s="67" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C7" s="67" t="inlineStr">
+      <c r="C7" s="72" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D7" s="67" t="inlineStr">
+      <c r="D7" s="72" t="inlineStr">
         <is>
           <t>chocolate</t>
         </is>
       </c>
-      <c r="E7" s="67" t="inlineStr">
+      <c r="E7" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -938,34 +961,34 @@
           <t>Número 1 do Brasil e... e... e... Cacau Show! Aquele chocolate maravilhoso, aquele chocolate refinado, aquele sabor... Hummm... já vai dando assim o negócio, é de louco, né? Quer levar pra casa? Então</t>
         </is>
       </c>
-      <c r="G7" s="67" t="inlineStr">
+      <c r="G7" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show__chocolate__09-03-2026_09-00-50.mp3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:01:04</t>
         </is>
       </c>
-      <c r="B8" s="67" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C8" s="67" t="inlineStr">
+      <c r="C8" s="72" t="inlineStr">
         <is>
           <t>Óticas FabriLem</t>
         </is>
       </c>
-      <c r="D8" s="67" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>lentes de visão simples com antirreflexo e filtro de luz azul</t>
         </is>
       </c>
-      <c r="E8" s="67" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -975,7 +998,7 @@
           <t>digitais noblem com antirreflexo, o segundo par é grátis. E mais, lentes de visão simples com antirreflexo e filtro de luz azul em até dez vezes de dezoito e noventa. Visite a loja na Rua Brasil Esqui</t>
         </is>
       </c>
-      <c r="G8" s="67" t="inlineStr">
+      <c r="G8" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Oticas_FabriLem__lentes_de_visao_simples_com_antirreflexo_e_filtro_de_luz_azu__09-03-2026_09-01-04__ad1.mp3</t>
         </is>
@@ -1019,27 +1042,27 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:01:21</t>
         </is>
       </c>
-      <c r="B10" s="67" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C10" s="67" t="inlineStr">
+      <c r="C10" s="72" t="inlineStr">
         <is>
           <t>Amaral Centro Automotivo Multimarcas</t>
         </is>
       </c>
-      <c r="D10" s="67" t="inlineStr">
+      <c r="D10" s="72" t="inlineStr">
         <is>
           <t>serviços automotivos</t>
         </is>
       </c>
-      <c r="E10" s="67" t="inlineStr">
+      <c r="E10" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1049,34 +1072,34 @@
           <t>FabriLem, a fábrica da sua lente. Amaral Centro Automotivo Multimarcas agradece a todos o carinho e a confiança no trabalho realizado com sua equipe de profissionais. Hoje estamos em novo endereço par</t>
         </is>
       </c>
-      <c r="G10" s="67" t="inlineStr">
+      <c r="G10" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Amaral_Centro_Automotivo_Multimarcas__servicos_automotivos__09-03-2026_09-01-21.mp3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:02:10</t>
         </is>
       </c>
-      <c r="B11" s="67" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C11" s="67" t="inlineStr">
+      <c r="C11" s="72" t="inlineStr">
         <is>
           <t>Unifipa</t>
         </is>
       </c>
-      <c r="D11" s="67" t="inlineStr">
+      <c r="D11" s="72" t="inlineStr">
         <is>
           <t>Cursos de graduação</t>
         </is>
       </c>
-      <c r="E11" s="67" t="inlineStr">
+      <c r="E11" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1086,7 +1109,7 @@
           <t>São onze opções de cursos de graduação na instituição que tem mais de cinquenta e cinco anos de tradição e é sinônimo de excelência em ensino com nota máxima na avaliação do MEC. Venha ser Unifipa. In</t>
         </is>
       </c>
-      <c r="G11" s="67" t="inlineStr">
+      <c r="G11" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Unifipa__Cursos_de_graduacao__09-03-2026_09-02-10__ad1.mp3</t>
         </is>
@@ -1130,27 +1153,27 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:02:27</t>
         </is>
       </c>
-      <c r="B13" s="67" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C13" s="67" t="inlineStr">
+      <c r="C13" s="72" t="inlineStr">
         <is>
           <t>Cicred</t>
         </is>
       </c>
-      <c r="D13" s="67" t="inlineStr">
+      <c r="D13" s="72" t="inlineStr">
         <is>
           <t>Poupança premiada</t>
         </is>
       </c>
-      <c r="E13" s="67" t="inlineStr">
+      <c r="E13" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1160,34 +1183,34 @@
           <t>A Unipipa, referência que transforma vidas. Aqui é a Nagacela, é hora de sonhar alto. A poupança premiada Cicred tá aí. Cicred, poupança é premiada Pra fazer tudo o que você sonhava Tem milhões em ben</t>
         </is>
       </c>
-      <c r="G13" s="67" t="inlineStr">
+      <c r="G13" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Cicred__Poupanca_premiada__09-03-2026_09-02-27.mp3</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:02:43</t>
         </is>
       </c>
-      <c r="B14" s="67" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C14" s="67" t="inlineStr">
+      <c r="C14" s="72" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D14" s="67" t="inlineStr">
+      <c r="D14" s="72" t="inlineStr">
         <is>
           <t>Produtos para Páscoa (chocolate, ovo de Páscoa, peixe, etc.)</t>
         </is>
       </c>
-      <c r="E14" s="67" t="inlineStr">
+      <c r="E14" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1197,34 +1220,34 @@
           <t>São mais de 600 ganhadores, 5 milhões em prêmios em dinheiro. Volte no Cicred e concorra! O Baré Show, olha onde eu tô! Corre para conferir os preços imperdíveis do Max e garanta sua Páscoa! Olha, tem</t>
         </is>
       </c>
-      <c r="G14" s="67" t="inlineStr">
+      <c r="G14" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Max__Produtos_para_Pascoa__chocolate__ovo_de_Pascoa__peixe__etc__09-03-2026_09-02-43__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:02:43</t>
         </is>
       </c>
-      <c r="B15" s="67" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C15" s="67" t="inlineStr">
+      <c r="C15" s="72" t="inlineStr">
         <is>
           <t>Cicred</t>
         </is>
       </c>
-      <c r="D15" s="67" t="inlineStr">
+      <c r="D15" s="72" t="inlineStr">
         <is>
           <t>Concurso com prêmios em dinheiro</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1234,34 +1257,34 @@
           <t>São mais de 600 ganhadores, 5 milhões em prêmios em dinheiro. Volte no Cicred e concorra! O Baré Show, olha onde eu tô! Corre para conferir os preços imperdíveis do Max e garanta sua Páscoa! Olha, tem</t>
         </is>
       </c>
-      <c r="G15" s="67" t="inlineStr">
+      <c r="G15" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Cicred__Concurso_com_premios_em_dinheiro__09-03-2026_09-02-43__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:00</t>
         </is>
       </c>
-      <c r="B16" s="67" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C16" s="67" t="inlineStr">
+      <c r="C16" s="72" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D16" s="67" t="inlineStr">
+      <c r="D16" s="72" t="inlineStr">
         <is>
           <t>Produtos para Páscoa (chocolate, ovo de Páscoa, peixe, etc.)</t>
         </is>
       </c>
-      <c r="E16" s="67" t="inlineStr">
+      <c r="E16" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1271,34 +1294,34 @@
           <t>Corre para conferir os preços imperdíveis do Max e garanta sua Páscoa. Olha, tem chocolate, ovo de Páscoa, peixe e muito mais. Tudo com preço baixinho pra você aproveitar. Filé de peito lá no quilo 14</t>
         </is>
       </c>
-      <c r="G16" s="67" t="inlineStr">
+      <c r="G16" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Max__Produtos_para_Pascoa__chocolate__ovo_de_Pascoa__peixe__etc__09-03-2026_09-03-00.mp3</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="67" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:14</t>
         </is>
       </c>
-      <c r="B17" s="67" t="inlineStr">
+      <c r="B17" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C17" s="67" t="inlineStr">
+      <c r="C17" s="72" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="D17" s="67" t="inlineStr">
+      <c r="D17" s="72" t="inlineStr">
         <is>
           <t>BTS The Comeback Live</t>
         </is>
       </c>
-      <c r="E17" s="67" t="inlineStr">
+      <c r="E17" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1308,34 +1331,34 @@
           <t xml:space="preserve">Uma delas é o trailer do especial da Netflix, BTS The Comeback Live, que chega à plataforma no próximo dia 20. O filme faz parte da poderosa campanha promocional do álbum I Run dos reis do K-Pop. Pra </t>
         </is>
       </c>
-      <c r="G17" s="67" t="inlineStr">
+      <c r="G17" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Netflix__BTS_The_Comeback_Live__09-03-2026_09-03-14.mp3</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="67" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:16</t>
         </is>
       </c>
-      <c r="B18" s="67" t="inlineStr">
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C18" s="67" t="inlineStr">
+      <c r="C18" s="72" t="inlineStr">
         <is>
           <t>Sete Farinha Globo</t>
         </is>
       </c>
-      <c r="D18" s="67" t="inlineStr">
+      <c r="D18" s="72" t="inlineStr">
         <is>
           <t>Farinha</t>
         </is>
       </c>
-      <c r="E18" s="67" t="inlineStr">
+      <c r="E18" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1345,34 +1368,34 @@
           <t>sete farinha globo, um quilo, dois e quarenta e sete. Tó de trezentos e setenta gramas, sete e noventa e nove. Mussarela a partir de vinte e seis e noventa um quilo. Papel Supra, vinte e nove e novent</t>
         </is>
       </c>
-      <c r="G18" s="67" t="inlineStr">
+      <c r="G18" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Sete_Farinha_Globo__Farinha__09-03-2026_09-03-16__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="67" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:16</t>
         </is>
       </c>
-      <c r="B19" s="67" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C19" s="67" t="inlineStr">
+      <c r="C19" s="72" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D19" s="67" t="inlineStr">
+      <c r="D19" s="72" t="inlineStr">
         <is>
           <t>Pasta</t>
         </is>
       </c>
-      <c r="E19" s="67" t="inlineStr">
+      <c r="E19" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1382,34 +1405,34 @@
           <t>sete farinha globo, um quilo, dois e quarenta e sete. Tó de trezentos e setenta gramas, sete e noventa e nove. Mussarela a partir de vinte e seis e noventa um quilo. Papel Supra, vinte e nove e novent</t>
         </is>
       </c>
-      <c r="G19" s="67" t="inlineStr">
+      <c r="G19" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Max__Pasta__09-03-2026_09-03-16__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="67" t="inlineStr">
+      <c r="A20" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:16</t>
         </is>
       </c>
-      <c r="B20" s="67" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C20" s="67" t="inlineStr">
+      <c r="C20" s="72" t="inlineStr">
         <is>
           <t>Drogaria Total Popular</t>
         </is>
       </c>
-      <c r="D20" s="67" t="inlineStr">
+      <c r="D20" s="72" t="inlineStr">
         <is>
           <t>Remédios</t>
         </is>
       </c>
-      <c r="E20" s="67" t="inlineStr">
+      <c r="E20" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1419,34 +1442,34 @@
           <t>sete farinha globo, um quilo, dois e quarenta e sete. Tó de trezentos e setenta gramas, sete e noventa e nove. Mussarela a partir de vinte e seis e noventa um quilo. Papel Supra, vinte e nove e novent</t>
         </is>
       </c>
-      <c r="G20" s="67" t="inlineStr">
+      <c r="G20" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Drogaria_Total_Popular__Remedios__09-03-2026_09-03-16__ad3.mp3</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="67" t="inlineStr">
+      <c r="A21" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:32</t>
         </is>
       </c>
-      <c r="B21" s="67" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C21" s="67" t="inlineStr">
+      <c r="C21" s="72" t="inlineStr">
         <is>
           <t>Doutor Alex Baraldo Portes</t>
         </is>
       </c>
-      <c r="D21" s="67" t="inlineStr">
+      <c r="D21" s="72" t="inlineStr">
         <is>
           <t>Serviços de Otorrino Laringologista</t>
         </is>
       </c>
-      <c r="E21" s="67" t="inlineStr">
+      <c r="E21" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1456,34 +1479,34 @@
           <t xml:space="preserve">Jovem Pan. Jovem Pan Brasil. Você está ouvindo. Manhã Pan. Catanduva. Oferecimento. Doutor Alex Baraldo Portes. Otorrino Laringologista. RQE 64202. Vive em empreendimentos. Municipa Catanduva. Doutor </t>
         </is>
       </c>
-      <c r="G21" s="67" t="inlineStr">
+      <c r="G21" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_Otorrino_Laringologista__09-03-2026_09-03-32__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="67" t="inlineStr">
+      <c r="A22" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:32</t>
         </is>
       </c>
-      <c r="B22" s="67" t="inlineStr">
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C22" s="67" t="inlineStr">
+      <c r="C22" s="72" t="inlineStr">
         <is>
           <t>IGA Proteção Veicular</t>
         </is>
       </c>
-      <c r="D22" s="67" t="inlineStr">
+      <c r="D22" s="72" t="inlineStr">
         <is>
           <t>Proteção Veicular</t>
         </is>
       </c>
-      <c r="E22" s="67" t="inlineStr">
+      <c r="E22" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1493,34 +1516,34 @@
           <t xml:space="preserve">Jovem Pan. Jovem Pan Brasil. Você está ouvindo. Manhã Pan. Catanduva. Oferecimento. Doutor Alex Baraldo Portes. Otorrino Laringologista. RQE 64202. Vive em empreendimentos. Municipa Catanduva. Doutor </t>
         </is>
       </c>
-      <c r="G22" s="67" t="inlineStr">
+      <c r="G22" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__IGA_Protecao_Veicular__Protecao_Veicular__09-03-2026_09-03-32__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="67" t="inlineStr">
+      <c r="A23" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:50</t>
         </is>
       </c>
-      <c r="B23" s="67" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C23" s="67" t="inlineStr">
+      <c r="C23" s="72" t="inlineStr">
         <is>
           <t>Doutor Alex Baraldo Portes</t>
         </is>
       </c>
-      <c r="D23" s="67" t="inlineStr">
+      <c r="D23" s="72" t="inlineStr">
         <is>
           <t>Serviços de otorrino laringologista</t>
         </is>
       </c>
-      <c r="E23" s="67" t="inlineStr">
+      <c r="E23" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1530,34 +1553,34 @@
           <t>Municipal, município de Catanduva, doutor Cristiano Herrera e GA Proteção Veicular. Nariz entupido, incômodos no ouvido, nariz ou garganta? Sua saúde pode estar precisando de atenção. Quando você sent</t>
         </is>
       </c>
-      <c r="G23" s="67" t="inlineStr">
+      <c r="G23" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_otorrino_laringologista__09-03-2026_09-03-50.mp3</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="67" t="inlineStr">
+      <c r="A24" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:08</t>
         </is>
       </c>
-      <c r="B24" s="67" t="inlineStr">
+      <c r="B24" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C24" s="67" t="inlineStr">
+      <c r="C24" s="72" t="inlineStr">
         <is>
           <t>Doutor Alex Baraldo Portes</t>
         </is>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="72" t="inlineStr">
         <is>
           <t>Serviços de otorrino-laringologia</t>
         </is>
       </c>
-      <c r="E24" s="67" t="inlineStr">
+      <c r="E24" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1567,34 +1590,34 @@
           <t>Cuida do nariz, ouvido e garganta. Não perca o foco da sua saúde. Essa é uma mensagem do doutor Alex Baraldo Portes, que é otorrino-laringologista. CRM 137582, RQE 64202. Lá no Instagram do doutor Ale</t>
         </is>
       </c>
-      <c r="G24" s="67" t="inlineStr">
+      <c r="G24" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_otorrino-laringologia__09-03-2026_09-04-08__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="A25" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:08</t>
         </is>
       </c>
-      <c r="B25" s="67" t="inlineStr">
+      <c r="B25" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="72" t="inlineStr">
         <is>
           <t>Unifipa Catanduva</t>
         </is>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="72" t="inlineStr">
         <is>
           <t>Vestibular continuado 2026</t>
         </is>
       </c>
-      <c r="E25" s="67" t="inlineStr">
+      <c r="E25" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1604,34 +1627,34 @@
           <t>Cuida do nariz, ouvido e garganta. Não perca o foco da sua saúde. Essa é uma mensagem do doutor Alex Baraldo Portes, que é otorrino-laringologista. CRM 137582, RQE 64202. Lá no Instagram do doutor Ale</t>
         </is>
       </c>
-      <c r="G25" s="67" t="inlineStr">
+      <c r="G25" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Unifipa_Catanduva__Vestibular_continuado_2026__09-03-2026_09-04-08__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="67" t="inlineStr">
+      <c r="A26" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:22</t>
         </is>
       </c>
-      <c r="B26" s="67" t="inlineStr">
+      <c r="B26" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C26" s="67" t="inlineStr">
+      <c r="C26" s="72" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="D26" s="67" t="inlineStr">
+      <c r="D26" s="72" t="inlineStr">
         <is>
           <t>Serviço de streaming</t>
         </is>
       </c>
-      <c r="E26" s="67" t="inlineStr">
+      <c r="E26" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1641,34 +1664,34 @@
           <t>Ligue agora ou mande um zap, dezessete três um cinco um mil, ou acesse NetflixBR.com. É Netflix! A FM da gente, Ondas Verde! A sua manhã fica completa na Ondas Verdes.</t>
         </is>
       </c>
-      <c r="G26" s="67" t="inlineStr">
+      <c r="G26" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Netflix__Servico_de_streaming__09-03-2026_09-04-22.mp3</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="67" t="inlineStr">
+      <c r="A27" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:44</t>
         </is>
       </c>
-      <c r="B27" s="67" t="inlineStr">
+      <c r="B27" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C27" s="67" t="inlineStr">
+      <c r="C27" s="72" t="inlineStr">
         <is>
           <t>Unifipa</t>
         </is>
       </c>
-      <c r="D27" s="67" t="inlineStr">
+      <c r="D27" s="72" t="inlineStr">
         <is>
           <t>Inscrições e provas online</t>
         </is>
       </c>
-      <c r="E27" s="67" t="inlineStr">
+      <c r="E27" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1678,34 +1701,34 @@
           <t>é que venha ser Unifipa, inscrições e provas online em unifipa.com.br barra vestibular. Unifipa, referência que transforma vidas. A clínica do doutor Cristiano Herrera, gente, atenção, é referência na</t>
         </is>
       </c>
-      <c r="G27" s="67" t="inlineStr">
+      <c r="G27" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Unifipa__Inscricoes_e_provas_online__09-03-2026_09-04-44__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="67" t="inlineStr">
+      <c r="A28" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:45</t>
         </is>
       </c>
-      <c r="B28" s="67" t="inlineStr">
+      <c r="B28" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C28" s="67" t="inlineStr">
+      <c r="C28" s="72" t="inlineStr">
         <is>
           <t>Clínica do Doutor Cristiano Herrera</t>
         </is>
       </c>
-      <c r="D28" s="67" t="inlineStr">
+      <c r="D28" s="72" t="inlineStr">
         <is>
           <t>Serviços de psicologia, neuropsicologia e psicopedagogia</t>
         </is>
       </c>
-      <c r="E28" s="67" t="inlineStr">
+      <c r="E28" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1715,34 +1738,34 @@
           <t>é que venha ser Unifipa, inscrições e provas online em unifipa.com.br barra vestibular. Unifipa, referência que transforma vidas. A clínica do doutor Cristiano Herrera, gente, atenção, é referência na</t>
         </is>
       </c>
-      <c r="G28" s="67" t="inlineStr">
+      <c r="G28" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Clinica_do_Doutor_Cristiano_Herrera__Servicos_de_psicologia__neuropsicologia_e_psicopedagogia__09-03-2026_09-04-45__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="67" t="inlineStr">
+      <c r="A29" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:02</t>
         </is>
       </c>
-      <c r="B29" s="67" t="inlineStr">
+      <c r="B29" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C29" s="67" t="inlineStr">
+      <c r="C29" s="72" t="inlineStr">
         <is>
           <t>Doutor Cristiano Herrera</t>
         </is>
       </c>
-      <c r="D29" s="67" t="inlineStr">
+      <c r="D29" s="72" t="inlineStr">
         <is>
           <t>Serviços de psicopedagogia e neuropsicologia</t>
         </is>
       </c>
-      <c r="E29" s="67" t="inlineStr">
+      <c r="E29" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1752,34 +1775,34 @@
           <t>Psicopedagogia, através da avaliação neuropsicológica com a equipe multidisciplinar, que você vai encontrar lá, pessoal maravilhoso, o doutor Cristiano Herrera, ele utiliza testes em escalas mais efet</t>
         </is>
       </c>
-      <c r="G29" s="67" t="inlineStr">
+      <c r="G29" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Cristiano_Herrera__Servicos_de_psicopedagogia_e_neuropsicologia__09-03-2026_09-05-02__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="67" t="inlineStr">
+      <c r="A30" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:03</t>
         </is>
       </c>
-      <c r="B30" s="67" t="inlineStr">
+      <c r="B30" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C30" s="67" t="inlineStr">
+      <c r="C30" s="72" t="inlineStr">
         <is>
           <t>Doutor Cristian Aranjeira</t>
         </is>
       </c>
-      <c r="D30" s="67" t="inlineStr">
+      <c r="D30" s="72" t="inlineStr">
         <is>
           <t>Serviços de psicologia e neuropsicologia</t>
         </is>
       </c>
-      <c r="E30" s="67" t="inlineStr">
+      <c r="E30" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1789,34 +1812,34 @@
           <t>Psicopedagogia, através da avaliação neuropsicológica com a equipe multidisciplinar, que você vai encontrar lá, pessoal maravilhoso, o doutor Cristiano Herrera, ele utiliza testes em escalas mais efet</t>
         </is>
       </c>
-      <c r="G30" s="67" t="inlineStr">
+      <c r="G30" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Cristian_Aranjeira__Servicos_de_psicologia_e_neuropsicologia__09-03-2026_09-05-03__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="67" t="inlineStr">
+      <c r="A31" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:21</t>
         </is>
       </c>
-      <c r="B31" s="67" t="inlineStr">
+      <c r="B31" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C31" s="67" t="inlineStr">
+      <c r="C31" s="72" t="inlineStr">
         <is>
           <t>Clínica do Dr. Cristiano Herrera</t>
         </is>
       </c>
-      <c r="D31" s="67" t="inlineStr">
+      <c r="D31" s="72" t="inlineStr">
         <is>
           <t>Serviços de psicologia e neuroreabilitação</t>
         </is>
       </c>
-      <c r="E31" s="67" t="inlineStr">
+      <c r="E31" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1826,34 +1849,34 @@
           <t>inclusive os tratamentos não medicamentosos, por exemplo, como neuromodulação e biofeedback. O doutor Cristiano Herrera, ele é psicólogo, neuropsicólogo formado pela USP, especialista em neuroreabilit</t>
         </is>
       </c>
-      <c r="G31" s="67" t="inlineStr">
+      <c r="G31" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Clinica_do_Dr__Cristiano_Herrera__Servicos_de_psicologia_e_neuroreabilitacao__09-03-2026_09-05-21.mp3</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="67" t="inlineStr">
+      <c r="A32" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:39</t>
         </is>
       </c>
-      <c r="B32" s="67" t="inlineStr">
+      <c r="B32" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C32" s="67" t="inlineStr">
+      <c r="C32" s="72" t="inlineStr">
         <is>
           <t>Antunes Mais</t>
         </is>
       </c>
-      <c r="D32" s="67" t="inlineStr">
+      <c r="D32" s="72" t="inlineStr">
         <is>
           <t>Arroz seleto e feijão carioca</t>
         </is>
       </c>
-      <c r="E32" s="67" t="inlineStr">
+      <c r="E32" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1863,34 +1886,34 @@
           <t xml:space="preserve">O segundo andar, então acesse arroba DR Cristiano Herrera no Instagram. Liga a fã no Instagram, arroba jovem fã Catanduba. Comece a semana com mais economia no Antunes Mais. Confira arroz seleto tipo </t>
         </is>
       </c>
-      <c r="G32" s="67" t="inlineStr">
+      <c r="G32" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Antunes_Mais__Arroz_seleto_e_feijao_carioca__09-03-2026_09-05-39__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="67" t="inlineStr">
+      <c r="A33" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:39</t>
         </is>
       </c>
-      <c r="B33" s="67" t="inlineStr">
+      <c r="B33" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C33" s="67" t="inlineStr">
+      <c r="C33" s="72" t="inlineStr">
         <is>
           <t>Clube do Precinho</t>
         </is>
       </c>
-      <c r="D33" s="67" t="inlineStr">
+      <c r="D33" s="72" t="inlineStr">
         <is>
           <t>Músculo bovino e cortes de carne</t>
         </is>
       </c>
-      <c r="E33" s="67" t="inlineStr">
+      <c r="E33" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1900,34 +1923,34 @@
           <t xml:space="preserve">O segundo andar, então acesse arroba DR Cristiano Herrera no Instagram. Liga a fã no Instagram, arroba jovem fã Catanduba. Comece a semana com mais economia no Antunes Mais. Confira arroz seleto tipo </t>
         </is>
       </c>
-      <c r="G33" s="67" t="inlineStr">
+      <c r="G33" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Clube_do_Precinho__Musculo_bovino_e_cortes_de_carne__09-03-2026_09-05-39__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="67" t="inlineStr">
+      <c r="A34" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:57</t>
         </is>
       </c>
-      <c r="B34" s="67" t="inlineStr">
+      <c r="B34" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C34" s="67" t="inlineStr">
+      <c r="C34" s="72" t="inlineStr">
         <is>
           <t>Antunes Mais</t>
         </is>
       </c>
-      <c r="D34" s="67" t="inlineStr">
+      <c r="D34" s="72" t="inlineStr">
         <is>
           <t>Produtos variados (feijão, carne, detergente, etc.)</t>
         </is>
       </c>
-      <c r="E34" s="67" t="inlineStr">
+      <c r="E34" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1937,34 +1960,34 @@
           <t>onze e noventa e nove, feijão carioca seleto, pacote um quilo, seis e noventa e nove, tem também as ofertas do Clube do Precinho, acenho, músculo bovino, trinta e quatro e noventa e cinco quilo, colch</t>
         </is>
       </c>
-      <c r="G34" s="67" t="inlineStr">
+      <c r="G34" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Antunes_Mais__Produtos_variados__feijao__carne__detergente__etc__09-03-2026_09-05-57.mp3</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="67" t="inlineStr">
+      <c r="A35" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:06:15</t>
         </is>
       </c>
-      <c r="B35" s="67" t="inlineStr">
+      <c r="B35" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C35" s="67" t="inlineStr">
+      <c r="C35" s="72" t="inlineStr">
         <is>
           <t>Antunes Mais</t>
         </is>
       </c>
-      <c r="D35" s="67" t="inlineStr">
+      <c r="D35" s="72" t="inlineStr">
         <is>
           <t>Produtos com descontos</t>
         </is>
       </c>
-      <c r="E35" s="67" t="inlineStr">
+      <c r="E35" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1974,34 +1997,34 @@
           <t>O Festas Válidas, até dia onze, no Antunes Mais. As melhores lojas de Catanduva, reunidas em um único lugar, com até setenta por cento off. Você já sabe de qual evento estamos falando? Bazar chique, é</t>
         </is>
       </c>
-      <c r="G35" s="67" t="inlineStr">
+      <c r="G35" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Antunes_Mais__Produtos_com_descontos__09-03-2026_09-06-15__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="67" t="inlineStr">
+      <c r="A36" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:06:15</t>
         </is>
       </c>
-      <c r="B36" s="67" t="inlineStr">
+      <c r="B36" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C36" s="67" t="inlineStr">
+      <c r="C36" s="72" t="inlineStr">
         <is>
           <t>Bazar Chique</t>
         </is>
       </c>
-      <c r="D36" s="67" t="inlineStr">
+      <c r="D36" s="72" t="inlineStr">
         <is>
           <t>Roupas, acessórios, calçados, óticas</t>
         </is>
       </c>
-      <c r="E36" s="67" t="inlineStr">
+      <c r="E36" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2011,34 +2034,34 @@
           <t>O Festas Válidas, até dia onze, no Antunes Mais. As melhores lojas de Catanduva, reunidas em um único lugar, com até setenta por cento off. Você já sabe de qual evento estamos falando? Bazar chique, é</t>
         </is>
       </c>
-      <c r="G36" s="67" t="inlineStr">
+      <c r="G36" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Bazar_Chique__Roupas__acessorios__calcados__oticas__09-03-2026_09-06-15__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="67" t="inlineStr">
+      <c r="A37" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:06:33</t>
         </is>
       </c>
-      <c r="B37" s="67" t="inlineStr">
+      <c r="B37" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C37" s="67" t="inlineStr">
+      <c r="C37" s="72" t="inlineStr">
         <is>
           <t>SimComércio e Vive Empre</t>
         </is>
       </c>
-      <c r="D37" s="67" t="inlineStr">
+      <c r="D37" s="72" t="inlineStr">
         <is>
           <t>Feira ou evento de vendas</t>
         </is>
       </c>
-      <c r="E37" s="67" t="inlineStr">
+      <c r="E37" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2048,34 +2071,34 @@
           <t>e muito mais com preços imperdíveis. Dias 19, 20 e 21 de março, na sede do SimComércio, Avenida Benedito Zancaner, 720, quinta e sexta, das nove às vinte e duas horas. Sábado, das nove às dezessete ho</t>
         </is>
       </c>
-      <c r="G37" s="67" t="inlineStr">
+      <c r="G37" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__SimComercio_e_Vive_Empre__Feira_ou_evento_de_vendas__09-03-2026_09-06-33.mp3</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="A38" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:06:52</t>
         </is>
       </c>
-      <c r="B38" s="67" t="inlineStr">
+      <c r="B38" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C38" s="67" t="inlineStr">
+      <c r="C38" s="72" t="inlineStr">
         <is>
           <t>Vive Empreendimentos</t>
         </is>
       </c>
-      <c r="D38" s="67" t="inlineStr">
+      <c r="D38" s="72" t="inlineStr">
         <is>
           <t>empreendimentos imobiliários</t>
         </is>
       </c>
-      <c r="E38" s="67" t="inlineStr">
+      <c r="E38" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2085,34 +2108,34 @@
           <t>Olha, se tem uma empresa que vem transformando o jeito de viver dos últimos anos, essa empresa seguramente é a Vive Empreendimentos. Nascida em Catanduva, a Vive hoje está presente em quatro estados d</t>
         </is>
       </c>
-      <c r="G38" s="67" t="inlineStr">
+      <c r="G38" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Vive_Empreendimentos__empreendimentos_imobiliarios__09-03-2026_09-06-52.mp3</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="67" t="inlineStr">
+      <c r="A39" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:07:08</t>
         </is>
       </c>
-      <c r="B39" s="67" t="inlineStr">
+      <c r="B39" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C39" s="67" t="inlineStr">
+      <c r="C39" s="72" t="inlineStr">
         <is>
           <t>Vive</t>
         </is>
       </c>
-      <c r="D39" s="67" t="inlineStr">
+      <c r="D39" s="72" t="inlineStr">
         <is>
           <t>Loteamentos e espaços planejados</t>
         </is>
       </c>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2122,34 +2145,34 @@
           <t>Atenção, São Paulo, Mato Grosso do Sul, Minas Gerais e Goiás. Sempre levando desempenho com responsabilidade, sustentabilidade e muita inovação. Quem conhece os projetos da Vive sabe, não são apenas l</t>
         </is>
       </c>
-      <c r="G39" s="67" t="inlineStr">
+      <c r="G39" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Vive__Loteamentos_e_espacos_planejados__09-03-2026_09-07-08.mp3</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="67" t="inlineStr">
+      <c r="A40" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:07:26</t>
         </is>
       </c>
-      <c r="B40" s="67" t="inlineStr">
+      <c r="B40" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C40" s="67" t="inlineStr">
+      <c r="C40" s="72" t="inlineStr">
         <is>
           <t>VIB</t>
         </is>
       </c>
-      <c r="D40" s="67" t="inlineStr">
+      <c r="D40" s="72" t="inlineStr">
         <is>
           <t>empreendimentos imobiliários</t>
         </is>
       </c>
-      <c r="E40" s="67" t="inlineStr">
+      <c r="E40" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2159,34 +2182,34 @@
           <t>para oferecer mais qualidade de vida, contato com a natureza e toda a infraestrutura que as famílias procuram para viver bem. E tem mais, como coligada no grupo Serradinho, a VIB carrega a credibilida</t>
         </is>
       </c>
-      <c r="G40" s="67" t="inlineStr">
+      <c r="G40" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__VIB__empreendimentos_imobiliarios__09-03-2026_09-07-26.mp3</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="67" t="inlineStr">
+      <c r="A41" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:07:44</t>
         </is>
       </c>
-      <c r="B41" s="67" t="inlineStr">
+      <c r="B41" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C41" s="67" t="inlineStr">
+      <c r="C41" s="72" t="inlineStr">
         <is>
           <t>Oralfai Catanduva</t>
         </is>
       </c>
-      <c r="D41" s="67" t="inlineStr">
+      <c r="D41" s="72" t="inlineStr">
         <is>
           <t>tratamentos odontológicos</t>
         </is>
       </c>
-      <c r="E41" s="67" t="inlineStr">
+      <c r="E41" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2196,34 +2219,34 @@
           <t xml:space="preserve">Visão de futuro e compromisso com as cidades onde atua, vive empreendimentos conectando pessoas, criando novas formas de viver e mudando o futuro. Jovem Pan Olá, eu sou o doutor Guilherme Pelegrin da </t>
         </is>
       </c>
-      <c r="G41" s="67" t="inlineStr">
+      <c r="G41" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Oralfai_Catanduva__tratamentos_odontologicos__09-03-2026_09-07-44.mp3</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="67" t="inlineStr">
+      <c r="A42" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:08:38</t>
         </is>
       </c>
-      <c r="B42" s="67" t="inlineStr">
+      <c r="B42" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C42" s="67" t="inlineStr">
+      <c r="C42" s="72" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D42" s="67" t="inlineStr">
+      <c r="D42" s="72" t="inlineStr">
         <is>
           <t>Ovos de Páscoa e tabletes</t>
         </is>
       </c>
-      <c r="E42" s="67" t="inlineStr">
+      <c r="E42" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2233,34 +2256,34 @@
           <t>E nos momentos em memórias que ficam para sempre. E quando o assunto é celebrar com sabor, a escolha é uma só. Cacau Show. Ovos de Páscoa encantadores. Tabletes irresistíveis. Presentes que emocionam.</t>
         </is>
       </c>
-      <c r="G42" s="67" t="inlineStr">
+      <c r="G42" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show__Ovos_de_Pascoa_e_tabletes__09-03-2026_09-08-38.mp3</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="67" t="inlineStr">
+      <c r="A43" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:09:51</t>
         </is>
       </c>
-      <c r="B43" s="67" t="inlineStr">
+      <c r="B43" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C43" s="67" t="inlineStr">
+      <c r="C43" s="72" t="inlineStr">
         <is>
           <t>Jovem Pan</t>
         </is>
       </c>
-      <c r="D43" s="67" t="inlineStr">
+      <c r="D43" s="72" t="inlineStr">
         <is>
           <t>Cobertura da Copa do Mundo</t>
         </is>
       </c>
-      <c r="E43" s="67" t="inlineStr">
+      <c r="E43" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2270,34 +2293,34 @@
           <t>Agora é dois mil e vinte e seis. Estados Unidos, México e Canadá. Desde sempre, a Jovem Pan está presente nas Copas do Mundo com equipe completa, informação em tempo real, opinião forte e a energia de</t>
         </is>
       </c>
-      <c r="G43" s="67" t="inlineStr">
+      <c r="G43" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Jovem_Pan__Cobertura_da_Copa_do_Mundo__09-03-2026_09-09-51.mp3</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="67" t="inlineStr">
+      <c r="A44" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:14:02</t>
         </is>
       </c>
-      <c r="B44" s="67" t="inlineStr">
+      <c r="B44" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C44" s="67" t="inlineStr">
+      <c r="C44" s="72" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D44" s="67" t="inlineStr">
+      <c r="D44" s="72" t="inlineStr">
         <is>
           <t>Ovo de Páscoa</t>
         </is>
       </c>
-      <c r="E44" s="67" t="inlineStr">
+      <c r="E44" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2307,34 +2330,34 @@
           <t>porque ele tá dando mau exemplo do programa, eu acho que ele tá muito besteirento, ô Babu, você tá muito besteirento, Babu, para de falar, tá falando muita besteira e ainda tá causando esse alvoroço n</t>
         </is>
       </c>
-      <c r="G44" s="67" t="inlineStr">
+      <c r="G44" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show__Ovo_de_Pascoa__09-03-2026_09-14-02.mp3</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="67" t="inlineStr">
+      <c r="A45" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:14:20</t>
         </is>
       </c>
-      <c r="B45" s="67" t="inlineStr">
+      <c r="B45" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C45" s="67" t="inlineStr">
+      <c r="C45" s="72" t="inlineStr">
         <is>
           <t>Jovem Pan</t>
         </is>
       </c>
-      <c r="D45" s="67" t="inlineStr">
+      <c r="D45" s="72" t="inlineStr">
         <is>
           <t>Ovo de Páscoa Cacau Show</t>
         </is>
       </c>
-      <c r="E45" s="67" t="inlineStr">
+      <c r="E45" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2344,34 +2367,34 @@
           <t xml:space="preserve">E nas redes sociais, a hashtag tá lá, Babu Expulso, o que que cê acha? Conta aí que eu quero saber, no finalzinho, da hora do Manhã Pan. Fique ligado porque tem o ovo de páscoa cacau show, tá rolando </t>
         </is>
       </c>
-      <c r="G45" s="67" t="inlineStr">
+      <c r="G45" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__Jovem_Pan__Ovo_de_Pascoa_Cacau_Show__09-03-2026_09-14-20.mp3</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="67" t="inlineStr">
+      <c r="A46" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:14:24</t>
         </is>
       </c>
-      <c r="B46" s="67" t="inlineStr">
+      <c r="B46" s="72" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C46" s="67" t="inlineStr">
+      <c r="C46" s="72" t="inlineStr">
         <is>
           <t>Sotintas</t>
         </is>
       </c>
-      <c r="D46" s="67" t="inlineStr">
+      <c r="D46" s="72" t="inlineStr">
         <is>
           <t>loja de produtos</t>
         </is>
       </c>
-      <c r="E46" s="67" t="inlineStr">
+      <c r="E46" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2381,7 +2404,7 @@
           <t>Música Não saia daí, já já tem muito mais músicas aqui na Band FM Música Conheça a nova loja da Sotintas em Catanduva, na avenida Berendito Zancaner 1481 Um novo, moderno e amplo espaço para você conh</t>
         </is>
       </c>
-      <c r="G46" s="67" t="inlineStr">
+      <c r="G46" s="72" t="inlineStr">
         <is>
           <t>Band_FM__Sotintas__loja_de_produtos__09-03-2026_09-14-24__ad1.mp3</t>
         </is>
@@ -2425,27 +2448,27 @@
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="67" t="inlineStr">
+      <c r="A48" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:15:00</t>
         </is>
       </c>
-      <c r="B48" s="67" t="inlineStr">
+      <c r="B48" s="72" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C48" s="67" t="inlineStr">
+      <c r="C48" s="72" t="inlineStr">
         <is>
           <t>Tatinho Veículos</t>
         </is>
       </c>
-      <c r="D48" s="67" t="inlineStr">
+      <c r="D48" s="72" t="inlineStr">
         <is>
           <t>Veículos</t>
         </is>
       </c>
-      <c r="E48" s="67" t="inlineStr">
+      <c r="E48" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2455,7 +2478,7 @@
           <t>José Nelson Machado, mil trezentos e setenta e nove, e agora também, na Avenida Benedito Zancanet, mil quatrocentos e oitenta e um, ao lado do Proença Supermercados. Só tintas, tudo em tintas, pra com</t>
         </is>
       </c>
-      <c r="G48" s="67" t="inlineStr">
+      <c r="G48" s="72" t="inlineStr">
         <is>
           <t>Band_FM__Tatinho_Veiculos__Veiculos__09-03-2026_09-15-00.mp3</t>
         </is>
@@ -2499,27 +2522,27 @@
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="67" t="inlineStr">
+      <c r="A50" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:17:16</t>
         </is>
       </c>
-      <c r="B50" s="67" t="inlineStr">
+      <c r="B50" s="72" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C50" s="67" t="inlineStr">
+      <c r="C50" s="72" t="inlineStr">
         <is>
           <t>Alto Posto Campeão</t>
         </is>
       </c>
-      <c r="D50" s="67" t="inlineStr">
+      <c r="D50" s="72" t="inlineStr">
         <is>
           <t>Combustível</t>
         </is>
       </c>
-      <c r="E50" s="67" t="inlineStr">
+      <c r="E50" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2529,34 +2552,34 @@
           <t>Filos folha dupla, vinte metros, com doze unidades, doze e noventa e nove. Refrigerante, roler cola pet, dois litros, seis e noventa e nove. Procuro, mora, esquete, supermercados, qualidade, confiança</t>
         </is>
       </c>
-      <c r="G50" s="67" t="inlineStr">
+      <c r="G50" s="72" t="inlineStr">
         <is>
           <t>Band_FM__Alto_Posto_Campeao__Combustivel__09-03-2026_09-17-16__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="67" t="inlineStr">
+      <c r="A51" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:17:33</t>
         </is>
       </c>
-      <c r="B51" s="67" t="inlineStr">
+      <c r="B51" s="72" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C51" s="67" t="inlineStr">
+      <c r="C51" s="72" t="inlineStr">
         <is>
           <t>Bande FM</t>
         </is>
       </c>
-      <c r="D51" s="67" t="inlineStr">
+      <c r="D51" s="72" t="inlineStr">
         <is>
           <t>Rádio</t>
         </is>
       </c>
-      <c r="E51" s="67" t="inlineStr">
+      <c r="E51" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2566,34 +2589,34 @@
           <t>É bem melhor, é Bande FM.</t>
         </is>
       </c>
-      <c r="G51" s="67" t="inlineStr">
+      <c r="G51" s="72" t="inlineStr">
         <is>
           <t>Band_FM__Bande_FM__Radio__09-03-2026_09-17-33.mp3</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="67" t="inlineStr">
+      <c r="A52" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:30:51</t>
         </is>
       </c>
-      <c r="B52" s="67" t="inlineStr">
+      <c r="B52" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C52" s="67" t="inlineStr">
+      <c r="C52" s="72" t="inlineStr">
         <is>
           <t>Traia Veia</t>
         </is>
       </c>
-      <c r="D52" s="67" t="inlineStr">
+      <c r="D52" s="72" t="inlineStr">
         <is>
           <t>Evento (show)</t>
         </is>
       </c>
-      <c r="E52" s="67" t="inlineStr">
+      <c r="E52" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2603,7 +2626,7 @@
           <t>Primeira vez na região, Traia Veia! E em palco, 360! Mesas, open pool de open bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br Seu moço e Traia Veia! Dia 20 de</t>
         </is>
       </c>
-      <c r="G52" s="67" t="inlineStr">
+      <c r="G52" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Traia_Veia__Evento__show__09-03-2026_09-30-51__ad1.mp3</t>
         </is>
@@ -2647,27 +2670,27 @@
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="67" t="inlineStr">
+      <c r="A54" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:30:51</t>
         </is>
       </c>
-      <c r="B54" s="67" t="inlineStr">
+      <c r="B54" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C54" s="67" t="inlineStr">
+      <c r="C54" s="72" t="inlineStr">
         <is>
           <t>Quero Dois Ingressos</t>
         </is>
       </c>
-      <c r="D54" s="67" t="inlineStr">
+      <c r="D54" s="72" t="inlineStr">
         <is>
           <t>Serviço de venda de ingressos</t>
         </is>
       </c>
-      <c r="E54" s="67" t="inlineStr">
+      <c r="E54" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2677,34 +2700,34 @@
           <t>Primeira vez na região, Traia Veia! E em palco, 360! Mesas, open pool de open bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br Seu moço e Traia Veia! Dia 20 de</t>
         </is>
       </c>
-      <c r="G54" s="67" t="inlineStr">
+      <c r="G54" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Quero_Dois_Ingressos__Servico_de_venda_de_ingressos__09-03-2026_09-30-51__ad3.mp3</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="67" t="inlineStr">
+      <c r="A55" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:31:07</t>
         </is>
       </c>
-      <c r="B55" s="67" t="inlineStr">
+      <c r="B55" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C55" s="67" t="inlineStr">
+      <c r="C55" s="72" t="inlineStr">
         <is>
           <t>Clube de Tênis Catanduva</t>
         </is>
       </c>
-      <c r="D55" s="67" t="inlineStr">
+      <c r="D55" s="72" t="inlineStr">
         <is>
           <t>Ingressos</t>
         </is>
       </c>
-      <c r="E55" s="67" t="inlineStr">
+      <c r="E55" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2714,34 +2737,34 @@
           <t>A venda na Secretaria do Clube ou quero dois ingressos ponto com ponto BR. Seu moço e praia velha, dia vinte de março no Clube de Tênis Catanduva. Na vida, os imprevistos são comuns. Aquela viagem ine</t>
         </is>
       </c>
-      <c r="G55" s="67" t="inlineStr">
+      <c r="G55" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Clube_de_Tenis_Catanduva__Ingressos__09-03-2026_09-31-07.mp3</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="67" t="inlineStr">
+      <c r="A56" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:31:56</t>
         </is>
       </c>
-      <c r="B56" s="67" t="inlineStr">
+      <c r="B56" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C56" s="67" t="inlineStr">
+      <c r="C56" s="72" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D56" s="67" t="inlineStr">
+      <c r="D56" s="72" t="inlineStr">
         <is>
           <t>Produtos alimentícios (peixe, camarão, farinha, queijo, papel)</t>
         </is>
       </c>
-      <c r="E56" s="67" t="inlineStr">
+      <c r="E56" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2751,34 +2774,34 @@
           <t>Peixe e muito mais, tudo com preço baixinho pra você aproveitar. Filé de peito laro, 1,1497. Camarão palimara, 180 gramas, 1,1497. Farinha globo, 1,247. Tó de 370 gramas, 7,99. Mussarela a partir de 2</t>
         </is>
       </c>
-      <c r="G56" s="67" t="inlineStr">
+      <c r="G56" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Mar__Produtos_alimenticios__peixe__camarao__farinha__queijo__pape__09-03-2026_09-31-56.mp3</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="67" t="inlineStr">
+      <c r="A57" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:32:13</t>
         </is>
       </c>
-      <c r="B57" s="67" t="inlineStr">
+      <c r="B57" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C57" s="67" t="inlineStr">
+      <c r="C57" s="72" t="inlineStr">
         <is>
           <t>Atacarejo Mar</t>
         </is>
       </c>
-      <c r="D57" s="67" t="inlineStr">
+      <c r="D57" s="72" t="inlineStr">
         <is>
           <t>Páscoa</t>
         </is>
       </c>
-      <c r="E57" s="67" t="inlineStr">
+      <c r="E57" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2788,7 +2811,7 @@
           <t xml:space="preserve">Tocando Papel Supra, vinte e nove e noventa. A maior páscoa do atacarejo é no mar. De voltar aqui na Ondas Verdes, nove e trinta e um agora. Alô, Toninha, bom dia, cê tá boa? Eu sou bem abençoado pra </t>
         </is>
       </c>
-      <c r="G57" s="67" t="inlineStr">
+      <c r="G57" s="72" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Atacarejo_Mar__Pascoa__09-03-2026_09-32-13.mp3</t>
         </is>
@@ -2869,27 +2892,27 @@
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="67" t="inlineStr">
+      <c r="A60" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:35:56</t>
         </is>
       </c>
-      <c r="B60" s="67" t="inlineStr">
+      <c r="B60" s="72" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C60" s="67" t="inlineStr">
+      <c r="C60" s="72" t="inlineStr">
         <is>
           <t>Rede Móveis Casa Vende</t>
         </is>
       </c>
-      <c r="D60" s="67" t="inlineStr">
+      <c r="D60" s="72" t="inlineStr">
         <is>
           <t>Produtos para renovar a casa</t>
         </is>
       </c>
-      <c r="E60" s="67" t="inlineStr">
+      <c r="E60" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2899,34 +2922,34 @@
           <t>Não saia daí, já já tem muito mais músicas aqui na Band FM. Band FM Atenção Catanduva e região, é aniversário da Rede Móveis Casa Vende. Com ofertas especiais para renovar a sua casa. Produtos selecio</t>
         </is>
       </c>
-      <c r="G60" s="67" t="inlineStr">
+      <c r="G60" s="72" t="inlineStr">
         <is>
           <t>Band_FM__Rede_Moveis_Casa_Vende__Produtos_para_renovar_a_casa__09-03-2026_09-35-56.mp3</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="67" t="inlineStr">
+      <c r="A61" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:36:33</t>
         </is>
       </c>
-      <c r="B61" s="67" t="inlineStr">
+      <c r="B61" s="72" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C61" s="67" t="inlineStr">
+      <c r="C61" s="72" t="inlineStr">
         <is>
           <t>Cressol</t>
         </is>
       </c>
-      <c r="D61" s="67" t="inlineStr">
+      <c r="D61" s="72" t="inlineStr">
         <is>
           <t>Promoção Operar é Ganhar</t>
         </is>
       </c>
-      <c r="E61" s="67" t="inlineStr">
+      <c r="E61" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2936,34 +2959,34 @@
           <t xml:space="preserve">Dá pra contar com a sorte, né? Mas se a sorte te ajudar, você ainda pode ganhar 12 milhões em prêmios com a promoção Operar é Ganhar. Invista com a Cressol, gere números da sorte e concorra. Você vai </t>
         </is>
       </c>
-      <c r="G61" s="67" t="inlineStr">
+      <c r="G61" s="72" t="inlineStr">
         <is>
           <t>Band_FM__Cressol__Promocao_Operar_e_Ganhar__09-03-2026_09-36-33__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="67" t="inlineStr">
+      <c r="A62" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:36:33</t>
         </is>
       </c>
-      <c r="B62" s="67" t="inlineStr">
+      <c r="B62" s="72" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C62" s="67" t="inlineStr">
+      <c r="C62" s="72" t="inlineStr">
         <is>
           <t>Alto Posto Campeão</t>
         </is>
       </c>
-      <c r="D62" s="67" t="inlineStr">
+      <c r="D62" s="72" t="inlineStr">
         <is>
           <t>Combustível</t>
         </is>
       </c>
-      <c r="E62" s="67" t="inlineStr">
+      <c r="E62" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2973,34 +2996,34 @@
           <t xml:space="preserve">Dá pra contar com a sorte, né? Mas se a sorte te ajudar, você ainda pode ganhar 12 milhões em prêmios com a promoção Operar é Ganhar. Invista com a Cressol, gere números da sorte e concorra. Você vai </t>
         </is>
       </c>
-      <c r="G62" s="67" t="inlineStr">
+      <c r="G62" s="72" t="inlineStr">
         <is>
           <t>Band_FM__Alto_Posto_Campeao__Combustivel__09-03-2026_09-36-33__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="67" t="inlineStr">
+      <c r="A63" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:36:50</t>
         </is>
       </c>
-      <c r="B63" s="67" t="inlineStr">
+      <c r="B63" s="72" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C63" s="67" t="inlineStr">
+      <c r="C63" s="72" t="inlineStr">
         <is>
           <t>Alto Posto Campeão</t>
         </is>
       </c>
-      <c r="D63" s="67" t="inlineStr">
+      <c r="D63" s="72" t="inlineStr">
         <is>
           <t>Combustível e conveniência</t>
         </is>
       </c>
-      <c r="E63" s="67" t="inlineStr">
+      <c r="E63" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3010,34 +3033,34 @@
           <t>Só poderá é ganhar Certificado de autorização SPAME, número 04047374 Alto Posto Campeão, o seu destino de qualidade em combustível Vá conhecer o Alto Posto Campeão, onde qualidade e preço campeão anda</t>
         </is>
       </c>
-      <c r="G63" s="67" t="inlineStr">
+      <c r="G63" s="72" t="inlineStr">
         <is>
           <t>Band_FM__Alto_Posto_Campeao__Combustivel_e_conveniencia__09-03-2026_09-36-50.mp3</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="67" t="inlineStr">
+      <c r="A64" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:37:08</t>
         </is>
       </c>
-      <c r="B64" s="67" t="inlineStr">
+      <c r="B64" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C64" s="67" t="inlineStr">
+      <c r="C64" s="72" t="inlineStr">
         <is>
           <t>UOL</t>
         </is>
       </c>
-      <c r="D64" s="67" t="inlineStr">
+      <c r="D64" s="72" t="inlineStr">
         <is>
           <t>Enquete do Big Brother 26</t>
         </is>
       </c>
-      <c r="E64" s="67" t="inlineStr">
+      <c r="E64" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3047,34 +3070,34 @@
           <t>Rafa, que negócio do Babu, hein? Babu, eu vou te falar, hein, Babu? O Paulo mandou pra gente aqui, o nosso ouvinte, ele falou assim Ô Rafa, cola no site do UOL Vai lá no UOL que tem a enquete A enquet</t>
         </is>
       </c>
-      <c r="G64" s="67" t="inlineStr">
+      <c r="G64" s="72" t="inlineStr">
         <is>
           <t>Jovem_Pan__UOL__Enquete_do_Big_Brother_26__09-03-2026_09-37-08.mp3</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="68" t="inlineStr">
+      <c r="A65" s="72" t="inlineStr">
         <is>
           <t>09/03/2026 09:39:48</t>
         </is>
       </c>
-      <c r="B65" s="68" t="inlineStr">
+      <c r="B65" s="72" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C65" s="68" t="inlineStr">
+      <c r="C65" s="72" t="inlineStr">
         <is>
           <t>Grupo Moresque</t>
         </is>
       </c>
-      <c r="D65" s="68" t="inlineStr">
+      <c r="D65" s="72" t="inlineStr">
         <is>
           <t>Carnes e arroz</t>
         </is>
       </c>
-      <c r="E65" s="68" t="inlineStr">
+      <c r="E65" s="72" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3084,9 +3107,194 @@
           <t>o mundo. Atenção para algumas das grandes ofertas do Grupo Moresque válidas até dia nove de março. Alcatra com a minha bovina quilo quarenta e três e noventa e nove contra filé bovino quilo quarenta e</t>
         </is>
       </c>
-      <c r="G65" s="68" t="inlineStr">
+      <c r="G65" s="72" t="inlineStr">
         <is>
           <t>Band_FM__Grupo_Moresque__Carnes_e_arroz__09-03-2026_09-39-48.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="73" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:03:52</t>
+        </is>
+      </c>
+      <c r="B66" s="73" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C66" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D66" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="73" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="F66" s="70" t="inlineStr">
+        <is>
+          <t>Primeiro par de lentes multifocais digitais da linha Nobre com antirreflexo, o segundo par é grátis. Consulte condições na loja, tá? E tem muito mais. Lentes de visão simples com antirreflexo e filtro</t>
+        </is>
+      </c>
+      <c r="G66" s="73" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Desconhecido__09-03-2026_10-03-52.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="72" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:05:17</t>
+        </is>
+      </c>
+      <c r="B67" s="72" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C67" s="72" t="inlineStr">
+        <is>
+          <t>Band FM</t>
+        </is>
+      </c>
+      <c r="D67" s="72" t="inlineStr">
+        <is>
+          <t>Rádio/Programa</t>
+        </is>
+      </c>
+      <c r="E67" s="72" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lógico, comentar nas nossas redes sociais. É isso que eu tava pensando. Escolher o nome e ganhar o mascote mais gostosinho do rádio brasileiro. É tudo de bom. É tudo de Band. Band FM. Band FM. Queria </t>
+        </is>
+      </c>
+      <c r="G67" s="72" t="inlineStr">
+        <is>
+          <t>Band_FM__Band_FM__Radio_Programa__09-03-2026_10-05-17.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="72" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28:54</t>
+        </is>
+      </c>
+      <c r="B68" s="72" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C68" s="72" t="inlineStr">
+        <is>
+          <t>Band FM</t>
+        </is>
+      </c>
+      <c r="D68" s="72" t="inlineStr">
+        <is>
+          <t>Smartphone novo</t>
+        </is>
+      </c>
+      <c r="E68" s="72" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Vinte e seis, resolvendo a vida. É, tudo da Band é ótimo, né? Tudo de boa qualidade. Mande um WhatsApp pra Band FM dizendo Smartphone novo, é na Band FM. Pronto, já tá concorrendo. Vende presente toda</t>
+        </is>
+      </c>
+      <c r="G68" s="72" t="inlineStr">
+        <is>
+          <t>Band_FM__Band_FM__Smartphone_novo__09-03-2026_10-28-54.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="73" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:32:17</t>
+        </is>
+      </c>
+      <c r="B69" s="73" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C69" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="73" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="F69" s="70" t="inlineStr">
+        <is>
+          <t>Seu Moço, na abertura! E pela primeira vez na região, Traia Veia! Você só vai achar lembrança boa! E em palco 360! E o sinal abria! Convites para a área VIP por 80 reais, a venda na Secretaria do Club</t>
+        </is>
+      </c>
+      <c r="G69" s="73" t="inlineStr">
+        <is>
+          <t>Band_FM__Desconhecido__09-03-2026_10-32-17.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="74" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:03:50</t>
+        </is>
+      </c>
+      <c r="B70" s="74" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes</t>
+        </is>
+      </c>
+      <c r="C70" s="74" t="inlineStr">
+        <is>
+          <t>Ótica Fabrilein</t>
+        </is>
+      </c>
+      <c r="D70" s="74" t="inlineStr">
+        <is>
+          <t>Lentes e atendimento óptico</t>
+        </is>
+      </c>
+      <c r="E70" s="74" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Ah, ofertas válidas até dia vinte e dois de março ou enquanto durarem os estoques. Vem conferir, um a noventa e nove, quem economiza pode mais. Quando o assunto é visão, a ótica Fabrilein é referência</t>
+        </is>
+      </c>
+      <c r="G70" s="74" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Otica_Fabrilein__Lentes_e_atendimento_optico__09-03-2026_11-03-50.mp3</t>
         </is>
       </c>
     </row>
@@ -3128,11 +3336,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09/03/2026 09:32:13</t>
+          <t>09/03/2026 11:03:50</t>
         </is>
       </c>
     </row>
@@ -3158,11 +3366,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09/03/2026 09:39:48</t>
+          <t>09/03/2026 10:32:17</t>
         </is>
       </c>
     </row>

--- a/radio_capture/relatorio_anuncios.xlsx
+++ b/radio_capture/relatorio_anuncios.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -326,6 +326,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -696,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -746,27 +755,27 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="72" t="inlineStr">
+      <c r="A2" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:14</t>
         </is>
       </c>
-      <c r="B2" s="72" t="inlineStr">
+      <c r="B2" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C2" s="72" t="inlineStr">
+      <c r="C2" s="76" t="inlineStr">
         <is>
           <t>Casa dos Construtores</t>
         </is>
       </c>
-      <c r="D2" s="72" t="inlineStr">
+      <c r="D2" s="76" t="inlineStr">
         <is>
           <t>espaços para casas</t>
         </is>
       </c>
-      <c r="E2" s="72" t="inlineStr">
+      <c r="E2" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -776,34 +785,34 @@
           <t>Mas em como se vive? O tempo bem vivido é feito de escolhas, de detalhes que permanecem, de casas que acolhem, de memórias que resistem. Há 65 anos, criamos espaços para que cada instante não apenas p</t>
         </is>
       </c>
-      <c r="G2" s="72" t="inlineStr">
+      <c r="G2" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Casa_dos_Construtores__espacos_para_casas__09-03-2026_09-00-14__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="72" t="inlineStr">
+      <c r="A3" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:15</t>
         </is>
       </c>
-      <c r="B3" s="72" t="inlineStr">
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C3" s="72" t="inlineStr">
+      <c r="C3" s="76" t="inlineStr">
         <is>
           <t>Ótica Fabriley</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="76" t="inlineStr">
         <is>
           <t>serviços de ótica</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -813,34 +822,34 @@
           <t>Mas em como se vive? O tempo bem vivido é feito de escolhas, de detalhes que permanecem, de casas que acolhem, de memórias que resistem. Há 65 anos, criamos espaços para que cada instante não apenas p</t>
         </is>
       </c>
-      <c r="G3" s="72" t="inlineStr">
+      <c r="G3" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Otica_Fabriley__servicos_de_otica__09-03-2026_09-00-15__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="72" t="inlineStr">
+      <c r="A4" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:31</t>
         </is>
       </c>
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C4" s="72" t="inlineStr">
+      <c r="C4" s="76" t="inlineStr">
         <is>
           <t>ótica FabriLen</t>
         </is>
       </c>
-      <c r="D4" s="72" t="inlineStr">
+      <c r="D4" s="76" t="inlineStr">
         <is>
           <t>lentes</t>
         </is>
       </c>
-      <c r="E4" s="72" t="inlineStr">
+      <c r="E4" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -850,34 +859,34 @@
           <t>Cada instante, não apenas passe, mas fique. Casa dos Construtores, o melhor tempo na sua casa. Quando o assunto é visão, a ótica FabriLen é referência. Atendimento diferenciado com profissionais prepa</t>
         </is>
       </c>
-      <c r="G4" s="72" t="inlineStr">
+      <c r="G4" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__otica_FabriLen__lentes__09-03-2026_09-00-30.mp3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="72" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:33</t>
         </is>
       </c>
-      <c r="B5" s="72" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C5" s="72" t="inlineStr">
+      <c r="C5" s="76" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D5" s="72" t="inlineStr">
+      <c r="D5" s="76" t="inlineStr">
         <is>
           <t>Chocolate</t>
         </is>
       </c>
-      <c r="E5" s="72" t="inlineStr">
+      <c r="E5" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -887,34 +896,34 @@
           <t>Viu? Bob Sinclair na programação número 1 do seu rádio, vocês viram aí, aliás, ouviram, né? Vai, Tassonzão! Tonsera, né, pra gente curtir aqui na programação. Jovem Pan, daqui a pouquinho, depois de i</t>
         </is>
       </c>
-      <c r="G5" s="72" t="inlineStr">
+      <c r="G5" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show__Chocolate__09-03-2026_09-00-33.mp3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="72" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:48</t>
         </is>
       </c>
-      <c r="B6" s="72" t="inlineStr">
+      <c r="B6" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C6" s="72" t="inlineStr">
+      <c r="C6" s="76" t="inlineStr">
         <is>
           <t>Noblen</t>
         </is>
       </c>
-      <c r="D6" s="72" t="inlineStr">
+      <c r="D6" s="76" t="inlineStr">
         <is>
           <t>lentes multifocais digitais e lentes de visão simples</t>
         </is>
       </c>
-      <c r="E6" s="72" t="inlineStr">
+      <c r="E6" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -924,34 +933,34 @@
           <t>Preparados para orientar você com atenção e confiança. As lentes são produzidas com alta tecnologia, garantindo precisão e conforto para o dia a dia. E tem promoção especial. Na compra do primeiro par</t>
         </is>
       </c>
-      <c r="G6" s="72" t="inlineStr">
+      <c r="G6" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Noblen__lentes_multifocais_digitais_e_lentes_de_visao_simples__09-03-2026_09-00-48.mp3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="72" t="inlineStr">
+      <c r="A7" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:00:50</t>
         </is>
       </c>
-      <c r="B7" s="72" t="inlineStr">
+      <c r="B7" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C7" s="72" t="inlineStr">
+      <c r="C7" s="76" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D7" s="72" t="inlineStr">
+      <c r="D7" s="76" t="inlineStr">
         <is>
           <t>chocolate</t>
         </is>
       </c>
-      <c r="E7" s="72" t="inlineStr">
+      <c r="E7" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -961,34 +970,34 @@
           <t>Número 1 do Brasil e... e... e... Cacau Show! Aquele chocolate maravilhoso, aquele chocolate refinado, aquele sabor... Hummm... já vai dando assim o negócio, é de louco, né? Quer levar pra casa? Então</t>
         </is>
       </c>
-      <c r="G7" s="72" t="inlineStr">
+      <c r="G7" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show__chocolate__09-03-2026_09-00-50.mp3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="72" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:01:04</t>
         </is>
       </c>
-      <c r="B8" s="72" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C8" s="72" t="inlineStr">
+      <c r="C8" s="76" t="inlineStr">
         <is>
           <t>Óticas FabriLem</t>
         </is>
       </c>
-      <c r="D8" s="72" t="inlineStr">
+      <c r="D8" s="76" t="inlineStr">
         <is>
           <t>lentes de visão simples com antirreflexo e filtro de luz azul</t>
         </is>
       </c>
-      <c r="E8" s="72" t="inlineStr">
+      <c r="E8" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -998,34 +1007,34 @@
           <t>digitais noblem com antirreflexo, o segundo par é grátis. E mais, lentes de visão simples com antirreflexo e filtro de luz azul em até dez vezes de dezoito e noventa. Visite a loja na Rua Brasil Esqui</t>
         </is>
       </c>
-      <c r="G8" s="72" t="inlineStr">
+      <c r="G8" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Oticas_FabriLem__lentes_de_visao_simples_com_antirreflexo_e_filtro_de_luz_azu__09-03-2026_09-01-04__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="62" t="inlineStr">
+      <c r="A9" s="75" t="inlineStr">
         <is>
           <t>09/03/2026 09:01:04</t>
         </is>
       </c>
-      <c r="B9" s="62" t="inlineStr">
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C9" s="62" t="inlineStr">
+      <c r="C9" s="75" t="inlineStr">
         <is>
           <t>Amaral Centro Automotivo Multimarcas</t>
         </is>
       </c>
-      <c r="D9" s="62" t="inlineStr">
+      <c r="D9" s="75" t="inlineStr">
         <is>
           <t>serviços automotivos</t>
         </is>
       </c>
-      <c r="E9" s="62" t="inlineStr">
+      <c r="E9" s="75" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -1035,34 +1044,34 @@
           <t>digitais noblem com antirreflexo, o segundo par é grátis. E mais, lentes de visão simples com antirreflexo e filtro de luz azul em até dez vezes de dezoito e noventa. Visite a loja na Rua Brasil Esqui</t>
         </is>
       </c>
-      <c r="G9" s="62" t="inlineStr">
+      <c r="G9" s="75" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Amaral_Centro_Automotivo_Multimarcas__servicos_automotivos__09-03-2026_09-01-04__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="72" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:01:21</t>
         </is>
       </c>
-      <c r="B10" s="72" t="inlineStr">
+      <c r="B10" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C10" s="72" t="inlineStr">
+      <c r="C10" s="76" t="inlineStr">
         <is>
           <t>Amaral Centro Automotivo Multimarcas</t>
         </is>
       </c>
-      <c r="D10" s="72" t="inlineStr">
+      <c r="D10" s="76" t="inlineStr">
         <is>
           <t>serviços automotivos</t>
         </is>
       </c>
-      <c r="E10" s="72" t="inlineStr">
+      <c r="E10" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1072,34 +1081,34 @@
           <t>FabriLem, a fábrica da sua lente. Amaral Centro Automotivo Multimarcas agradece a todos o carinho e a confiança no trabalho realizado com sua equipe de profissionais. Hoje estamos em novo endereço par</t>
         </is>
       </c>
-      <c r="G10" s="72" t="inlineStr">
+      <c r="G10" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Amaral_Centro_Automotivo_Multimarcas__servicos_automotivos__09-03-2026_09-01-21.mp3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:02:10</t>
         </is>
       </c>
-      <c r="B11" s="72" t="inlineStr">
+      <c r="B11" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C11" s="72" t="inlineStr">
+      <c r="C11" s="76" t="inlineStr">
         <is>
           <t>Unifipa</t>
         </is>
       </c>
-      <c r="D11" s="72" t="inlineStr">
+      <c r="D11" s="76" t="inlineStr">
         <is>
           <t>Cursos de graduação</t>
         </is>
       </c>
-      <c r="E11" s="72" t="inlineStr">
+      <c r="E11" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1109,34 +1118,34 @@
           <t>São onze opções de cursos de graduação na instituição que tem mais de cinquenta e cinco anos de tradição e é sinônimo de excelência em ensino com nota máxima na avaliação do MEC. Venha ser Unifipa. In</t>
         </is>
       </c>
-      <c r="G11" s="72" t="inlineStr">
+      <c r="G11" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Unifipa__Cursos_de_graduacao__09-03-2026_09-02-10__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="62" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t>09/03/2026 09:02:10</t>
         </is>
       </c>
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="75" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C12" s="62" t="inlineStr">
+      <c r="C12" s="75" t="inlineStr">
         <is>
           <t>Nagatela</t>
         </is>
       </c>
-      <c r="D12" s="62" t="inlineStr">
+      <c r="D12" s="75" t="inlineStr">
         <is>
           <t>Poupança premiada</t>
         </is>
       </c>
-      <c r="E12" s="62" t="inlineStr">
+      <c r="E12" s="75" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -1146,34 +1155,34 @@
           <t>São onze opções de cursos de graduação na instituição que tem mais de cinquenta e cinco anos de tradição e é sinônimo de excelência em ensino com nota máxima na avaliação do MEC. Venha ser Unifipa. In</t>
         </is>
       </c>
-      <c r="G12" s="62" t="inlineStr">
+      <c r="G12" s="75" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Nagatela__Poupanca_premiada__09-03-2026_09-02-10__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="72" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:02:27</t>
         </is>
       </c>
-      <c r="B13" s="72" t="inlineStr">
+      <c r="B13" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C13" s="72" t="inlineStr">
+      <c r="C13" s="76" t="inlineStr">
         <is>
           <t>Cicred</t>
         </is>
       </c>
-      <c r="D13" s="72" t="inlineStr">
+      <c r="D13" s="76" t="inlineStr">
         <is>
           <t>Poupança premiada</t>
         </is>
       </c>
-      <c r="E13" s="72" t="inlineStr">
+      <c r="E13" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1183,34 +1192,34 @@
           <t>A Unipipa, referência que transforma vidas. Aqui é a Nagacela, é hora de sonhar alto. A poupança premiada Cicred tá aí. Cicred, poupança é premiada Pra fazer tudo o que você sonhava Tem milhões em ben</t>
         </is>
       </c>
-      <c r="G13" s="72" t="inlineStr">
+      <c r="G13" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Cicred__Poupanca_premiada__09-03-2026_09-02-27.mp3</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="72" t="inlineStr">
+      <c r="A14" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:02:43</t>
         </is>
       </c>
-      <c r="B14" s="72" t="inlineStr">
+      <c r="B14" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C14" s="72" t="inlineStr">
+      <c r="C14" s="76" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D14" s="72" t="inlineStr">
+      <c r="D14" s="76" t="inlineStr">
         <is>
           <t>Produtos para Páscoa (chocolate, ovo de Páscoa, peixe, etc.)</t>
         </is>
       </c>
-      <c r="E14" s="72" t="inlineStr">
+      <c r="E14" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1220,34 +1229,34 @@
           <t>São mais de 600 ganhadores, 5 milhões em prêmios em dinheiro. Volte no Cicred e concorra! O Baré Show, olha onde eu tô! Corre para conferir os preços imperdíveis do Max e garanta sua Páscoa! Olha, tem</t>
         </is>
       </c>
-      <c r="G14" s="72" t="inlineStr">
+      <c r="G14" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Max__Produtos_para_Pascoa__chocolate__ovo_de_Pascoa__peixe__etc__09-03-2026_09-02-43__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:02:43</t>
         </is>
       </c>
-      <c r="B15" s="72" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C15" s="72" t="inlineStr">
+      <c r="C15" s="76" t="inlineStr">
         <is>
           <t>Cicred</t>
         </is>
       </c>
-      <c r="D15" s="72" t="inlineStr">
+      <c r="D15" s="76" t="inlineStr">
         <is>
           <t>Concurso com prêmios em dinheiro</t>
         </is>
       </c>
-      <c r="E15" s="72" t="inlineStr">
+      <c r="E15" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1257,34 +1266,34 @@
           <t>São mais de 600 ganhadores, 5 milhões em prêmios em dinheiro. Volte no Cicred e concorra! O Baré Show, olha onde eu tô! Corre para conferir os preços imperdíveis do Max e garanta sua Páscoa! Olha, tem</t>
         </is>
       </c>
-      <c r="G15" s="72" t="inlineStr">
+      <c r="G15" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Cicred__Concurso_com_premios_em_dinheiro__09-03-2026_09-02-43__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="72" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:00</t>
         </is>
       </c>
-      <c r="B16" s="72" t="inlineStr">
+      <c r="B16" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C16" s="72" t="inlineStr">
+      <c r="C16" s="76" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D16" s="72" t="inlineStr">
+      <c r="D16" s="76" t="inlineStr">
         <is>
           <t>Produtos para Páscoa (chocolate, ovo de Páscoa, peixe, etc.)</t>
         </is>
       </c>
-      <c r="E16" s="72" t="inlineStr">
+      <c r="E16" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1294,34 +1303,34 @@
           <t>Corre para conferir os preços imperdíveis do Max e garanta sua Páscoa. Olha, tem chocolate, ovo de Páscoa, peixe e muito mais. Tudo com preço baixinho pra você aproveitar. Filé de peito lá no quilo 14</t>
         </is>
       </c>
-      <c r="G16" s="72" t="inlineStr">
+      <c r="G16" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Max__Produtos_para_Pascoa__chocolate__ovo_de_Pascoa__peixe__etc__09-03-2026_09-03-00.mp3</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="72" t="inlineStr">
+      <c r="A17" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:14</t>
         </is>
       </c>
-      <c r="B17" s="72" t="inlineStr">
+      <c r="B17" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C17" s="72" t="inlineStr">
+      <c r="C17" s="76" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="D17" s="72" t="inlineStr">
+      <c r="D17" s="76" t="inlineStr">
         <is>
           <t>BTS The Comeback Live</t>
         </is>
       </c>
-      <c r="E17" s="72" t="inlineStr">
+      <c r="E17" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1331,34 +1340,34 @@
           <t xml:space="preserve">Uma delas é o trailer do especial da Netflix, BTS The Comeback Live, que chega à plataforma no próximo dia 20. O filme faz parte da poderosa campanha promocional do álbum I Run dos reis do K-Pop. Pra </t>
         </is>
       </c>
-      <c r="G17" s="72" t="inlineStr">
+      <c r="G17" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Netflix__BTS_The_Comeback_Live__09-03-2026_09-03-14.mp3</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="72" t="inlineStr">
+      <c r="A18" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:16</t>
         </is>
       </c>
-      <c r="B18" s="72" t="inlineStr">
+      <c r="B18" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C18" s="72" t="inlineStr">
+      <c r="C18" s="76" t="inlineStr">
         <is>
           <t>Sete Farinha Globo</t>
         </is>
       </c>
-      <c r="D18" s="72" t="inlineStr">
+      <c r="D18" s="76" t="inlineStr">
         <is>
           <t>Farinha</t>
         </is>
       </c>
-      <c r="E18" s="72" t="inlineStr">
+      <c r="E18" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1368,34 +1377,34 @@
           <t>sete farinha globo, um quilo, dois e quarenta e sete. Tó de trezentos e setenta gramas, sete e noventa e nove. Mussarela a partir de vinte e seis e noventa um quilo. Papel Supra, vinte e nove e novent</t>
         </is>
       </c>
-      <c r="G18" s="72" t="inlineStr">
+      <c r="G18" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Sete_Farinha_Globo__Farinha__09-03-2026_09-03-16__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:16</t>
         </is>
       </c>
-      <c r="B19" s="72" t="inlineStr">
+      <c r="B19" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C19" s="72" t="inlineStr">
+      <c r="C19" s="76" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D19" s="72" t="inlineStr">
+      <c r="D19" s="76" t="inlineStr">
         <is>
           <t>Pasta</t>
         </is>
       </c>
-      <c r="E19" s="72" t="inlineStr">
+      <c r="E19" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1405,34 +1414,34 @@
           <t>sete farinha globo, um quilo, dois e quarenta e sete. Tó de trezentos e setenta gramas, sete e noventa e nove. Mussarela a partir de vinte e seis e noventa um quilo. Papel Supra, vinte e nove e novent</t>
         </is>
       </c>
-      <c r="G19" s="72" t="inlineStr">
+      <c r="G19" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Max__Pasta__09-03-2026_09-03-16__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="72" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:16</t>
         </is>
       </c>
-      <c r="B20" s="72" t="inlineStr">
+      <c r="B20" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C20" s="72" t="inlineStr">
+      <c r="C20" s="76" t="inlineStr">
         <is>
           <t>Drogaria Total Popular</t>
         </is>
       </c>
-      <c r="D20" s="72" t="inlineStr">
+      <c r="D20" s="76" t="inlineStr">
         <is>
           <t>Remédios</t>
         </is>
       </c>
-      <c r="E20" s="72" t="inlineStr">
+      <c r="E20" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1442,34 +1451,34 @@
           <t>sete farinha globo, um quilo, dois e quarenta e sete. Tó de trezentos e setenta gramas, sete e noventa e nove. Mussarela a partir de vinte e seis e noventa um quilo. Papel Supra, vinte e nove e novent</t>
         </is>
       </c>
-      <c r="G20" s="72" t="inlineStr">
+      <c r="G20" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Drogaria_Total_Popular__Remedios__09-03-2026_09-03-16__ad3.mp3</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="72" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:32</t>
         </is>
       </c>
-      <c r="B21" s="72" t="inlineStr">
+      <c r="B21" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C21" s="72" t="inlineStr">
+      <c r="C21" s="76" t="inlineStr">
         <is>
           <t>Doutor Alex Baraldo Portes</t>
         </is>
       </c>
-      <c r="D21" s="72" t="inlineStr">
+      <c r="D21" s="76" t="inlineStr">
         <is>
           <t>Serviços de Otorrino Laringologista</t>
         </is>
       </c>
-      <c r="E21" s="72" t="inlineStr">
+      <c r="E21" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1479,34 +1488,34 @@
           <t xml:space="preserve">Jovem Pan. Jovem Pan Brasil. Você está ouvindo. Manhã Pan. Catanduva. Oferecimento. Doutor Alex Baraldo Portes. Otorrino Laringologista. RQE 64202. Vive em empreendimentos. Municipa Catanduva. Doutor </t>
         </is>
       </c>
-      <c r="G21" s="72" t="inlineStr">
+      <c r="G21" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_Otorrino_Laringologista__09-03-2026_09-03-32__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="72" t="inlineStr">
+      <c r="A22" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:32</t>
         </is>
       </c>
-      <c r="B22" s="72" t="inlineStr">
+      <c r="B22" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C22" s="72" t="inlineStr">
+      <c r="C22" s="76" t="inlineStr">
         <is>
           <t>IGA Proteção Veicular</t>
         </is>
       </c>
-      <c r="D22" s="72" t="inlineStr">
+      <c r="D22" s="76" t="inlineStr">
         <is>
           <t>Proteção Veicular</t>
         </is>
       </c>
-      <c r="E22" s="72" t="inlineStr">
+      <c r="E22" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1516,34 +1525,34 @@
           <t xml:space="preserve">Jovem Pan. Jovem Pan Brasil. Você está ouvindo. Manhã Pan. Catanduva. Oferecimento. Doutor Alex Baraldo Portes. Otorrino Laringologista. RQE 64202. Vive em empreendimentos. Municipa Catanduva. Doutor </t>
         </is>
       </c>
-      <c r="G22" s="72" t="inlineStr">
+      <c r="G22" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__IGA_Protecao_Veicular__Protecao_Veicular__09-03-2026_09-03-32__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="72" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:03:50</t>
         </is>
       </c>
-      <c r="B23" s="72" t="inlineStr">
+      <c r="B23" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C23" s="72" t="inlineStr">
+      <c r="C23" s="76" t="inlineStr">
         <is>
           <t>Doutor Alex Baraldo Portes</t>
         </is>
       </c>
-      <c r="D23" s="72" t="inlineStr">
+      <c r="D23" s="76" t="inlineStr">
         <is>
           <t>Serviços de otorrino laringologista</t>
         </is>
       </c>
-      <c r="E23" s="72" t="inlineStr">
+      <c r="E23" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1553,34 +1562,34 @@
           <t>Municipal, município de Catanduva, doutor Cristiano Herrera e GA Proteção Veicular. Nariz entupido, incômodos no ouvido, nariz ou garganta? Sua saúde pode estar precisando de atenção. Quando você sent</t>
         </is>
       </c>
-      <c r="G23" s="72" t="inlineStr">
+      <c r="G23" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_otorrino_laringologista__09-03-2026_09-03-50.mp3</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="72" t="inlineStr">
+      <c r="A24" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:08</t>
         </is>
       </c>
-      <c r="B24" s="72" t="inlineStr">
+      <c r="B24" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C24" s="72" t="inlineStr">
+      <c r="C24" s="76" t="inlineStr">
         <is>
           <t>Doutor Alex Baraldo Portes</t>
         </is>
       </c>
-      <c r="D24" s="72" t="inlineStr">
+      <c r="D24" s="76" t="inlineStr">
         <is>
           <t>Serviços de otorrino-laringologia</t>
         </is>
       </c>
-      <c r="E24" s="72" t="inlineStr">
+      <c r="E24" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1590,34 +1599,34 @@
           <t>Cuida do nariz, ouvido e garganta. Não perca o foco da sua saúde. Essa é uma mensagem do doutor Alex Baraldo Portes, que é otorrino-laringologista. CRM 137582, RQE 64202. Lá no Instagram do doutor Ale</t>
         </is>
       </c>
-      <c r="G24" s="72" t="inlineStr">
+      <c r="G24" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_otorrino-laringologia__09-03-2026_09-04-08__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="72" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:08</t>
         </is>
       </c>
-      <c r="B25" s="72" t="inlineStr">
+      <c r="B25" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C25" s="72" t="inlineStr">
+      <c r="C25" s="76" t="inlineStr">
         <is>
           <t>Unifipa Catanduva</t>
         </is>
       </c>
-      <c r="D25" s="72" t="inlineStr">
+      <c r="D25" s="76" t="inlineStr">
         <is>
           <t>Vestibular continuado 2026</t>
         </is>
       </c>
-      <c r="E25" s="72" t="inlineStr">
+      <c r="E25" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1627,34 +1636,34 @@
           <t>Cuida do nariz, ouvido e garganta. Não perca o foco da sua saúde. Essa é uma mensagem do doutor Alex Baraldo Portes, que é otorrino-laringologista. CRM 137582, RQE 64202. Lá no Instagram do doutor Ale</t>
         </is>
       </c>
-      <c r="G25" s="72" t="inlineStr">
+      <c r="G25" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Unifipa_Catanduva__Vestibular_continuado_2026__09-03-2026_09-04-08__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="72" t="inlineStr">
+      <c r="A26" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:22</t>
         </is>
       </c>
-      <c r="B26" s="72" t="inlineStr">
+      <c r="B26" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C26" s="72" t="inlineStr">
+      <c r="C26" s="76" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="D26" s="72" t="inlineStr">
+      <c r="D26" s="76" t="inlineStr">
         <is>
           <t>Serviço de streaming</t>
         </is>
       </c>
-      <c r="E26" s="72" t="inlineStr">
+      <c r="E26" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1664,34 +1673,34 @@
           <t>Ligue agora ou mande um zap, dezessete três um cinco um mil, ou acesse NetflixBR.com. É Netflix! A FM da gente, Ondas Verde! A sua manhã fica completa na Ondas Verdes.</t>
         </is>
       </c>
-      <c r="G26" s="72" t="inlineStr">
+      <c r="G26" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Netflix__Servico_de_streaming__09-03-2026_09-04-22.mp3</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="72" t="inlineStr">
+      <c r="A27" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:44</t>
         </is>
       </c>
-      <c r="B27" s="72" t="inlineStr">
+      <c r="B27" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C27" s="72" t="inlineStr">
+      <c r="C27" s="76" t="inlineStr">
         <is>
           <t>Unifipa</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="76" t="inlineStr">
         <is>
           <t>Inscrições e provas online</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1701,34 +1710,34 @@
           <t>é que venha ser Unifipa, inscrições e provas online em unifipa.com.br barra vestibular. Unifipa, referência que transforma vidas. A clínica do doutor Cristiano Herrera, gente, atenção, é referência na</t>
         </is>
       </c>
-      <c r="G27" s="72" t="inlineStr">
+      <c r="G27" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Unifipa__Inscricoes_e_provas_online__09-03-2026_09-04-44__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="72" t="inlineStr">
+      <c r="A28" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:04:45</t>
         </is>
       </c>
-      <c r="B28" s="72" t="inlineStr">
+      <c r="B28" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C28" s="72" t="inlineStr">
+      <c r="C28" s="76" t="inlineStr">
         <is>
           <t>Clínica do Doutor Cristiano Herrera</t>
         </is>
       </c>
-      <c r="D28" s="72" t="inlineStr">
+      <c r="D28" s="76" t="inlineStr">
         <is>
           <t>Serviços de psicologia, neuropsicologia e psicopedagogia</t>
         </is>
       </c>
-      <c r="E28" s="72" t="inlineStr">
+      <c r="E28" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1738,34 +1747,34 @@
           <t>é que venha ser Unifipa, inscrições e provas online em unifipa.com.br barra vestibular. Unifipa, referência que transforma vidas. A clínica do doutor Cristiano Herrera, gente, atenção, é referência na</t>
         </is>
       </c>
-      <c r="G28" s="72" t="inlineStr">
+      <c r="G28" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Clinica_do_Doutor_Cristiano_Herrera__Servicos_de_psicologia__neuropsicologia_e_psicopedagogia__09-03-2026_09-04-45__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="72" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:02</t>
         </is>
       </c>
-      <c r="B29" s="72" t="inlineStr">
+      <c r="B29" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C29" s="72" t="inlineStr">
+      <c r="C29" s="76" t="inlineStr">
         <is>
           <t>Doutor Cristiano Herrera</t>
         </is>
       </c>
-      <c r="D29" s="72" t="inlineStr">
+      <c r="D29" s="76" t="inlineStr">
         <is>
           <t>Serviços de psicopedagogia e neuropsicologia</t>
         </is>
       </c>
-      <c r="E29" s="72" t="inlineStr">
+      <c r="E29" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1775,34 +1784,34 @@
           <t>Psicopedagogia, através da avaliação neuropsicológica com a equipe multidisciplinar, que você vai encontrar lá, pessoal maravilhoso, o doutor Cristiano Herrera, ele utiliza testes em escalas mais efet</t>
         </is>
       </c>
-      <c r="G29" s="72" t="inlineStr">
+      <c r="G29" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Cristiano_Herrera__Servicos_de_psicopedagogia_e_neuropsicologia__09-03-2026_09-05-02__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="72" t="inlineStr">
+      <c r="A30" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:03</t>
         </is>
       </c>
-      <c r="B30" s="72" t="inlineStr">
+      <c r="B30" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C30" s="72" t="inlineStr">
+      <c r="C30" s="76" t="inlineStr">
         <is>
           <t>Doutor Cristian Aranjeira</t>
         </is>
       </c>
-      <c r="D30" s="72" t="inlineStr">
+      <c r="D30" s="76" t="inlineStr">
         <is>
           <t>Serviços de psicologia e neuropsicologia</t>
         </is>
       </c>
-      <c r="E30" s="72" t="inlineStr">
+      <c r="E30" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1812,34 +1821,34 @@
           <t>Psicopedagogia, através da avaliação neuropsicológica com a equipe multidisciplinar, que você vai encontrar lá, pessoal maravilhoso, o doutor Cristiano Herrera, ele utiliza testes em escalas mais efet</t>
         </is>
       </c>
-      <c r="G30" s="72" t="inlineStr">
+      <c r="G30" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Cristian_Aranjeira__Servicos_de_psicologia_e_neuropsicologia__09-03-2026_09-05-03__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="72" t="inlineStr">
+      <c r="A31" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:21</t>
         </is>
       </c>
-      <c r="B31" s="72" t="inlineStr">
+      <c r="B31" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C31" s="72" t="inlineStr">
+      <c r="C31" s="76" t="inlineStr">
         <is>
           <t>Clínica do Dr. Cristiano Herrera</t>
         </is>
       </c>
-      <c r="D31" s="72" t="inlineStr">
+      <c r="D31" s="76" t="inlineStr">
         <is>
           <t>Serviços de psicologia e neuroreabilitação</t>
         </is>
       </c>
-      <c r="E31" s="72" t="inlineStr">
+      <c r="E31" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1849,34 +1858,34 @@
           <t>inclusive os tratamentos não medicamentosos, por exemplo, como neuromodulação e biofeedback. O doutor Cristiano Herrera, ele é psicólogo, neuropsicólogo formado pela USP, especialista em neuroreabilit</t>
         </is>
       </c>
-      <c r="G31" s="72" t="inlineStr">
+      <c r="G31" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Clinica_do_Dr__Cristiano_Herrera__Servicos_de_psicologia_e_neuroreabilitacao__09-03-2026_09-05-21.mp3</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="72" t="inlineStr">
+      <c r="A32" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:39</t>
         </is>
       </c>
-      <c r="B32" s="72" t="inlineStr">
+      <c r="B32" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C32" s="72" t="inlineStr">
+      <c r="C32" s="76" t="inlineStr">
         <is>
           <t>Antunes Mais</t>
         </is>
       </c>
-      <c r="D32" s="72" t="inlineStr">
+      <c r="D32" s="76" t="inlineStr">
         <is>
           <t>Arroz seleto e feijão carioca</t>
         </is>
       </c>
-      <c r="E32" s="72" t="inlineStr">
+      <c r="E32" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1886,34 +1895,34 @@
           <t xml:space="preserve">O segundo andar, então acesse arroba DR Cristiano Herrera no Instagram. Liga a fã no Instagram, arroba jovem fã Catanduba. Comece a semana com mais economia no Antunes Mais. Confira arroz seleto tipo </t>
         </is>
       </c>
-      <c r="G32" s="72" t="inlineStr">
+      <c r="G32" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Antunes_Mais__Arroz_seleto_e_feijao_carioca__09-03-2026_09-05-39__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="72" t="inlineStr">
+      <c r="A33" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:39</t>
         </is>
       </c>
-      <c r="B33" s="72" t="inlineStr">
+      <c r="B33" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C33" s="72" t="inlineStr">
+      <c r="C33" s="76" t="inlineStr">
         <is>
           <t>Clube do Precinho</t>
         </is>
       </c>
-      <c r="D33" s="72" t="inlineStr">
+      <c r="D33" s="76" t="inlineStr">
         <is>
           <t>Músculo bovino e cortes de carne</t>
         </is>
       </c>
-      <c r="E33" s="72" t="inlineStr">
+      <c r="E33" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1923,34 +1932,34 @@
           <t xml:space="preserve">O segundo andar, então acesse arroba DR Cristiano Herrera no Instagram. Liga a fã no Instagram, arroba jovem fã Catanduba. Comece a semana com mais economia no Antunes Mais. Confira arroz seleto tipo </t>
         </is>
       </c>
-      <c r="G33" s="72" t="inlineStr">
+      <c r="G33" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Clube_do_Precinho__Musculo_bovino_e_cortes_de_carne__09-03-2026_09-05-39__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="72" t="inlineStr">
+      <c r="A34" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:05:57</t>
         </is>
       </c>
-      <c r="B34" s="72" t="inlineStr">
+      <c r="B34" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C34" s="72" t="inlineStr">
+      <c r="C34" s="76" t="inlineStr">
         <is>
           <t>Antunes Mais</t>
         </is>
       </c>
-      <c r="D34" s="72" t="inlineStr">
+      <c r="D34" s="76" t="inlineStr">
         <is>
           <t>Produtos variados (feijão, carne, detergente, etc.)</t>
         </is>
       </c>
-      <c r="E34" s="72" t="inlineStr">
+      <c r="E34" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1960,34 +1969,34 @@
           <t>onze e noventa e nove, feijão carioca seleto, pacote um quilo, seis e noventa e nove, tem também as ofertas do Clube do Precinho, acenho, músculo bovino, trinta e quatro e noventa e cinco quilo, colch</t>
         </is>
       </c>
-      <c r="G34" s="72" t="inlineStr">
+      <c r="G34" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Antunes_Mais__Produtos_variados__feijao__carne__detergente__etc__09-03-2026_09-05-57.mp3</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="72" t="inlineStr">
+      <c r="A35" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:06:15</t>
         </is>
       </c>
-      <c r="B35" s="72" t="inlineStr">
+      <c r="B35" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C35" s="72" t="inlineStr">
+      <c r="C35" s="76" t="inlineStr">
         <is>
           <t>Antunes Mais</t>
         </is>
       </c>
-      <c r="D35" s="72" t="inlineStr">
+      <c r="D35" s="76" t="inlineStr">
         <is>
           <t>Produtos com descontos</t>
         </is>
       </c>
-      <c r="E35" s="72" t="inlineStr">
+      <c r="E35" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1997,34 +2006,34 @@
           <t>O Festas Válidas, até dia onze, no Antunes Mais. As melhores lojas de Catanduva, reunidas em um único lugar, com até setenta por cento off. Você já sabe de qual evento estamos falando? Bazar chique, é</t>
         </is>
       </c>
-      <c r="G35" s="72" t="inlineStr">
+      <c r="G35" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Antunes_Mais__Produtos_com_descontos__09-03-2026_09-06-15__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="72" t="inlineStr">
+      <c r="A36" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:06:15</t>
         </is>
       </c>
-      <c r="B36" s="72" t="inlineStr">
+      <c r="B36" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C36" s="72" t="inlineStr">
+      <c r="C36" s="76" t="inlineStr">
         <is>
           <t>Bazar Chique</t>
         </is>
       </c>
-      <c r="D36" s="72" t="inlineStr">
+      <c r="D36" s="76" t="inlineStr">
         <is>
           <t>Roupas, acessórios, calçados, óticas</t>
         </is>
       </c>
-      <c r="E36" s="72" t="inlineStr">
+      <c r="E36" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2034,34 +2043,34 @@
           <t>O Festas Válidas, até dia onze, no Antunes Mais. As melhores lojas de Catanduva, reunidas em um único lugar, com até setenta por cento off. Você já sabe de qual evento estamos falando? Bazar chique, é</t>
         </is>
       </c>
-      <c r="G36" s="72" t="inlineStr">
+      <c r="G36" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Bazar_Chique__Roupas__acessorios__calcados__oticas__09-03-2026_09-06-15__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="72" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:06:33</t>
         </is>
       </c>
-      <c r="B37" s="72" t="inlineStr">
+      <c r="B37" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C37" s="72" t="inlineStr">
+      <c r="C37" s="76" t="inlineStr">
         <is>
           <t>SimComércio e Vive Empre</t>
         </is>
       </c>
-      <c r="D37" s="72" t="inlineStr">
+      <c r="D37" s="76" t="inlineStr">
         <is>
           <t>Feira ou evento de vendas</t>
         </is>
       </c>
-      <c r="E37" s="72" t="inlineStr">
+      <c r="E37" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2071,34 +2080,34 @@
           <t>e muito mais com preços imperdíveis. Dias 19, 20 e 21 de março, na sede do SimComércio, Avenida Benedito Zancaner, 720, quinta e sexta, das nove às vinte e duas horas. Sábado, das nove às dezessete ho</t>
         </is>
       </c>
-      <c r="G37" s="72" t="inlineStr">
+      <c r="G37" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__SimComercio_e_Vive_Empre__Feira_ou_evento_de_vendas__09-03-2026_09-06-33.mp3</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="72" t="inlineStr">
+      <c r="A38" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:06:52</t>
         </is>
       </c>
-      <c r="B38" s="72" t="inlineStr">
+      <c r="B38" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C38" s="72" t="inlineStr">
+      <c r="C38" s="76" t="inlineStr">
         <is>
           <t>Vive Empreendimentos</t>
         </is>
       </c>
-      <c r="D38" s="72" t="inlineStr">
+      <c r="D38" s="76" t="inlineStr">
         <is>
           <t>empreendimentos imobiliários</t>
         </is>
       </c>
-      <c r="E38" s="72" t="inlineStr">
+      <c r="E38" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2108,34 +2117,34 @@
           <t>Olha, se tem uma empresa que vem transformando o jeito de viver dos últimos anos, essa empresa seguramente é a Vive Empreendimentos. Nascida em Catanduva, a Vive hoje está presente em quatro estados d</t>
         </is>
       </c>
-      <c r="G38" s="72" t="inlineStr">
+      <c r="G38" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Vive_Empreendimentos__empreendimentos_imobiliarios__09-03-2026_09-06-52.mp3</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="72" t="inlineStr">
+      <c r="A39" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:07:08</t>
         </is>
       </c>
-      <c r="B39" s="72" t="inlineStr">
+      <c r="B39" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C39" s="72" t="inlineStr">
+      <c r="C39" s="76" t="inlineStr">
         <is>
           <t>Vive</t>
         </is>
       </c>
-      <c r="D39" s="72" t="inlineStr">
+      <c r="D39" s="76" t="inlineStr">
         <is>
           <t>Loteamentos e espaços planejados</t>
         </is>
       </c>
-      <c r="E39" s="72" t="inlineStr">
+      <c r="E39" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2145,34 +2154,34 @@
           <t>Atenção, São Paulo, Mato Grosso do Sul, Minas Gerais e Goiás. Sempre levando desempenho com responsabilidade, sustentabilidade e muita inovação. Quem conhece os projetos da Vive sabe, não são apenas l</t>
         </is>
       </c>
-      <c r="G39" s="72" t="inlineStr">
+      <c r="G39" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Vive__Loteamentos_e_espacos_planejados__09-03-2026_09-07-08.mp3</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="72" t="inlineStr">
+      <c r="A40" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:07:26</t>
         </is>
       </c>
-      <c r="B40" s="72" t="inlineStr">
+      <c r="B40" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C40" s="72" t="inlineStr">
+      <c r="C40" s="76" t="inlineStr">
         <is>
           <t>VIB</t>
         </is>
       </c>
-      <c r="D40" s="72" t="inlineStr">
+      <c r="D40" s="76" t="inlineStr">
         <is>
           <t>empreendimentos imobiliários</t>
         </is>
       </c>
-      <c r="E40" s="72" t="inlineStr">
+      <c r="E40" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2182,34 +2191,34 @@
           <t>para oferecer mais qualidade de vida, contato com a natureza e toda a infraestrutura que as famílias procuram para viver bem. E tem mais, como coligada no grupo Serradinho, a VIB carrega a credibilida</t>
         </is>
       </c>
-      <c r="G40" s="72" t="inlineStr">
+      <c r="G40" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__VIB__empreendimentos_imobiliarios__09-03-2026_09-07-26.mp3</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="72" t="inlineStr">
+      <c r="A41" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:07:44</t>
         </is>
       </c>
-      <c r="B41" s="72" t="inlineStr">
+      <c r="B41" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C41" s="72" t="inlineStr">
+      <c r="C41" s="76" t="inlineStr">
         <is>
           <t>Oralfai Catanduva</t>
         </is>
       </c>
-      <c r="D41" s="72" t="inlineStr">
+      <c r="D41" s="76" t="inlineStr">
         <is>
           <t>tratamentos odontológicos</t>
         </is>
       </c>
-      <c r="E41" s="72" t="inlineStr">
+      <c r="E41" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2219,34 +2228,34 @@
           <t xml:space="preserve">Visão de futuro e compromisso com as cidades onde atua, vive empreendimentos conectando pessoas, criando novas formas de viver e mudando o futuro. Jovem Pan Olá, eu sou o doutor Guilherme Pelegrin da </t>
         </is>
       </c>
-      <c r="G41" s="72" t="inlineStr">
+      <c r="G41" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Oralfai_Catanduva__tratamentos_odontologicos__09-03-2026_09-07-44.mp3</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="72" t="inlineStr">
+      <c r="A42" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:08:38</t>
         </is>
       </c>
-      <c r="B42" s="72" t="inlineStr">
+      <c r="B42" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C42" s="72" t="inlineStr">
+      <c r="C42" s="76" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D42" s="72" t="inlineStr">
+      <c r="D42" s="76" t="inlineStr">
         <is>
           <t>Ovos de Páscoa e tabletes</t>
         </is>
       </c>
-      <c r="E42" s="72" t="inlineStr">
+      <c r="E42" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2256,34 +2265,34 @@
           <t>E nos momentos em memórias que ficam para sempre. E quando o assunto é celebrar com sabor, a escolha é uma só. Cacau Show. Ovos de Páscoa encantadores. Tabletes irresistíveis. Presentes que emocionam.</t>
         </is>
       </c>
-      <c r="G42" s="72" t="inlineStr">
+      <c r="G42" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show__Ovos_de_Pascoa_e_tabletes__09-03-2026_09-08-38.mp3</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="72" t="inlineStr">
+      <c r="A43" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:09:51</t>
         </is>
       </c>
-      <c r="B43" s="72" t="inlineStr">
+      <c r="B43" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C43" s="72" t="inlineStr">
+      <c r="C43" s="76" t="inlineStr">
         <is>
           <t>Jovem Pan</t>
         </is>
       </c>
-      <c r="D43" s="72" t="inlineStr">
+      <c r="D43" s="76" t="inlineStr">
         <is>
           <t>Cobertura da Copa do Mundo</t>
         </is>
       </c>
-      <c r="E43" s="72" t="inlineStr">
+      <c r="E43" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2293,34 +2302,34 @@
           <t>Agora é dois mil e vinte e seis. Estados Unidos, México e Canadá. Desde sempre, a Jovem Pan está presente nas Copas do Mundo com equipe completa, informação em tempo real, opinião forte e a energia de</t>
         </is>
       </c>
-      <c r="G43" s="72" t="inlineStr">
+      <c r="G43" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Jovem_Pan__Cobertura_da_Copa_do_Mundo__09-03-2026_09-09-51.mp3</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="72" t="inlineStr">
+      <c r="A44" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:14:02</t>
         </is>
       </c>
-      <c r="B44" s="72" t="inlineStr">
+      <c r="B44" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C44" s="72" t="inlineStr">
+      <c r="C44" s="76" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D44" s="72" t="inlineStr">
+      <c r="D44" s="76" t="inlineStr">
         <is>
           <t>Ovo de Páscoa</t>
         </is>
       </c>
-      <c r="E44" s="72" t="inlineStr">
+      <c r="E44" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2330,34 +2339,34 @@
           <t>porque ele tá dando mau exemplo do programa, eu acho que ele tá muito besteirento, ô Babu, você tá muito besteirento, Babu, para de falar, tá falando muita besteira e ainda tá causando esse alvoroço n</t>
         </is>
       </c>
-      <c r="G44" s="72" t="inlineStr">
+      <c r="G44" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show__Ovo_de_Pascoa__09-03-2026_09-14-02.mp3</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="72" t="inlineStr">
+      <c r="A45" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:14:20</t>
         </is>
       </c>
-      <c r="B45" s="72" t="inlineStr">
+      <c r="B45" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C45" s="72" t="inlineStr">
+      <c r="C45" s="76" t="inlineStr">
         <is>
           <t>Jovem Pan</t>
         </is>
       </c>
-      <c r="D45" s="72" t="inlineStr">
+      <c r="D45" s="76" t="inlineStr">
         <is>
           <t>Ovo de Páscoa Cacau Show</t>
         </is>
       </c>
-      <c r="E45" s="72" t="inlineStr">
+      <c r="E45" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2367,34 +2376,34 @@
           <t xml:space="preserve">E nas redes sociais, a hashtag tá lá, Babu Expulso, o que que cê acha? Conta aí que eu quero saber, no finalzinho, da hora do Manhã Pan. Fique ligado porque tem o ovo de páscoa cacau show, tá rolando </t>
         </is>
       </c>
-      <c r="G45" s="72" t="inlineStr">
+      <c r="G45" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__Jovem_Pan__Ovo_de_Pascoa_Cacau_Show__09-03-2026_09-14-20.mp3</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="72" t="inlineStr">
+      <c r="A46" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:14:24</t>
         </is>
       </c>
-      <c r="B46" s="72" t="inlineStr">
+      <c r="B46" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C46" s="72" t="inlineStr">
+      <c r="C46" s="76" t="inlineStr">
         <is>
           <t>Sotintas</t>
         </is>
       </c>
-      <c r="D46" s="72" t="inlineStr">
+      <c r="D46" s="76" t="inlineStr">
         <is>
           <t>loja de produtos</t>
         </is>
       </c>
-      <c r="E46" s="72" t="inlineStr">
+      <c r="E46" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2404,34 +2413,34 @@
           <t>Música Não saia daí, já já tem muito mais músicas aqui na Band FM Música Conheça a nova loja da Sotintas em Catanduva, na avenida Berendito Zancaner 1481 Um novo, moderno e amplo espaço para você conh</t>
         </is>
       </c>
-      <c r="G46" s="72" t="inlineStr">
+      <c r="G46" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Sotintas__loja_de_produtos__09-03-2026_09-14-24__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="62" t="inlineStr">
+      <c r="A47" s="75" t="inlineStr">
         <is>
           <t>09/03/2026 09:14:24</t>
         </is>
       </c>
-      <c r="B47" s="62" t="inlineStr">
+      <c r="B47" s="75" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C47" s="62" t="inlineStr">
+      <c r="C47" s="75" t="inlineStr">
         <is>
           <t>Lufthansa</t>
         </is>
       </c>
-      <c r="D47" s="62" t="inlineStr">
+      <c r="D47" s="75" t="inlineStr">
         <is>
           <t>linha de produtos</t>
         </is>
       </c>
-      <c r="E47" s="62" t="inlineStr">
+      <c r="E47" s="75" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -2441,34 +2450,34 @@
           <t>Música Não saia daí, já já tem muito mais músicas aqui na Band FM Música Conheça a nova loja da Sotintas em Catanduva, na avenida Berendito Zancaner 1481 Um novo, moderno e amplo espaço para você conh</t>
         </is>
       </c>
-      <c r="G47" s="62" t="inlineStr">
+      <c r="G47" s="75" t="inlineStr">
         <is>
           <t>Band_FM__Lufthansa__linha_de_produtos__09-03-2026_09-14-24__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="72" t="inlineStr">
+      <c r="A48" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:15:00</t>
         </is>
       </c>
-      <c r="B48" s="72" t="inlineStr">
+      <c r="B48" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C48" s="72" t="inlineStr">
+      <c r="C48" s="76" t="inlineStr">
         <is>
           <t>Tatinho Veículos</t>
         </is>
       </c>
-      <c r="D48" s="72" t="inlineStr">
+      <c r="D48" s="76" t="inlineStr">
         <is>
           <t>Veículos</t>
         </is>
       </c>
-      <c r="E48" s="72" t="inlineStr">
+      <c r="E48" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2478,34 +2487,34 @@
           <t>José Nelson Machado, mil trezentos e setenta e nove, e agora também, na Avenida Benedito Zancanet, mil quatrocentos e oitenta e um, ao lado do Proença Supermercados. Só tintas, tudo em tintas, pra com</t>
         </is>
       </c>
-      <c r="G48" s="72" t="inlineStr">
+      <c r="G48" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Tatinho_Veiculos__Veiculos__09-03-2026_09-15-00.mp3</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="62" t="inlineStr">
+      <c r="A49" s="75" t="inlineStr">
         <is>
           <t>09/03/2026 09:17:16</t>
         </is>
       </c>
-      <c r="B49" s="62" t="inlineStr">
+      <c r="B49" s="75" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C49" s="62" t="inlineStr">
+      <c r="C49" s="75" t="inlineStr">
         <is>
           <t>Procuro, mora, esquete, supermercados</t>
         </is>
       </c>
-      <c r="D49" s="62" t="inlineStr">
+      <c r="D49" s="75" t="inlineStr">
         <is>
           <t>Produtos de supermercado</t>
         </is>
       </c>
-      <c r="E49" s="62" t="inlineStr">
+      <c r="E49" s="75" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -2515,34 +2524,34 @@
           <t>Filos folha dupla, vinte metros, com doze unidades, doze e noventa e nove. Refrigerante, roler cola pet, dois litros, seis e noventa e nove. Procuro, mora, esquete, supermercados, qualidade, confiança</t>
         </is>
       </c>
-      <c r="G49" s="62" t="inlineStr">
+      <c r="G49" s="75" t="inlineStr">
         <is>
           <t>Band_FM__Procuro__mora__esquete__supermercados__Produtos_de_supermercado__09-03-2026_09-17-15__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="72" t="inlineStr">
+      <c r="A50" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:17:16</t>
         </is>
       </c>
-      <c r="B50" s="72" t="inlineStr">
+      <c r="B50" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C50" s="72" t="inlineStr">
+      <c r="C50" s="76" t="inlineStr">
         <is>
           <t>Alto Posto Campeão</t>
         </is>
       </c>
-      <c r="D50" s="72" t="inlineStr">
+      <c r="D50" s="76" t="inlineStr">
         <is>
           <t>Combustível</t>
         </is>
       </c>
-      <c r="E50" s="72" t="inlineStr">
+      <c r="E50" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2552,34 +2561,34 @@
           <t>Filos folha dupla, vinte metros, com doze unidades, doze e noventa e nove. Refrigerante, roler cola pet, dois litros, seis e noventa e nove. Procuro, mora, esquete, supermercados, qualidade, confiança</t>
         </is>
       </c>
-      <c r="G50" s="72" t="inlineStr">
+      <c r="G50" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Alto_Posto_Campeao__Combustivel__09-03-2026_09-17-16__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="72" t="inlineStr">
+      <c r="A51" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:17:33</t>
         </is>
       </c>
-      <c r="B51" s="72" t="inlineStr">
+      <c r="B51" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C51" s="72" t="inlineStr">
+      <c r="C51" s="76" t="inlineStr">
         <is>
           <t>Bande FM</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="76" t="inlineStr">
         <is>
           <t>Rádio</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2589,34 +2598,34 @@
           <t>É bem melhor, é Bande FM.</t>
         </is>
       </c>
-      <c r="G51" s="72" t="inlineStr">
+      <c r="G51" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Bande_FM__Radio__09-03-2026_09-17-33.mp3</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="72" t="inlineStr">
+      <c r="A52" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:30:51</t>
         </is>
       </c>
-      <c r="B52" s="72" t="inlineStr">
+      <c r="B52" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C52" s="72" t="inlineStr">
+      <c r="C52" s="76" t="inlineStr">
         <is>
           <t>Traia Veia</t>
         </is>
       </c>
-      <c r="D52" s="72" t="inlineStr">
+      <c r="D52" s="76" t="inlineStr">
         <is>
           <t>Evento (show)</t>
         </is>
       </c>
-      <c r="E52" s="72" t="inlineStr">
+      <c r="E52" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2626,34 +2635,34 @@
           <t>Primeira vez na região, Traia Veia! E em palco, 360! Mesas, open pool de open bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br Seu moço e Traia Veia! Dia 20 de</t>
         </is>
       </c>
-      <c r="G52" s="72" t="inlineStr">
+      <c r="G52" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Traia_Veia__Evento__show__09-03-2026_09-30-51__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="62" t="inlineStr">
+      <c r="A53" s="75" t="inlineStr">
         <is>
           <t>09/03/2026 09:30:51</t>
         </is>
       </c>
-      <c r="B53" s="62" t="inlineStr">
+      <c r="B53" s="75" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C53" s="62" t="inlineStr">
+      <c r="C53" s="75" t="inlineStr">
         <is>
           <t>Clube de Tênis Catanduva</t>
         </is>
       </c>
-      <c r="D53" s="62" t="inlineStr">
+      <c r="D53" s="75" t="inlineStr">
         <is>
           <t>Espaço para eventos</t>
         </is>
       </c>
-      <c r="E53" s="62" t="inlineStr">
+      <c r="E53" s="75" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -2663,34 +2672,34 @@
           <t>Primeira vez na região, Traia Veia! E em palco, 360! Mesas, open pool de open bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br Seu moço e Traia Veia! Dia 20 de</t>
         </is>
       </c>
-      <c r="G53" s="62" t="inlineStr">
+      <c r="G53" s="75" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Clube_de_Tenis_Catanduva__Espaco_para_eventos__09-03-2026_09-30-51__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="72" t="inlineStr">
+      <c r="A54" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:30:51</t>
         </is>
       </c>
-      <c r="B54" s="72" t="inlineStr">
+      <c r="B54" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C54" s="72" t="inlineStr">
+      <c r="C54" s="76" t="inlineStr">
         <is>
           <t>Quero Dois Ingressos</t>
         </is>
       </c>
-      <c r="D54" s="72" t="inlineStr">
+      <c r="D54" s="76" t="inlineStr">
         <is>
           <t>Serviço de venda de ingressos</t>
         </is>
       </c>
-      <c r="E54" s="72" t="inlineStr">
+      <c r="E54" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2700,34 +2709,34 @@
           <t>Primeira vez na região, Traia Veia! E em palco, 360! Mesas, open pool de open bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br Seu moço e Traia Veia! Dia 20 de</t>
         </is>
       </c>
-      <c r="G54" s="72" t="inlineStr">
+      <c r="G54" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Quero_Dois_Ingressos__Servico_de_venda_de_ingressos__09-03-2026_09-30-51__ad3.mp3</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="72" t="inlineStr">
+      <c r="A55" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:31:07</t>
         </is>
       </c>
-      <c r="B55" s="72" t="inlineStr">
+      <c r="B55" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C55" s="72" t="inlineStr">
+      <c r="C55" s="76" t="inlineStr">
         <is>
           <t>Clube de Tênis Catanduva</t>
         </is>
       </c>
-      <c r="D55" s="72" t="inlineStr">
+      <c r="D55" s="76" t="inlineStr">
         <is>
           <t>Ingressos</t>
         </is>
       </c>
-      <c r="E55" s="72" t="inlineStr">
+      <c r="E55" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2737,34 +2746,34 @@
           <t>A venda na Secretaria do Clube ou quero dois ingressos ponto com ponto BR. Seu moço e praia velha, dia vinte de março no Clube de Tênis Catanduva. Na vida, os imprevistos são comuns. Aquela viagem ine</t>
         </is>
       </c>
-      <c r="G55" s="72" t="inlineStr">
+      <c r="G55" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Clube_de_Tenis_Catanduva__Ingressos__09-03-2026_09-31-07.mp3</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="72" t="inlineStr">
+      <c r="A56" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:31:56</t>
         </is>
       </c>
-      <c r="B56" s="72" t="inlineStr">
+      <c r="B56" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C56" s="72" t="inlineStr">
+      <c r="C56" s="76" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D56" s="72" t="inlineStr">
+      <c r="D56" s="76" t="inlineStr">
         <is>
           <t>Produtos alimentícios (peixe, camarão, farinha, queijo, papel)</t>
         </is>
       </c>
-      <c r="E56" s="72" t="inlineStr">
+      <c r="E56" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2774,34 +2783,34 @@
           <t>Peixe e muito mais, tudo com preço baixinho pra você aproveitar. Filé de peito laro, 1,1497. Camarão palimara, 180 gramas, 1,1497. Farinha globo, 1,247. Tó de 370 gramas, 7,99. Mussarela a partir de 2</t>
         </is>
       </c>
-      <c r="G56" s="72" t="inlineStr">
+      <c r="G56" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Mar__Produtos_alimenticios__peixe__camarao__farinha__queijo__pape__09-03-2026_09-31-56.mp3</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="72" t="inlineStr">
+      <c r="A57" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:32:13</t>
         </is>
       </c>
-      <c r="B57" s="72" t="inlineStr">
+      <c r="B57" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C57" s="72" t="inlineStr">
+      <c r="C57" s="76" t="inlineStr">
         <is>
           <t>Atacarejo Mar</t>
         </is>
       </c>
-      <c r="D57" s="72" t="inlineStr">
+      <c r="D57" s="76" t="inlineStr">
         <is>
           <t>Páscoa</t>
         </is>
       </c>
-      <c r="E57" s="72" t="inlineStr">
+      <c r="E57" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2811,34 +2820,34 @@
           <t xml:space="preserve">Tocando Papel Supra, vinte e nove e noventa. A maior páscoa do atacarejo é no mar. De voltar aqui na Ondas Verdes, nove e trinta e um agora. Alô, Toninha, bom dia, cê tá boa? Eu sou bem abençoado pra </t>
         </is>
       </c>
-      <c r="G57" s="72" t="inlineStr">
+      <c r="G57" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Atacarejo_Mar__Pascoa__09-03-2026_09-32-13.mp3</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="62" t="inlineStr">
+      <c r="A58" s="75" t="inlineStr">
         <is>
           <t>09/03/2026 09:34:10</t>
         </is>
       </c>
-      <c r="B58" s="62" t="inlineStr">
+      <c r="B58" s="75" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C58" s="62" t="inlineStr">
+      <c r="C58" s="75" t="inlineStr">
         <is>
           <t>Desconhecido</t>
         </is>
       </c>
-      <c r="D58" s="62" t="inlineStr">
+      <c r="D58" s="75" t="inlineStr">
         <is>
           <t>Promoção</t>
         </is>
       </c>
-      <c r="E58" s="62" t="inlineStr">
+      <c r="E58" s="75" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -2848,34 +2857,34 @@
           <t>O barulho que eu vou causar Peguei o meu carro, comprei mega fone É hoje que cê escuta a minha saudade de longe Olha o carro do ex passando na sua porta Olha o beijo docinho, abraço quentinho, a pegad</t>
         </is>
       </c>
-      <c r="G58" s="62" t="inlineStr">
+      <c r="G58" s="75" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__Promocao__09-03-2026_09-34-10.mp3</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="62" t="inlineStr">
+      <c r="A59" s="75" t="inlineStr">
         <is>
           <t>09/03/2026 09:35:03</t>
         </is>
       </c>
-      <c r="B59" s="62" t="inlineStr">
+      <c r="B59" s="75" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C59" s="62" t="inlineStr">
+      <c r="C59" s="75" t="inlineStr">
         <is>
           <t>Desconhecido</t>
         </is>
       </c>
-      <c r="D59" s="62" t="inlineStr">
+      <c r="D59" s="75" t="inlineStr">
         <is>
           <t>Produto ou serviço desconhecido</t>
         </is>
       </c>
-      <c r="E59" s="62" t="inlineStr">
+      <c r="E59" s="75" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -2885,34 +2894,34 @@
           <t>O carro comprei, megafone, é hoje que você escuta a minha saudade hoje Olha o carro do ex, olha o beijo docinho, abraço, minha pegada gostosa Olha o carro do ex parando aqui na frente, aproveita a pro</t>
         </is>
       </c>
-      <c r="G59" s="62" t="inlineStr">
+      <c r="G59" s="75" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__Produto_ou_servico_desconhecido__09-03-2026_09-35-03.mp3</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="72" t="inlineStr">
+      <c r="A60" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:35:56</t>
         </is>
       </c>
-      <c r="B60" s="72" t="inlineStr">
+      <c r="B60" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C60" s="72" t="inlineStr">
+      <c r="C60" s="76" t="inlineStr">
         <is>
           <t>Rede Móveis Casa Vende</t>
         </is>
       </c>
-      <c r="D60" s="72" t="inlineStr">
+      <c r="D60" s="76" t="inlineStr">
         <is>
           <t>Produtos para renovar a casa</t>
         </is>
       </c>
-      <c r="E60" s="72" t="inlineStr">
+      <c r="E60" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2922,34 +2931,34 @@
           <t>Não saia daí, já já tem muito mais músicas aqui na Band FM. Band FM Atenção Catanduva e região, é aniversário da Rede Móveis Casa Vende. Com ofertas especiais para renovar a sua casa. Produtos selecio</t>
         </is>
       </c>
-      <c r="G60" s="72" t="inlineStr">
+      <c r="G60" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Rede_Moveis_Casa_Vende__Produtos_para_renovar_a_casa__09-03-2026_09-35-56.mp3</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="72" t="inlineStr">
+      <c r="A61" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:36:33</t>
         </is>
       </c>
-      <c r="B61" s="72" t="inlineStr">
+      <c r="B61" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C61" s="72" t="inlineStr">
+      <c r="C61" s="76" t="inlineStr">
         <is>
           <t>Cressol</t>
         </is>
       </c>
-      <c r="D61" s="72" t="inlineStr">
+      <c r="D61" s="76" t="inlineStr">
         <is>
           <t>Promoção Operar é Ganhar</t>
         </is>
       </c>
-      <c r="E61" s="72" t="inlineStr">
+      <c r="E61" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2959,34 +2968,34 @@
           <t xml:space="preserve">Dá pra contar com a sorte, né? Mas se a sorte te ajudar, você ainda pode ganhar 12 milhões em prêmios com a promoção Operar é Ganhar. Invista com a Cressol, gere números da sorte e concorra. Você vai </t>
         </is>
       </c>
-      <c r="G61" s="72" t="inlineStr">
+      <c r="G61" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Cressol__Promocao_Operar_e_Ganhar__09-03-2026_09-36-33__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="72" t="inlineStr">
+      <c r="A62" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:36:33</t>
         </is>
       </c>
-      <c r="B62" s="72" t="inlineStr">
+      <c r="B62" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C62" s="72" t="inlineStr">
+      <c r="C62" s="76" t="inlineStr">
         <is>
           <t>Alto Posto Campeão</t>
         </is>
       </c>
-      <c r="D62" s="72" t="inlineStr">
+      <c r="D62" s="76" t="inlineStr">
         <is>
           <t>Combustível</t>
         </is>
       </c>
-      <c r="E62" s="72" t="inlineStr">
+      <c r="E62" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2996,34 +3005,34 @@
           <t xml:space="preserve">Dá pra contar com a sorte, né? Mas se a sorte te ajudar, você ainda pode ganhar 12 milhões em prêmios com a promoção Operar é Ganhar. Invista com a Cressol, gere números da sorte e concorra. Você vai </t>
         </is>
       </c>
-      <c r="G62" s="72" t="inlineStr">
+      <c r="G62" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Alto_Posto_Campeao__Combustivel__09-03-2026_09-36-33__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="72" t="inlineStr">
+      <c r="A63" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:36:50</t>
         </is>
       </c>
-      <c r="B63" s="72" t="inlineStr">
+      <c r="B63" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C63" s="72" t="inlineStr">
+      <c r="C63" s="76" t="inlineStr">
         <is>
           <t>Alto Posto Campeão</t>
         </is>
       </c>
-      <c r="D63" s="72" t="inlineStr">
+      <c r="D63" s="76" t="inlineStr">
         <is>
           <t>Combustível e conveniência</t>
         </is>
       </c>
-      <c r="E63" s="72" t="inlineStr">
+      <c r="E63" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3033,34 +3042,34 @@
           <t>Só poderá é ganhar Certificado de autorização SPAME, número 04047374 Alto Posto Campeão, o seu destino de qualidade em combustível Vá conhecer o Alto Posto Campeão, onde qualidade e preço campeão anda</t>
         </is>
       </c>
-      <c r="G63" s="72" t="inlineStr">
+      <c r="G63" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Alto_Posto_Campeao__Combustivel_e_conveniencia__09-03-2026_09-36-50.mp3</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="72" t="inlineStr">
+      <c r="A64" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:37:08</t>
         </is>
       </c>
-      <c r="B64" s="72" t="inlineStr">
+      <c r="B64" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C64" s="72" t="inlineStr">
+      <c r="C64" s="76" t="inlineStr">
         <is>
           <t>UOL</t>
         </is>
       </c>
-      <c r="D64" s="72" t="inlineStr">
+      <c r="D64" s="76" t="inlineStr">
         <is>
           <t>Enquete do Big Brother 26</t>
         </is>
       </c>
-      <c r="E64" s="72" t="inlineStr">
+      <c r="E64" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3070,34 +3079,34 @@
           <t>Rafa, que negócio do Babu, hein? Babu, eu vou te falar, hein, Babu? O Paulo mandou pra gente aqui, o nosso ouvinte, ele falou assim Ô Rafa, cola no site do UOL Vai lá no UOL que tem a enquete A enquet</t>
         </is>
       </c>
-      <c r="G64" s="72" t="inlineStr">
+      <c r="G64" s="76" t="inlineStr">
         <is>
           <t>Jovem_Pan__UOL__Enquete_do_Big_Brother_26__09-03-2026_09-37-08.mp3</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="72" t="inlineStr">
+      <c r="A65" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 09:39:48</t>
         </is>
       </c>
-      <c r="B65" s="72" t="inlineStr">
+      <c r="B65" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C65" s="72" t="inlineStr">
+      <c r="C65" s="76" t="inlineStr">
         <is>
           <t>Grupo Moresque</t>
         </is>
       </c>
-      <c r="D65" s="72" t="inlineStr">
+      <c r="D65" s="76" t="inlineStr">
         <is>
           <t>Carnes e arroz</t>
         </is>
       </c>
-      <c r="E65" s="72" t="inlineStr">
+      <c r="E65" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3107,7 +3116,7 @@
           <t>o mundo. Atenção para algumas das grandes ofertas do Grupo Moresque válidas até dia nove de março. Alcatra com a minha bovina quilo quarenta e três e noventa e nove contra filé bovino quilo quarenta e</t>
         </is>
       </c>
-      <c r="G65" s="72" t="inlineStr">
+      <c r="G65" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Grupo_Moresque__Carnes_e_arroz__09-03-2026_09-39-48.mp3</t>
         </is>
@@ -3151,27 +3160,27 @@
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="72" t="inlineStr">
+      <c r="A67" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 10:05:17</t>
         </is>
       </c>
-      <c r="B67" s="72" t="inlineStr">
+      <c r="B67" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C67" s="72" t="inlineStr">
+      <c r="C67" s="76" t="inlineStr">
         <is>
           <t>Band FM</t>
         </is>
       </c>
-      <c r="D67" s="72" t="inlineStr">
+      <c r="D67" s="76" t="inlineStr">
         <is>
           <t>Rádio/Programa</t>
         </is>
       </c>
-      <c r="E67" s="72" t="inlineStr">
+      <c r="E67" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3181,34 +3190,34 @@
           <t xml:space="preserve">Lógico, comentar nas nossas redes sociais. É isso que eu tava pensando. Escolher o nome e ganhar o mascote mais gostosinho do rádio brasileiro. É tudo de bom. É tudo de Band. Band FM. Band FM. Queria </t>
         </is>
       </c>
-      <c r="G67" s="72" t="inlineStr">
+      <c r="G67" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Band_FM__Radio_Programa__09-03-2026_10-05-17.mp3</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="72" t="inlineStr">
+      <c r="A68" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 10:28:54</t>
         </is>
       </c>
-      <c r="B68" s="72" t="inlineStr">
+      <c r="B68" s="76" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C68" s="72" t="inlineStr">
+      <c r="C68" s="76" t="inlineStr">
         <is>
           <t>Band FM</t>
         </is>
       </c>
-      <c r="D68" s="72" t="inlineStr">
+      <c r="D68" s="76" t="inlineStr">
         <is>
           <t>Smartphone novo</t>
         </is>
       </c>
-      <c r="E68" s="72" t="inlineStr">
+      <c r="E68" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3218,7 +3227,7 @@
           <t>Vinte e seis, resolvendo a vida. É, tudo da Band é ótimo, né? Tudo de boa qualidade. Mande um WhatsApp pra Band FM dizendo Smartphone novo, é na Band FM. Pronto, já tá concorrendo. Vende presente toda</t>
         </is>
       </c>
-      <c r="G68" s="72" t="inlineStr">
+      <c r="G68" s="76" t="inlineStr">
         <is>
           <t>Band_FM__Band_FM__Smartphone_novo__09-03-2026_10-28-54.mp3</t>
         </is>
@@ -3262,27 +3271,27 @@
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="74" t="inlineStr">
+      <c r="A70" s="76" t="inlineStr">
         <is>
           <t>09/03/2026 11:03:50</t>
         </is>
       </c>
-      <c r="B70" s="74" t="inlineStr">
+      <c r="B70" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C70" s="74" t="inlineStr">
+      <c r="C70" s="76" t="inlineStr">
         <is>
           <t>Ótica Fabrilein</t>
         </is>
       </c>
-      <c r="D70" s="74" t="inlineStr">
+      <c r="D70" s="76" t="inlineStr">
         <is>
           <t>Lentes e atendimento óptico</t>
         </is>
       </c>
-      <c r="E70" s="74" t="inlineStr">
+      <c r="E70" s="76" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3292,9 +3301,120 @@
           <t>Ah, ofertas válidas até dia vinte e dois de março ou enquanto durarem os estoques. Vem conferir, um a noventa e nove, quem economiza pode mais. Quando o assunto é visão, a ótica Fabrilein é referência</t>
         </is>
       </c>
-      <c r="G70" s="74" t="inlineStr">
+      <c r="G70" s="76" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Otica_Fabrilein__Lentes_e_atendimento_optico__09-03-2026_11-03-50.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="75" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:33:05</t>
+        </is>
+      </c>
+      <c r="B71" s="75" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C71" s="75" t="inlineStr">
+        <is>
+          <t>Band FM</t>
+        </is>
+      </c>
+      <c r="D71" s="75" t="inlineStr">
+        <is>
+          <t>Rádio/Programação</t>
+        </is>
+      </c>
+      <c r="E71" s="75" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>Médias ou grandes, faça agora mesmo um orçamento. 17-997-616-341. Equipe DJ Fabrício Moreira. Fique por dentro de tudo o que rola na Band FM. Acesse a nossa página no Facebook. 96.1 Band FM Catanduva.</t>
+        </is>
+      </c>
+      <c r="G71" s="75" t="inlineStr">
+        <is>
+          <t>Band_FM__Band_FM__Radio_Programacao__09-03-2026_11-33-05__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="76" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:33:05</t>
+        </is>
+      </c>
+      <c r="B72" s="76" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C72" s="76" t="inlineStr">
+        <is>
+          <t>Equipe DJ Fabrício Moreira</t>
+        </is>
+      </c>
+      <c r="D72" s="76" t="inlineStr">
+        <is>
+          <t>Serviço de orçamento</t>
+        </is>
+      </c>
+      <c r="E72" s="76" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Médias ou grandes, faça agora mesmo um orçamento. 17-997-616-341. Equipe DJ Fabrício Moreira. Fique por dentro de tudo o que rola na Band FM. Acesse a nossa página no Facebook. 96.1 Band FM Catanduva.</t>
+        </is>
+      </c>
+      <c r="G72" s="76" t="inlineStr">
+        <is>
+          <t>Band_FM__Equipe_DJ_Fabricio_Moreira__Servico_de_orcamento__09-03-2026_11-33-05__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="77" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:33:18</t>
+        </is>
+      </c>
+      <c r="B73" s="77" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C73" s="77" t="inlineStr">
+        <is>
+          <t>Restaurante Sabor da Casa</t>
+        </is>
+      </c>
+      <c r="D73" s="77" t="inlineStr">
+        <is>
+          <t>Refeição por quilo, self-service e marmitex</t>
+        </is>
+      </c>
+      <c r="E73" s="77" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Band FM Catanduva Imagine você almoçar em um restaurante que tem o sabor da casa. Em Catanduva você consegue. Restaurante Sabor da Casa. Refeição por quilo, self-service e marmitex. O Restaurante Sabo</t>
+        </is>
+      </c>
+      <c r="G73" s="77" t="inlineStr">
+        <is>
+          <t>Band_FM__Restaurante_Sabor_da_Casa__Refeicao_por_quilo__self-service_e_marmitex__09-03-2026_11-33-18.mp3</t>
         </is>
       </c>
     </row>
@@ -3366,11 +3486,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09/03/2026 10:32:17</t>
+          <t>09/03/2026 11:33:18</t>
         </is>
       </c>
     </row>

--- a/radio_capture/relatorio_anuncios.xlsx
+++ b/radio_capture/relatorio_anuncios.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -683,6 +683,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1050,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1100,27 +1103,27 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="176" t="inlineStr">
+      <c r="A2" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:17:31</t>
         </is>
       </c>
-      <c r="B2" s="176" t="inlineStr">
+      <c r="B2" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C2" s="176" t="inlineStr">
+      <c r="C2" s="192" t="inlineStr">
         <is>
           <t>AXE</t>
         </is>
       </c>
-      <c r="D2" s="176" t="inlineStr">
+      <c r="D2" s="192" t="inlineStr">
         <is>
           <t>produtos de Páscoa</t>
         </is>
       </c>
-      <c r="E2" s="176" t="inlineStr">
+      <c r="E2" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1130,7 +1133,7 @@
           <t>Ação Espírita Boa Nova convida você para uma palestra espírita com Silvio dos Santos. Quarta-feira, 11 de março, às 20h, com entrada gratuita. Não perca! A partir das 19h30, teremos a música espírita.</t>
         </is>
       </c>
-      <c r="G2" s="176" t="inlineStr">
+      <c r="G2" s="192" t="inlineStr">
         <is>
           <t>Band_FM__AXE__produtos_de_Pascoa__11-03-2026_15-17-31__ad1.mp3</t>
         </is>
@@ -1174,27 +1177,27 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="176" t="inlineStr">
+      <c r="A4" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:17:43</t>
         </is>
       </c>
-      <c r="B4" s="176" t="inlineStr">
+      <c r="B4" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C4" s="176" t="inlineStr">
+      <c r="C4" s="192" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D4" s="176" t="inlineStr">
+      <c r="D4" s="192" t="inlineStr">
         <is>
           <t>Produtos alimentícios</t>
         </is>
       </c>
-      <c r="E4" s="176" t="inlineStr">
+      <c r="E4" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1204,34 +1207,34 @@
           <t>Vida Porto Ferreira, 931, no Parque Nacema, em Catanduva. Tem surpresa de Páscoa melhor do que preço baixo? Não! Com os preços baixos do Max, você não abalba de Páscoa pra todo mundo. E ainda economiz</t>
         </is>
       </c>
-      <c r="G4" s="176" t="inlineStr">
+      <c r="G4" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Max__Produtos_alimenticios__11-03-2026_15-17-43.mp3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="176" t="inlineStr">
+      <c r="A5" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:18:18</t>
         </is>
       </c>
-      <c r="B5" s="176" t="inlineStr">
+      <c r="B5" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C5" s="176" t="inlineStr">
+      <c r="C5" s="192" t="inlineStr">
         <is>
           <t>Rede Móveis Casa Vinde</t>
         </is>
       </c>
-      <c r="D5" s="176" t="inlineStr">
+      <c r="D5" s="192" t="inlineStr">
         <is>
           <t>Produtos para renovar a casa</t>
         </is>
       </c>
-      <c r="E5" s="176" t="inlineStr">
+      <c r="E5" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1241,34 +1244,34 @@
           <t>A Bande FM é bem melhor porque é do seu jeito. A gente é o que é afinal. Atenção, Catanduba e região. É aniversário da Rede Móveis Casa Vinde. Com ofertas especiais para renovar a sua casa. Produtos s</t>
         </is>
       </c>
-      <c r="G5" s="176" t="inlineStr">
+      <c r="G5" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Rede_Moveis_Casa_Vinde__Produtos_para_renovar_a_casa__11-03-2026_15-18-18.mp3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="176" t="inlineStr">
+      <c r="A6" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:18:36</t>
         </is>
       </c>
-      <c r="B6" s="176" t="inlineStr">
+      <c r="B6" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C6" s="176" t="inlineStr">
+      <c r="C6" s="192" t="inlineStr">
         <is>
           <t>Rede Móveis Casa Bende</t>
         </is>
       </c>
-      <c r="D6" s="176" t="inlineStr">
+      <c r="D6" s="192" t="inlineStr">
         <is>
           <t>produtos para casa</t>
         </is>
       </c>
-      <c r="E6" s="176" t="inlineStr">
+      <c r="E6" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1278,7 +1281,7 @@
           <t>de pagamento facilitado em até 15 vezes no boleto. Visite a loja na Rua Amazônia 617, no centro. Rede Móveis Casa Bende. O melhor cenário da vida é a sua casa. Você que vai casar, pare um instante. Im</t>
         </is>
       </c>
-      <c r="G6" s="176" t="inlineStr">
+      <c r="G6" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Rede_Moveis_Casa_Bende__produtos_para_casa__11-03-2026_15-18-36__ad1.mp3</t>
         </is>
@@ -1322,27 +1325,27 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="176" t="inlineStr">
+      <c r="A8" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:18:54</t>
         </is>
       </c>
-      <c r="B8" s="176" t="inlineStr">
+      <c r="B8" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C8" s="176" t="inlineStr">
+      <c r="C8" s="192" t="inlineStr">
         <is>
           <t>Projeto Corujas do Bem</t>
         </is>
       </c>
-      <c r="D8" s="176" t="inlineStr">
+      <c r="D8" s="192" t="inlineStr">
         <is>
           <t>Vestidos de noiva</t>
         </is>
       </c>
-      <c r="E8" s="176" t="inlineStr">
+      <c r="E8" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1352,34 +1355,34 @@
           <t>Imagine encontrar um vestido de noiva maravilhoso por apenas 200 reais. Sim, 200 reais. No dia 28 de março, sábado, a partir das 10 horas da manhã, acontece o grande bazar de vestidos de noiva em prol</t>
         </is>
       </c>
-      <c r="G8" s="176" t="inlineStr">
+      <c r="G8" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Projeto_Corujas_do_Bem__Vestidos_de_noiva__11-03-2026_15-18-54.mp3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="176" t="inlineStr">
+      <c r="A9" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:19:12</t>
         </is>
       </c>
-      <c r="B9" s="176" t="inlineStr">
+      <c r="B9" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C9" s="176" t="inlineStr">
+      <c r="C9" s="192" t="inlineStr">
         <is>
           <t>Projeto Corujas do Bem</t>
         </is>
       </c>
-      <c r="D9" s="176" t="inlineStr">
+      <c r="D9" s="192" t="inlineStr">
         <is>
           <t>Vestidos de noiva</t>
         </is>
       </c>
-      <c r="E9" s="176" t="inlineStr">
+      <c r="E9" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1389,34 +1392,34 @@
           <t>em prol do projeto Corujas do Bem. Serão mais de 80 vestidos de noiva. Lindos, esperando você. Rua São Paulo, 1033, sábado, dia 28, a partir das 10 da manhã. Informações WhatsApp 17 92002 5805. Bom di</t>
         </is>
       </c>
-      <c r="G9" s="176" t="inlineStr">
+      <c r="G9" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Projeto_Corujas_do_Bem__Vestidos_de_noiva__11-03-2026_15-19-12.mp3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="176" t="inlineStr">
+      <c r="A10" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:19:29</t>
         </is>
       </c>
-      <c r="B10" s="176" t="inlineStr">
+      <c r="B10" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C10" s="176" t="inlineStr">
+      <c r="C10" s="192" t="inlineStr">
         <is>
           <t>Óticas FabriLem</t>
         </is>
       </c>
-      <c r="D10" s="176" t="inlineStr">
+      <c r="D10" s="192" t="inlineStr">
         <is>
           <t>óculos femininos</t>
         </is>
       </c>
-      <c r="E10" s="176" t="inlineStr">
+      <c r="E10" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1426,34 +1429,34 @@
           <t>zero zero dois cinco oito zero cinco. Bom dia Fih, adoro você. É prêmio em dobro na Band. Gostei. Isso. Março é o mês da mulher, o momento de celebrar sua força, seu estilo e tudo que faz você ser úni</t>
         </is>
       </c>
-      <c r="G10" s="176" t="inlineStr">
+      <c r="G10" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Oticas_FabriLem__oculos_femininos__11-03-2026_15-19-29.mp3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="176" t="inlineStr">
+      <c r="A11" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:20:41</t>
         </is>
       </c>
-      <c r="B11" s="176" t="inlineStr">
+      <c r="B11" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C11" s="176" t="inlineStr">
+      <c r="C11" s="192" t="inlineStr">
         <is>
           <t>Band FM</t>
         </is>
       </c>
-      <c r="D11" s="176" t="inlineStr">
+      <c r="D11" s="192" t="inlineStr">
         <is>
           <t>Mascote da rádio</t>
         </is>
       </c>
-      <c r="E11" s="176" t="inlineStr">
+      <c r="E11" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1463,34 +1466,34 @@
           <t>Minha paixão. Dá uma olhadinha nas redes sociais da Band FM. E aí, você escolhe um nome pra ele. Mas capricha, porque os mais criativos já concorrem ao mascotinho. É, então, eu tô ligadinha na Band. P</t>
         </is>
       </c>
-      <c r="G11" s="176" t="inlineStr">
+      <c r="G11" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Band_FM__Mascote_da_radio__11-03-2026_15-20-41.mp3</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="176" t="inlineStr">
+      <c r="A12" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:20:58</t>
         </is>
       </c>
-      <c r="B12" s="176" t="inlineStr">
+      <c r="B12" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C12" s="176" t="inlineStr">
+      <c r="C12" s="192" t="inlineStr">
         <is>
           <t>Band FM</t>
         </is>
       </c>
-      <c r="D12" s="176" t="inlineStr">
+      <c r="D12" s="192" t="inlineStr">
         <is>
           <t>Rádio</t>
         </is>
       </c>
-      <c r="E12" s="176" t="inlineStr">
+      <c r="E12" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1500,34 +1503,34 @@
           <t>É isso que eu tava pensando. Escolher o nome e ganhar o mascote mais gostosinho do rádio brasileiro. É tudo de bom. É tudo de Band. Band FM. Toca toda. Band FM.</t>
         </is>
       </c>
-      <c r="G12" s="176" t="inlineStr">
+      <c r="G12" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Band_FM__Radio__11-03-2026_15-20-58.mp3</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="176" t="inlineStr">
+      <c r="A13" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:26:44</t>
         </is>
       </c>
-      <c r="B13" s="176" t="inlineStr">
+      <c r="B13" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C13" s="176" t="inlineStr">
+      <c r="C13" s="192" t="inlineStr">
         <is>
           <t>Corpo Atleta</t>
         </is>
       </c>
-      <c r="D13" s="176" t="inlineStr">
+      <c r="D13" s="192" t="inlineStr">
         <is>
           <t>tênis e roupas esportivas</t>
         </is>
       </c>
-      <c r="E13" s="176" t="inlineStr">
+      <c r="E13" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1537,34 +1540,34 @@
           <t>e quatro onze oito dois dois um com um grito mais criativo de Montanha Russa. Será sorteado um ganhador por mês até abril de dois mil e vinte e seis. Se o esporte evolui, seu estilo também precisa evo</t>
         </is>
       </c>
-      <c r="G13" s="176" t="inlineStr">
+      <c r="G13" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Corpo_Atleta__tenis_e_roupas_esportivas__11-03-2026_15-26-44.mp3</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="176" t="inlineStr">
+      <c r="A14" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:27:21</t>
         </is>
       </c>
-      <c r="B14" s="176" t="inlineStr">
+      <c r="B14" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C14" s="176" t="inlineStr">
+      <c r="C14" s="192" t="inlineStr">
         <is>
           <t>Corpo Atleta</t>
         </is>
       </c>
-      <c r="D14" s="176" t="inlineStr">
+      <c r="D14" s="192" t="inlineStr">
         <is>
           <t>produtos esportivos</t>
         </is>
       </c>
-      <c r="E14" s="176" t="inlineStr">
+      <c r="E14" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1574,34 +1577,34 @@
           <t>São as lojas, Corpo Atleta, patrocinadora oficial do seu esporte. Lojas em Catanduva, Rio Preto e Barretos. Corpo Atleta. Medicamento barato de verdade, só na Drogaria Economia. É economia até no nome</t>
         </is>
       </c>
-      <c r="G14" s="176" t="inlineStr">
+      <c r="G14" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Corpo_Atleta__produtos_esportivos__11-03-2026_15-27-21__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="176" t="inlineStr">
+      <c r="A15" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:27:21</t>
         </is>
       </c>
-      <c r="B15" s="176" t="inlineStr">
+      <c r="B15" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C15" s="176" t="inlineStr">
+      <c r="C15" s="192" t="inlineStr">
         <is>
           <t>Drogaria Economia</t>
         </is>
       </c>
-      <c r="D15" s="176" t="inlineStr">
+      <c r="D15" s="192" t="inlineStr">
         <is>
           <t>medicamentos</t>
         </is>
       </c>
-      <c r="E15" s="176" t="inlineStr">
+      <c r="E15" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1611,34 +1614,34 @@
           <t>São as lojas, Corpo Atleta, patrocinadora oficial do seu esporte. Lojas em Catanduva, Rio Preto e Barretos. Corpo Atleta. Medicamento barato de verdade, só na Drogaria Economia. É economia até no nome</t>
         </is>
       </c>
-      <c r="G15" s="176" t="inlineStr">
+      <c r="G15" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Drogaria_Economia__medicamentos__11-03-2026_15-27-21__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="176" t="inlineStr">
+      <c r="A16" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:29:11</t>
         </is>
       </c>
-      <c r="B16" s="176" t="inlineStr">
+      <c r="B16" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C16" s="176" t="inlineStr">
+      <c r="C16" s="192" t="inlineStr">
         <is>
           <t>Antunes Mais</t>
         </is>
       </c>
-      <c r="D16" s="176" t="inlineStr">
+      <c r="D16" s="192" t="inlineStr">
         <is>
           <t>pescados e peixe</t>
         </is>
       </c>
-      <c r="E16" s="176" t="inlineStr">
+      <c r="E16" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1648,34 +1651,34 @@
           <t>E Fiquilo, quarenta e quatro e oitenta e cinco. Essas ofertas são válidas somente hoje em toda a rede Antunes Mais. E tá rolando o festival do peixe e pescados no Antunes Mais. São produtos selecionad</t>
         </is>
       </c>
-      <c r="G16" s="176" t="inlineStr">
+      <c r="G16" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Antunes_Mais__pescados_e_peixe__11-03-2026_15-29-11__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="176" t="inlineStr">
+      <c r="A17" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:29:11</t>
         </is>
       </c>
-      <c r="B17" s="176" t="inlineStr">
+      <c r="B17" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C17" s="176" t="inlineStr">
+      <c r="C17" s="192" t="inlineStr">
         <is>
           <t>Unifipa Catanduva</t>
         </is>
       </c>
-      <c r="D17" s="176" t="inlineStr">
+      <c r="D17" s="192" t="inlineStr">
         <is>
           <t>educação</t>
         </is>
       </c>
-      <c r="E17" s="176" t="inlineStr">
+      <c r="E17" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1685,34 +1688,34 @@
           <t>E Fiquilo, quarenta e quatro e oitenta e cinco. Essas ofertas são válidas somente hoje em toda a rede Antunes Mais. E tá rolando o festival do peixe e pescados no Antunes Mais. São produtos selecionad</t>
         </is>
       </c>
-      <c r="G17" s="176" t="inlineStr">
+      <c r="G17" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Unifipa_Catanduva__educacao__11-03-2026_15-29-11__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="176" t="inlineStr">
+      <c r="A18" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:29:28</t>
         </is>
       </c>
-      <c r="B18" s="176" t="inlineStr">
+      <c r="B18" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C18" s="176" t="inlineStr">
+      <c r="C18" s="192" t="inlineStr">
         <is>
           <t>Unifipa Catanduva</t>
         </is>
       </c>
-      <c r="D18" s="176" t="inlineStr">
+      <c r="D18" s="192" t="inlineStr">
         <is>
           <t>Cursos de graduação</t>
         </is>
       </c>
-      <c r="E18" s="176" t="inlineStr">
+      <c r="E18" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1722,34 +1725,34 @@
           <t>Música, notícia. Na Unifipa Catanduva, nossa missão é formar para crescer e ensinar para ser grande. Acreditamos que o verdadeiro crescimento começa com formação sólida, humana e conectada ao mundo re</t>
         </is>
       </c>
-      <c r="G18" s="176" t="inlineStr">
+      <c r="G18" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Unifipa_Catanduva__Cursos_de_graduacao__11-03-2026_15-29-28.mp3</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="176" t="inlineStr">
+      <c r="A19" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:30:03</t>
         </is>
       </c>
-      <c r="B19" s="176" t="inlineStr">
+      <c r="B19" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C19" s="176" t="inlineStr">
+      <c r="C19" s="192" t="inlineStr">
         <is>
           <t>Lela Modas</t>
         </is>
       </c>
-      <c r="D19" s="176" t="inlineStr">
+      <c r="D19" s="192" t="inlineStr">
         <is>
           <t>looks (roupas)</t>
         </is>
       </c>
-      <c r="E19" s="176" t="inlineStr">
+      <c r="E19" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1759,34 +1762,34 @@
           <t>Neste mês da comemoração internacional da mulher, a Lela Modas homenageia todas que inspiram, lideram e transformam o mundo todos os dias. E para celebrar essa data especial, tem descontos especiais e</t>
         </is>
       </c>
-      <c r="G19" s="176" t="inlineStr">
+      <c r="G19" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Lela_Modas__looks__roupas__11-03-2026_15-30-03.mp3</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="176" t="inlineStr">
+      <c r="A20" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:30:07</t>
         </is>
       </c>
-      <c r="B20" s="176" t="inlineStr">
+      <c r="B20" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C20" s="176" t="inlineStr">
+      <c r="C20" s="192" t="inlineStr">
         <is>
           <t>Enoi Kegami Supermercados</t>
         </is>
       </c>
-      <c r="D20" s="176" t="inlineStr">
+      <c r="D20" s="192" t="inlineStr">
         <is>
           <t>Açúcar Cristal Colombo e outros produtos</t>
         </is>
       </c>
-      <c r="E20" s="176" t="inlineStr">
+      <c r="E20" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1796,34 +1799,34 @@
           <t xml:space="preserve">da terceira idade, da melhor idade de Embaúba, um abraço e um beijo em todos vocês, eu volto já já, não sai daí. Todo mundo, numa só estação, Ondas Verdes FM. Ondas Verdes FM. Ondas Verdes. Mastro da </t>
         </is>
       </c>
-      <c r="G20" s="176" t="inlineStr">
+      <c r="G20" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Enoi_Kegami_Supermercados__Acucar_Cristal_Colombo_e_outros_produtos__11-03-2026_15-30-07.mp3</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="176" t="inlineStr">
+      <c r="A21" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:30:20</t>
         </is>
       </c>
-      <c r="B21" s="176" t="inlineStr">
+      <c r="B21" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C21" s="176" t="inlineStr">
+      <c r="C21" s="192" t="inlineStr">
         <is>
           <t>Lela Modas</t>
         </is>
       </c>
-      <c r="D21" s="176" t="inlineStr">
+      <c r="D21" s="192" t="inlineStr">
         <is>
           <t>Modas</t>
         </is>
       </c>
-      <c r="E21" s="176" t="inlineStr">
+      <c r="E21" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1833,34 +1836,34 @@
           <t xml:space="preserve">Lela Modas, Rua Minas Gerais 382 e 390. Você faz da moda, Lela Modas. Arthur. Presente. Ok. Bianca. Presente. Tá. Bruno. Presente. O Pé de Meia tá completando dois anos e já dá pra ver os resultados. </t>
         </is>
       </c>
-      <c r="G21" s="176" t="inlineStr">
+      <c r="G21" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Lela_Modas__Modas__11-03-2026_15-30-20.mp3</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="176" t="inlineStr">
+      <c r="A22" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:30:39</t>
         </is>
       </c>
-      <c r="B22" s="176" t="inlineStr">
+      <c r="B22" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C22" s="176" t="inlineStr">
+      <c r="C22" s="192" t="inlineStr">
         <is>
           <t>Pan</t>
         </is>
       </c>
-      <c r="D22" s="176" t="inlineStr">
+      <c r="D22" s="192" t="inlineStr">
         <is>
           <t>Páscoa</t>
         </is>
       </c>
-      <c r="E22" s="176" t="inlineStr">
+      <c r="E22" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1870,34 +1873,34 @@
           <t>Estudantes abandonando os estudos. É cada vez mais estudantes ganhando até nove mil e duzentos reais pra concluírem o ensino médio. Já são mais de seis milhões de beneficiados. E esse número vai ser a</t>
         </is>
       </c>
-      <c r="G22" s="176" t="inlineStr">
+      <c r="G22" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Pan__Pascoa__11-03-2026_15-30-39__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="176" t="inlineStr">
+      <c r="A23" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:30:39</t>
         </is>
       </c>
-      <c r="B23" s="176" t="inlineStr">
+      <c r="B23" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C23" s="176" t="inlineStr">
+      <c r="C23" s="192" t="inlineStr">
         <is>
           <t>Cacau Show Catanduva</t>
         </is>
       </c>
-      <c r="D23" s="176" t="inlineStr">
+      <c r="D23" s="192" t="inlineStr">
         <is>
           <t>Chocolate</t>
         </is>
       </c>
-      <c r="E23" s="176" t="inlineStr">
+      <c r="E23" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1907,34 +1910,34 @@
           <t>Estudantes abandonando os estudos. É cada vez mais estudantes ganhando até nove mil e duzentos reais pra concluírem o ensino médio. Já são mais de seis milhões de beneficiados. E esse número vai ser a</t>
         </is>
       </c>
-      <c r="G23" s="176" t="inlineStr">
+      <c r="G23" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show_Catanduva__Chocolate__11-03-2026_15-30-39__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="176" t="inlineStr">
+      <c r="A24" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:30:41</t>
         </is>
       </c>
-      <c r="B24" s="176" t="inlineStr">
+      <c r="B24" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C24" s="176" t="inlineStr">
+      <c r="C24" s="192" t="inlineStr">
         <is>
           <t>Ikegami Supermercados</t>
         </is>
       </c>
-      <c r="D24" s="176" t="inlineStr">
+      <c r="D24" s="192" t="inlineStr">
         <is>
           <t>produtos em geral (paleta poruruca e melancia)</t>
         </is>
       </c>
-      <c r="E24" s="176" t="inlineStr">
+      <c r="E24" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1944,34 +1947,34 @@
           <t>Tequinha da paleta poruruca no clube do japonezinho, dez e quarenta. E melancia quilo, um e oitenta e nove no clube do japonezinho. Quarta da economia, é no Ikegami Supermercados. Quando o assunto é v</t>
         </is>
       </c>
-      <c r="G24" s="176" t="inlineStr">
+      <c r="G24" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Ikegami_Supermercados__produtos_em_geral__paleta_poruruca_e_melancia__11-03-2026_15-30-41__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="176" t="inlineStr">
+      <c r="A25" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:30:41</t>
         </is>
       </c>
-      <c r="B25" s="176" t="inlineStr">
+      <c r="B25" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C25" s="176" t="inlineStr">
+      <c r="C25" s="192" t="inlineStr">
         <is>
           <t>Ótica Fabrileia</t>
         </is>
       </c>
-      <c r="D25" s="176" t="inlineStr">
+      <c r="D25" s="192" t="inlineStr">
         <is>
           <t>lentes e serviços de ótica</t>
         </is>
       </c>
-      <c r="E25" s="176" t="inlineStr">
+      <c r="E25" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -1981,34 +1984,34 @@
           <t>Tequinha da paleta poruruca no clube do japonezinho, dez e quarenta. E melancia quilo, um e oitenta e nove no clube do japonezinho. Quarta da economia, é no Ikegami Supermercados. Quando o assunto é v</t>
         </is>
       </c>
-      <c r="G25" s="176" t="inlineStr">
+      <c r="G25" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Otica_Fabrileia__lentes_e_servicos_de_otica__11-03-2026_15-30-41__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="176" t="inlineStr">
+      <c r="A26" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:30:57</t>
         </is>
       </c>
-      <c r="B26" s="176" t="inlineStr">
+      <c r="B26" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C26" s="176" t="inlineStr">
+      <c r="C26" s="192" t="inlineStr">
         <is>
           <t>Ótica Fabrileia Referência</t>
         </is>
       </c>
-      <c r="D26" s="176" t="inlineStr">
+      <c r="D26" s="192" t="inlineStr">
         <is>
           <t>lentes multifocais digitais Noblen</t>
         </is>
       </c>
-      <c r="E26" s="176" t="inlineStr">
+      <c r="E26" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2018,34 +2021,34 @@
           <t>Ótica Fabrileia Referência, atendimento diferenciado com profissionais preparados para orientar você com atenção e confiança. As lentes são produzidas com alta tecnologia, garantindo precisão e confor</t>
         </is>
       </c>
-      <c r="G26" s="176" t="inlineStr">
+      <c r="G26" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Otica_Fabrileia_Referencia__lentes_multifocais_digitais_Noblen__11-03-2026_15-30-57.mp3</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="176" t="inlineStr">
+      <c r="A27" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:31:14</t>
         </is>
       </c>
-      <c r="B27" s="176" t="inlineStr">
+      <c r="B27" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C27" s="176" t="inlineStr">
+      <c r="C27" s="192" t="inlineStr">
         <is>
           <t>Óticas FabriLem</t>
         </is>
       </c>
-      <c r="D27" s="176" t="inlineStr">
+      <c r="D27" s="192" t="inlineStr">
         <is>
           <t>lentes multifocais digitais Noblin e lentes de visão simples</t>
         </is>
       </c>
-      <c r="E27" s="176" t="inlineStr">
+      <c r="E27" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2055,34 +2058,34 @@
           <t xml:space="preserve">dia e tem promoção especial. Na compra do primeiro par de lentes multifocais digitais Noblin com antirreflexo, o segundo par é grátis. E mais, lentes de visão simples com antirreflexo e filtro de luz </t>
         </is>
       </c>
-      <c r="G27" s="176" t="inlineStr">
+      <c r="G27" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Oticas_FabriLem__lentes_multifocais_digitais_Noblin_e_lentes_de_visao_simples__11-03-2026_15-31-14.mp3</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="176" t="inlineStr">
+      <c r="A28" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:31:16</t>
         </is>
       </c>
-      <c r="B28" s="176" t="inlineStr">
+      <c r="B28" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C28" s="176" t="inlineStr">
+      <c r="C28" s="192" t="inlineStr">
         <is>
           <t>Cacau Show</t>
         </is>
       </c>
-      <c r="D28" s="176" t="inlineStr">
+      <c r="D28" s="192" t="inlineStr">
         <is>
           <t>Gigante de dois quilos de chocolate</t>
         </is>
       </c>
-      <c r="E28" s="176" t="inlineStr">
+      <c r="E28" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2092,7 +2095,7 @@
           <t>Gigante de dois quilos da Cacau Show. Quer ganhar? Siga arroba Jovem Pan Catanduva e arroba loja Cacau Show Catanduva no Insta e comente eu quero no post oficial. Páscoa com muito chocolate. É na núme</t>
         </is>
       </c>
-      <c r="G28" s="176" t="inlineStr">
+      <c r="G28" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Cacau_Show__Gigante_de_dois_quilos_de_chocolate__11-03-2026_15-31-16.mp3</t>
         </is>
@@ -2136,27 +2139,27 @@
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="176" t="inlineStr">
+      <c r="A30" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:31:47</t>
         </is>
       </c>
-      <c r="B30" s="176" t="inlineStr">
+      <c r="B30" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C30" s="176" t="inlineStr">
+      <c r="C30" s="192" t="inlineStr">
         <is>
           <t>Volkswagen e Faria Veículos</t>
         </is>
       </c>
-      <c r="D30" s="176" t="inlineStr">
+      <c r="D30" s="192" t="inlineStr">
         <is>
           <t>Veículos zero quilômetro (The Cross duzentos, TSI e Nivus Highline)</t>
         </is>
       </c>
-      <c r="E30" s="176" t="inlineStr">
+      <c r="E30" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2166,7 +2169,7 @@
           <t>Zero quilômetro, descontos e taxas incríveis. The Cross duzentos, TSI e Nivus Highline, com descontos de até vinte e cinco mil reais com seu usado na troca. E ainda taxa zero, entrada e saldo em até t</t>
         </is>
       </c>
-      <c r="G30" s="176" t="inlineStr">
+      <c r="G30" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Volkswagen_e_Faria_Veiculos__Veiculos_zero_quilometro__The_Cross_duzentos__TSI_e_Nivus_Hi__11-03-2026_15-31-47__ad1.mp3</t>
         </is>
@@ -2210,27 +2213,27 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="176" t="inlineStr">
+      <c r="A32" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:32:03</t>
         </is>
       </c>
-      <c r="B32" s="176" t="inlineStr">
+      <c r="B32" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C32" s="176" t="inlineStr">
+      <c r="C32" s="192" t="inlineStr">
         <is>
           <t>Veículos Catanduva</t>
         </is>
       </c>
-      <c r="D32" s="176" t="inlineStr">
+      <c r="D32" s="192" t="inlineStr">
         <is>
           <t>veículos</t>
         </is>
       </c>
-      <c r="E32" s="176" t="inlineStr">
+      <c r="E32" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2240,34 +2243,34 @@
           <t>E a Veículos Catanduva, sua melhor escolha. Forksat. Desacelere, seu bem maior é a vida. Amaral Centro Automotivo Multimarcas agradece a todos o carinho e a confiança no trabalho realizado com sua equ</t>
         </is>
       </c>
-      <c r="G32" s="176" t="inlineStr">
+      <c r="G32" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Veiculos_Catanduva__veiculos__11-03-2026_15-32-03__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="176" t="inlineStr">
+      <c r="A33" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:32:03</t>
         </is>
       </c>
-      <c r="B33" s="176" t="inlineStr">
+      <c r="B33" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C33" s="176" t="inlineStr">
+      <c r="C33" s="192" t="inlineStr">
         <is>
           <t>Amaral Centro Automotivo Multimarcas</t>
         </is>
       </c>
-      <c r="D33" s="176" t="inlineStr">
+      <c r="D33" s="192" t="inlineStr">
         <is>
           <t>serviços automotivos</t>
         </is>
       </c>
-      <c r="E33" s="176" t="inlineStr">
+      <c r="E33" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2277,34 +2280,34 @@
           <t>E a Veículos Catanduva, sua melhor escolha. Forksat. Desacelere, seu bem maior é a vida. Amaral Centro Automotivo Multimarcas agradece a todos o carinho e a confiança no trabalho realizado com sua equ</t>
         </is>
       </c>
-      <c r="G33" s="176" t="inlineStr">
+      <c r="G33" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Amaral_Centro_Automotivo_Multimarcas__servicos_automotivos__11-03-2026_15-32-03__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="176" t="inlineStr">
+      <c r="A34" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:32:36</t>
         </is>
       </c>
-      <c r="B34" s="176" t="inlineStr">
+      <c r="B34" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C34" s="176" t="inlineStr">
+      <c r="C34" s="192" t="inlineStr">
         <is>
           <t>Nagatela</t>
         </is>
       </c>
-      <c r="D34" s="176" t="inlineStr">
+      <c r="D34" s="192" t="inlineStr">
         <is>
           <t>Poupança Premiada</t>
         </is>
       </c>
-      <c r="E34" s="176" t="inlineStr">
+      <c r="E34" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2314,34 +2317,34 @@
           <t>de seguradoras, bateu, amassou, amarao, consertou, Rua Martinópolis, oitocentos e oitenta e seis, o telefone, três zero, quatro cinco, nove um, três sete. Aqui é a Nagatela, é hora de sonhar alto, a p</t>
         </is>
       </c>
-      <c r="G34" s="176" t="inlineStr">
+      <c r="G34" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Nagatela__Poupanca_Premiada__11-03-2026_15-32-36.mp3</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="176" t="inlineStr">
+      <c r="A35" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:32:53</t>
         </is>
       </c>
-      <c r="B35" s="176" t="inlineStr">
+      <c r="B35" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C35" s="176" t="inlineStr">
+      <c r="C35" s="192" t="inlineStr">
         <is>
           <t>Grupo Moreschi</t>
         </is>
       </c>
-      <c r="D35" s="176" t="inlineStr">
+      <c r="D35" s="192" t="inlineStr">
         <is>
           <t>ofertas</t>
         </is>
       </c>
-      <c r="E35" s="176" t="inlineStr">
+      <c r="E35" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2351,34 +2354,34 @@
           <t>Tá aí! Se crede, Poucos é premiada Pra fazer tudo o que você sonhava Tem milhões em prêmios toda semana São mais de 600 ganhadores 5 milhões em prêmios em dinheiro Poupinou-se, crede? E concorra! Pouc</t>
         </is>
       </c>
-      <c r="G35" s="176" t="inlineStr">
+      <c r="G35" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Grupo_Moreschi__ofertas__11-03-2026_15-32-53__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="176" t="inlineStr">
+      <c r="A36" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:32:53</t>
         </is>
       </c>
-      <c r="B36" s="176" t="inlineStr">
+      <c r="B36" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C36" s="176" t="inlineStr">
+      <c r="C36" s="192" t="inlineStr">
         <is>
           <t>Poupinou-se</t>
         </is>
       </c>
-      <c r="D36" s="176" t="inlineStr">
+      <c r="D36" s="192" t="inlineStr">
         <is>
           <t>prêmios</t>
         </is>
       </c>
-      <c r="E36" s="176" t="inlineStr">
+      <c r="E36" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2388,34 +2391,34 @@
           <t>Tá aí! Se crede, Poucos é premiada Pra fazer tudo o que você sonhava Tem milhões em prêmios toda semana São mais de 600 ganhadores 5 milhões em prêmios em dinheiro Poupinou-se, crede? E concorra! Pouc</t>
         </is>
       </c>
-      <c r="G36" s="176" t="inlineStr">
+      <c r="G36" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Poupinou-se__premios__11-03-2026_15-32-53__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="176" t="inlineStr">
+      <c r="A37" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:33:09</t>
         </is>
       </c>
-      <c r="B37" s="176" t="inlineStr">
+      <c r="B37" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C37" s="176" t="inlineStr">
+      <c r="C37" s="192" t="inlineStr">
         <is>
           <t>Grupo Moreschi</t>
         </is>
       </c>
-      <c r="D37" s="176" t="inlineStr">
+      <c r="D37" s="192" t="inlineStr">
         <is>
           <t>Bisteca suína e Costela bovina</t>
         </is>
       </c>
-      <c r="E37" s="176" t="inlineStr">
+      <c r="E37" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2425,7 +2428,7 @@
           <t>O plantão de ofertas do Grupo Moreschi informa. Pra você ligado na Rádio Ondas Verdes no ar, mais um plantão de ofertas do Grupo Moreschi. Escuta só, valores por quilo no açougue. Bisteca suína, quato</t>
         </is>
       </c>
-      <c r="G37" s="176" t="inlineStr">
+      <c r="G37" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Grupo_Moreschi__Bisteca_suina_e_Costela_bovina__11-03-2026_15-33-09.mp3</t>
         </is>
@@ -2469,27 +2472,27 @@
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="176" t="inlineStr">
+      <c r="A39" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:34:32</t>
         </is>
       </c>
-      <c r="B39" s="176" t="inlineStr">
+      <c r="B39" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C39" s="176" t="inlineStr">
+      <c r="C39" s="192" t="inlineStr">
         <is>
           <t>Grupo Moreschi</t>
         </is>
       </c>
-      <c r="D39" s="176" t="inlineStr">
+      <c r="D39" s="192" t="inlineStr">
         <is>
           <t>Refrigerante Pique-Nique, Sabonete Francis</t>
         </is>
       </c>
-      <c r="E39" s="176" t="inlineStr">
+      <c r="E39" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2499,34 +2502,34 @@
           <t xml:space="preserve">30 metros com 4 rolos, R$ 3,99. Refrigerante Pique-Nique, pet 2 litros, vários sabores, R$ 3,99 também. Sabonete Francis, 85 gramas, várias fragrâncias, R$ 1,99. Ofertas válidas até este dia 12. Você </t>
         </is>
       </c>
-      <c r="G39" s="176" t="inlineStr">
+      <c r="G39" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Grupo_Moreschi__Refrigerante_Pique-Nique__Sabonete_Francis__11-03-2026_15-34-32.mp3</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="176" t="inlineStr">
+      <c r="A40" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:36:05</t>
         </is>
       </c>
-      <c r="B40" s="176" t="inlineStr">
+      <c r="B40" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C40" s="176" t="inlineStr">
+      <c r="C40" s="192" t="inlineStr">
         <is>
           <t>Lela Modas</t>
         </is>
       </c>
-      <c r="D40" s="176" t="inlineStr">
+      <c r="D40" s="192" t="inlineStr">
         <is>
           <t>Roupas ou serviços de moda</t>
         </is>
       </c>
-      <c r="E40" s="176" t="inlineStr">
+      <c r="E40" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2536,34 +2539,34 @@
           <t>Trinta e cinco, ótima tarde pra você ligado na Band, na volta do intervalo tem muito mais. Não saia daí, já já tem muito mais músicas aqui na Band FM. Band FM Lela Modas, trinta e cinco anos celebrand</t>
         </is>
       </c>
-      <c r="G40" s="176" t="inlineStr">
+      <c r="G40" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Lela_Modas__Roupas_ou_servicos_de_moda__11-03-2026_15-36-05.mp3</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="176" t="inlineStr">
+      <c r="A41" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:36:23</t>
         </is>
       </c>
-      <c r="B41" s="176" t="inlineStr">
+      <c r="B41" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C41" s="176" t="inlineStr">
+      <c r="C41" s="192" t="inlineStr">
         <is>
           <t>Lela Modas</t>
         </is>
       </c>
-      <c r="D41" s="176" t="inlineStr">
+      <c r="D41" s="192" t="inlineStr">
         <is>
           <t>Roupas femininas</t>
         </is>
       </c>
-      <c r="E41" s="176" t="inlineStr">
+      <c r="E41" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2573,34 +2576,34 @@
           <t xml:space="preserve">No mês da comemoração internacional da mulher, a Lela Modas homenageia todas as mulheres que inspiram, lideram e transformam. Parabéns a você mulher, parabéns a todas as mulheres. Descontos especiais </t>
         </is>
       </c>
-      <c r="G41" s="176" t="inlineStr">
+      <c r="G41" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Lela_Modas__Roupas_femininas__11-03-2026_15-36-23.mp3</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="176" t="inlineStr">
+      <c r="A42" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:36:41</t>
         </is>
       </c>
-      <c r="B42" s="176" t="inlineStr">
+      <c r="B42" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C42" s="176" t="inlineStr">
+      <c r="C42" s="192" t="inlineStr">
         <is>
           <t>Lela Modas</t>
         </is>
       </c>
-      <c r="D42" s="176" t="inlineStr">
+      <c r="D42" s="192" t="inlineStr">
         <is>
           <t>Vestuário</t>
         </is>
       </c>
-      <c r="E42" s="176" t="inlineStr">
+      <c r="E42" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2610,34 +2613,34 @@
           <t>Lela Modas, vestindo mulheres com estilo e paixão. Minas Gerais, 382 e 390. Você faz a moda, Lela Moda. Chegou a hora de você fazer seu futuro acontecer. Participe do vestibular continuado 2026 da Uni</t>
         </is>
       </c>
-      <c r="G42" s="176" t="inlineStr">
+      <c r="G42" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Lela_Modas__Vestuario__11-03-2026_15-36-41__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="176" t="inlineStr">
+      <c r="A43" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:36:41</t>
         </is>
       </c>
-      <c r="B43" s="176" t="inlineStr">
+      <c r="B43" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C43" s="176" t="inlineStr">
+      <c r="C43" s="192" t="inlineStr">
         <is>
           <t>Unifipa Catanduva</t>
         </is>
       </c>
-      <c r="D43" s="176" t="inlineStr">
+      <c r="D43" s="192" t="inlineStr">
         <is>
           <t>Cursos de graduação</t>
         </is>
       </c>
-      <c r="E43" s="176" t="inlineStr">
+      <c r="E43" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2647,34 +2650,34 @@
           <t>Lela Modas, vestindo mulheres com estilo e paixão. Minas Gerais, 382 e 390. Você faz a moda, Lela Moda. Chegou a hora de você fazer seu futuro acontecer. Participe do vestibular continuado 2026 da Uni</t>
         </is>
       </c>
-      <c r="G43" s="176" t="inlineStr">
+      <c r="G43" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Unifipa_Catanduva__Cursos_de_graduacao__11-03-2026_15-36-41__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="176" t="inlineStr">
+      <c r="A44" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:36:58</t>
         </is>
       </c>
-      <c r="B44" s="176" t="inlineStr">
+      <c r="B44" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C44" s="176" t="inlineStr">
+      <c r="C44" s="192" t="inlineStr">
         <is>
           <t>Unifipa</t>
         </is>
       </c>
-      <c r="D44" s="176" t="inlineStr">
+      <c r="D44" s="192" t="inlineStr">
         <is>
           <t>Cursos de graduação</t>
         </is>
       </c>
-      <c r="E44" s="176" t="inlineStr">
+      <c r="E44" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2684,34 +2687,34 @@
           <t>Opções de cursos de graduação na instituição que tem mais de 55 anos de tradição e é sinônimo de excelência em ensino, com nota máxima na avaliação do MEC. Venha ser Unifipa. Inscrições e provas onlin</t>
         </is>
       </c>
-      <c r="G44" s="176" t="inlineStr">
+      <c r="G44" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Unifipa__Cursos_de_graduacao__11-03-2026_15-36-58.mp3</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="176" t="inlineStr">
+      <c r="A45" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:37:17</t>
         </is>
       </c>
-      <c r="B45" s="176" t="inlineStr">
+      <c r="B45" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C45" s="176" t="inlineStr">
+      <c r="C45" s="192" t="inlineStr">
         <is>
           <t>Padre Albino Saúde</t>
         </is>
       </c>
-      <c r="D45" s="176" t="inlineStr">
+      <c r="D45" s="192" t="inlineStr">
         <is>
           <t>serviços de saúde</t>
         </is>
       </c>
-      <c r="E45" s="176" t="inlineStr">
+      <c r="E45" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2721,34 +2724,34 @@
           <t>que transforma vidas. Aqui é o Marcos. E aqui é o Beluti. A Band FM toca tudo que tá na boca da galera. Nossa, a música na Band FM fica bem melhor. Você busca sempre o melhor para o futuro da sua famí</t>
         </is>
       </c>
-      <c r="G45" s="176" t="inlineStr">
+      <c r="G45" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Padre_Albino_Saude__servicos_de_saude__11-03-2026_15-37-17.mp3</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="176" t="inlineStr">
+      <c r="A46" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:38:10</t>
         </is>
       </c>
-      <c r="B46" s="176" t="inlineStr">
+      <c r="B46" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C46" s="176" t="inlineStr">
+      <c r="C46" s="192" t="inlineStr">
         <is>
           <t>Óticas FabriLem</t>
         </is>
       </c>
-      <c r="D46" s="176" t="inlineStr">
+      <c r="D46" s="192" t="inlineStr">
         <is>
           <t>óculos de som femininos e lentes de fabricação própria</t>
         </is>
       </c>
-      <c r="E46" s="176" t="inlineStr">
+      <c r="E46" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2758,7 +2761,7 @@
           <t xml:space="preserve">Modelos elegantes, modernos e cheio de estilo. E tem presente especial. Durante todo o mês de março, óculos de som femininos com 20% de desconto. Consulte armações na loja. Aproveite também lentes de </t>
         </is>
       </c>
-      <c r="G46" s="176" t="inlineStr">
+      <c r="G46" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Oticas_FabriLem__oculos_de_som_femininos_e_lentes_de_fabricacao_propria__11-03-2026_15-38-10__ad1.mp3</t>
         </is>
@@ -2802,27 +2805,27 @@
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="176" t="inlineStr">
+      <c r="A48" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:38:28</t>
         </is>
       </c>
-      <c r="B48" s="176" t="inlineStr">
+      <c r="B48" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C48" s="176" t="inlineStr">
+      <c r="C48" s="192" t="inlineStr">
         <is>
           <t>Ikegami Supermercados</t>
         </is>
       </c>
-      <c r="D48" s="176" t="inlineStr">
+      <c r="D48" s="192" t="inlineStr">
         <is>
           <t>Produtos em geral</t>
         </is>
       </c>
-      <c r="E48" s="176" t="inlineStr">
+      <c r="E48" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2832,34 +2835,34 @@
           <t>Beleza, cuidando da sua visão. Rua Brasil, esquina com a Cuiabá. Macho imbatível! É no Ikegami Supermercados, confira! Açúcar Cristal Colombo, 5 quilos, 10,95 no Clube do Japoneizinho. Perdi o suíno p</t>
         </is>
       </c>
-      <c r="G48" s="176" t="inlineStr">
+      <c r="G48" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Ikegami_Supermercados__Produtos_em_geral__11-03-2026_15-38-28__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="176" t="inlineStr">
+      <c r="A49" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:38:28</t>
         </is>
       </c>
-      <c r="B49" s="176" t="inlineStr">
+      <c r="B49" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C49" s="176" t="inlineStr">
+      <c r="C49" s="192" t="inlineStr">
         <is>
           <t>Clube do Japoneizinho</t>
         </is>
       </c>
-      <c r="D49" s="176" t="inlineStr">
+      <c r="D49" s="192" t="inlineStr">
         <is>
           <t>Produtos em geral</t>
         </is>
       </c>
-      <c r="E49" s="176" t="inlineStr">
+      <c r="E49" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2869,34 +2872,34 @@
           <t>Beleza, cuidando da sua visão. Rua Brasil, esquina com a Cuiabá. Macho imbatível! É no Ikegami Supermercados, confira! Açúcar Cristal Colombo, 5 quilos, 10,95 no Clube do Japoneizinho. Perdi o suíno p</t>
         </is>
       </c>
-      <c r="G49" s="176" t="inlineStr">
+      <c r="G49" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Clube_do_Japoneizinho__Produtos_em_geral__11-03-2026_15-38-28__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="176" t="inlineStr">
+      <c r="A50" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:38:46</t>
         </is>
       </c>
-      <c r="B50" s="176" t="inlineStr">
+      <c r="B50" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C50" s="176" t="inlineStr">
+      <c r="C50" s="192" t="inlineStr">
         <is>
           <t>Clube do Japonezinho</t>
         </is>
       </c>
-      <c r="D50" s="176" t="inlineStr">
+      <c r="D50" s="192" t="inlineStr">
         <is>
           <t>Produtos alimentícios (costela, filé de tilapia, melancia)</t>
         </is>
       </c>
-      <c r="E50" s="176" t="inlineStr">
+      <c r="E50" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2906,34 +2909,34 @@
           <t>no Clube do Japonezinho. Costela, bovina, ripa, balcão, quilo, dezenove e oitenta no Clube do Japonezinho. Filé de tilapia, água viva, quinhentos gramas, vinte e quatro e noventa no Clube do Japonezin</t>
         </is>
       </c>
-      <c r="G50" s="176" t="inlineStr">
+      <c r="G50" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Clube_do_Japonezinho__Produtos_alimenticios__costela__file_de_tilapia__melancia__11-03-2026_15-38-46__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="176" t="inlineStr">
+      <c r="A51" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:38:46</t>
         </is>
       </c>
-      <c r="B51" s="176" t="inlineStr">
+      <c r="B51" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C51" s="176" t="inlineStr">
+      <c r="C51" s="192" t="inlineStr">
         <is>
           <t>Ikegami Supermercados</t>
         </is>
       </c>
-      <c r="D51" s="176" t="inlineStr">
+      <c r="D51" s="192" t="inlineStr">
         <is>
           <t>Produtos em geral</t>
         </is>
       </c>
-      <c r="E51" s="176" t="inlineStr">
+      <c r="E51" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2943,34 +2946,34 @@
           <t>no Clube do Japonezinho. Costela, bovina, ripa, balcão, quilo, dezenove e oitenta no Clube do Japonezinho. Filé de tilapia, água viva, quinhentos gramas, vinte e quatro e noventa no Clube do Japonezin</t>
         </is>
       </c>
-      <c r="G51" s="176" t="inlineStr">
+      <c r="G51" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Ikegami_Supermercados__Produtos_em_geral__11-03-2026_15-38-46__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="176" t="inlineStr">
+      <c r="A52" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:38:46</t>
         </is>
       </c>
-      <c r="B52" s="176" t="inlineStr">
+      <c r="B52" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C52" s="176" t="inlineStr">
+      <c r="C52" s="192" t="inlineStr">
         <is>
           <t>Rede Móveis Casa Verde</t>
         </is>
       </c>
-      <c r="D52" s="176" t="inlineStr">
+      <c r="D52" s="192" t="inlineStr">
         <is>
           <t>Serviços de telefonia</t>
         </is>
       </c>
-      <c r="E52" s="176" t="inlineStr">
+      <c r="E52" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -2980,34 +2983,34 @@
           <t>no Clube do Japonezinho. Costela, bovina, ripa, balcão, quilo, dezenove e oitenta no Clube do Japonezinho. Filé de tilapia, água viva, quinhentos gramas, vinte e quatro e noventa no Clube do Japonezin</t>
         </is>
       </c>
-      <c r="G52" s="176" t="inlineStr">
+      <c r="G52" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Rede_Moveis_Casa_Verde__Servicos_de_telefonia__11-03-2026_15-38-46__ad3.mp3</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="176" t="inlineStr">
+      <c r="A53" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:39:03</t>
         </is>
       </c>
-      <c r="B53" s="176" t="inlineStr">
+      <c r="B53" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C53" s="176" t="inlineStr">
+      <c r="C53" s="192" t="inlineStr">
         <is>
           <t>Rede Móveis Casa Vende</t>
         </is>
       </c>
-      <c r="D53" s="176" t="inlineStr">
+      <c r="D53" s="192" t="inlineStr">
         <is>
           <t>Produtos para renovar a casa</t>
         </is>
       </c>
-      <c r="E53" s="176" t="inlineStr">
+      <c r="E53" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3017,34 +3020,34 @@
           <t xml:space="preserve">em supermercados. Atenção, Catanduba e região, é aniversário da Rede Móveis Casa Vende, com ofertas especiais para renovar a sua casa. Produtos selecionados e pagamento facilitado em até quinze vezes </t>
         </is>
       </c>
-      <c r="G53" s="176" t="inlineStr">
+      <c r="G53" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Rede_Moveis_Casa_Vende__Produtos_para_renovar_a_casa__11-03-2026_15-39-03.mp3</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="176" t="inlineStr">
+      <c r="A54" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:40:50</t>
         </is>
       </c>
-      <c r="B54" s="176" t="inlineStr">
+      <c r="B54" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C54" s="176" t="inlineStr">
+      <c r="C54" s="192" t="inlineStr">
         <is>
           <t>Dicopel</t>
         </is>
       </c>
-      <c r="D54" s="176" t="inlineStr">
+      <c r="D54" s="192" t="inlineStr">
         <is>
           <t>produtos para Páscoa (ovos, bombons, embalagens, etc.)</t>
         </is>
       </c>
-      <c r="E54" s="176" t="inlineStr">
+      <c r="E54" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3054,34 +3057,34 @@
           <t xml:space="preserve">Chega! 3, 5, 2, 4, 3, 4, 2, 2! Pensa em água e gás, tem que ser! Chega! Peça também pelo WhatsApp! 996653422 O reiinho da Páscoa que trazes pra mim A sua Páscoa é mais gostosa na Dicopel! Formas para </t>
         </is>
       </c>
-      <c r="G54" s="176" t="inlineStr">
+      <c r="G54" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Dicopel__produtos_para_Pascoa__ovos__bombons__embalagens__etc__11-03-2026_15-40-50.mp3</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="176" t="inlineStr">
+      <c r="A55" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:41:08</t>
         </is>
       </c>
-      <c r="B55" s="176" t="inlineStr">
+      <c r="B55" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C55" s="176" t="inlineStr">
+      <c r="C55" s="192" t="inlineStr">
         <is>
           <t>Copel</t>
         </is>
       </c>
-      <c r="D55" s="176" t="inlineStr">
+      <c r="D55" s="192" t="inlineStr">
         <is>
           <t>embalagens, doces e confeitos</t>
         </is>
       </c>
-      <c r="E55" s="176" t="inlineStr">
+      <c r="E55" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3091,34 +3094,34 @@
           <t>Copel, formas para ovos e bombons de acetato e também silicone, embalagens, envelopes, caixa para ovos, papéis decorados, chocolates, confeitos, linha completa de doces e muito mais. De Copel, Avenida</t>
         </is>
       </c>
-      <c r="G55" s="176" t="inlineStr">
+      <c r="G55" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Copel__embalagens__doces_e_confeitos__11-03-2026_15-41-08.mp3</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="176" t="inlineStr">
+      <c r="A56" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:41:26</t>
         </is>
       </c>
-      <c r="B56" s="176" t="inlineStr">
+      <c r="B56" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C56" s="176" t="inlineStr">
+      <c r="C56" s="192" t="inlineStr">
         <is>
           <t>Habitar Catanduva</t>
         </is>
       </c>
-      <c r="D56" s="176" t="inlineStr">
+      <c r="D56" s="192" t="inlineStr">
         <is>
           <t>imóveis e regularização de propriedade</t>
         </is>
       </c>
-      <c r="E56" s="176" t="inlineStr">
+      <c r="E56" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3128,34 +3131,34 @@
           <t>Em frente a rotatória em Catanduva, e no dia 28 de março tem pedágio da Band das 9 às 11 da manhã, com muitos prêmios. Pedágio do jeito Band. Quem fala é o Jorge, e aqui quem fala é o Matheus. Band FM</t>
         </is>
       </c>
-      <c r="G56" s="176" t="inlineStr">
+      <c r="G56" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Habitar_Catanduva__imoveis_e_regularizacao_de_propriedade__11-03-2026_15-41-26.mp3</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="176" t="inlineStr">
+      <c r="A57" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:41:28</t>
         </is>
       </c>
-      <c r="B57" s="176" t="inlineStr">
+      <c r="B57" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C57" s="176" t="inlineStr">
+      <c r="C57" s="192" t="inlineStr">
         <is>
           <t>Cicred</t>
         </is>
       </c>
-      <c r="D57" s="176" t="inlineStr">
+      <c r="D57" s="192" t="inlineStr">
         <is>
           <t>Cartão Black</t>
         </is>
       </c>
-      <c r="E57" s="176" t="inlineStr">
+      <c r="E57" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3165,34 +3168,34 @@
           <t>Futa tem dois lados, eu vou viver só o lado pão Alô, gerente da Cicred, aumenta aí o limite do cartão black Que eu vou soltar ele na mão das pirigate Passa combo de black, passa combo de red e passa c</t>
         </is>
       </c>
-      <c r="G57" s="176" t="inlineStr">
+      <c r="G57" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Cicred__Cartao_Black__11-03-2026_15-41-28.mp3</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="176" t="inlineStr">
+      <c r="A58" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:41:43</t>
         </is>
       </c>
-      <c r="B58" s="176" t="inlineStr">
+      <c r="B58" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C58" s="176" t="inlineStr">
+      <c r="C58" s="192" t="inlineStr">
         <is>
           <t>Cicred</t>
         </is>
       </c>
-      <c r="D58" s="176" t="inlineStr">
+      <c r="D58" s="192" t="inlineStr">
         <is>
           <t>Cartão black</t>
         </is>
       </c>
-      <c r="E58" s="176" t="inlineStr">
+      <c r="E58" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3202,34 +3205,34 @@
           <t xml:space="preserve">Combo de Jack, alô gerente da Cicred, aumenta aí o limite do cartão black Eu vou soltar ele na mão das periguetes, passa combo de black, passa combo de red, passa combo de jack Alô gerente da Cicred, </t>
         </is>
       </c>
-      <c r="G58" s="176" t="inlineStr">
+      <c r="G58" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Cicred__Cartao_black__11-03-2026_15-41-43.mp3</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="176" t="inlineStr">
+      <c r="A59" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:42:01</t>
         </is>
       </c>
-      <c r="B59" s="176" t="inlineStr">
+      <c r="B59" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C59" s="176" t="inlineStr">
+      <c r="C59" s="192" t="inlineStr">
         <is>
           <t>Prefeitura de Catanduva</t>
         </is>
       </c>
-      <c r="D59" s="176" t="inlineStr">
+      <c r="D59" s="192" t="inlineStr">
         <is>
           <t>Imóveis, financiamento, regularização</t>
         </is>
       </c>
-      <c r="E59" s="176" t="inlineStr">
+      <c r="E59" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3239,34 +3242,34 @@
           <t>Imóveis, financiamento, regularização e muito mais. Tudo em um só lugar. Habitar Catanduva. Dias 24 e 25 na Estação Cultura. E a entrada é de graça. Realização Prefeitura de Catanduva. Toca toda. Band</t>
         </is>
       </c>
-      <c r="G59" s="176" t="inlineStr">
+      <c r="G59" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Prefeitura_de_Catanduva__Imoveis__financiamento__regularizacao__11-03-2026_15-42-01.mp3</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="176" t="inlineStr">
+      <c r="A60" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:42:16</t>
         </is>
       </c>
-      <c r="B60" s="176" t="inlineStr">
+      <c r="B60" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C60" s="176" t="inlineStr">
+      <c r="C60" s="192" t="inlineStr">
         <is>
           <t>Cicrede</t>
         </is>
       </c>
-      <c r="D60" s="176" t="inlineStr">
+      <c r="D60" s="192" t="inlineStr">
         <is>
           <t>Cartão black</t>
         </is>
       </c>
-      <c r="E60" s="176" t="inlineStr">
+      <c r="E60" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3276,34 +3279,34 @@
           <t>Só pra dar as menina nega samba com o soltão Comprei um raio tão exige ela de som Se a vida tem dois lados eu vou me ver só um lado pão Alô gerente da Cicrede, aumenta aí o limite do cartão black Eu v</t>
         </is>
       </c>
-      <c r="G60" s="176" t="inlineStr">
+      <c r="G60" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Cicrede__Cartao_black__11-03-2026_15-42-16.mp3</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="176" t="inlineStr">
+      <c r="A61" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:42:34</t>
         </is>
       </c>
-      <c r="B61" s="176" t="inlineStr">
+      <c r="B61" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C61" s="176" t="inlineStr">
+      <c r="C61" s="192" t="inlineStr">
         <is>
           <t>SIG Alimentos</t>
         </is>
       </c>
-      <c r="D61" s="176" t="inlineStr">
+      <c r="D61" s="192" t="inlineStr">
         <is>
           <t>Cartão Black</t>
         </is>
       </c>
-      <c r="E61" s="176" t="inlineStr">
+      <c r="E61" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3313,34 +3316,34 @@
           <t>Eu vou sortar ele na mão das piriguete, passa combo de black, passa combo de red, passa combo de jet Alô, gerente da sig alimentos, o limite do cartão black Eu vou sortar ele na mão das piriguete, pas</t>
         </is>
       </c>
-      <c r="G61" s="176" t="inlineStr">
+      <c r="G61" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__SIG_Alimentos__Cartao_Black__11-03-2026_15-42-34.mp3</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="176" t="inlineStr">
+      <c r="A62" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:45:19</t>
         </is>
       </c>
-      <c r="B62" s="176" t="inlineStr">
+      <c r="B62" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C62" s="176" t="inlineStr">
+      <c r="C62" s="192" t="inlineStr">
         <is>
           <t>Ondas Verdes</t>
         </is>
       </c>
-      <c r="D62" s="176" t="inlineStr">
+      <c r="D62" s="192" t="inlineStr">
         <is>
           <t>Aplicativo</t>
         </is>
       </c>
-      <c r="E62" s="176" t="inlineStr">
+      <c r="E62" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3350,34 +3353,34 @@
           <t>Minha aí, Fuscão Preto, por favor, João Carreira e Fardinho. Muito bem, um abração pessoal de Embaú, Banu Vaz, Pindorama, sempre ouvindo a Enfimida, a gente volta já já. Ondas Verdes Quer ouvir a Onda</t>
         </is>
       </c>
-      <c r="G62" s="176" t="inlineStr">
+      <c r="G62" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Ondas_Verdes__Aplicativo__11-03-2026_15-45-19.mp3</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="176" t="inlineStr">
+      <c r="A63" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:45:36</t>
         </is>
       </c>
-      <c r="B63" s="176" t="inlineStr">
+      <c r="B63" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C63" s="176" t="inlineStr">
+      <c r="C63" s="192" t="inlineStr">
         <is>
           <t>Farmopatia</t>
         </is>
       </c>
-      <c r="D63" s="176" t="inlineStr">
+      <c r="D63" s="192" t="inlineStr">
         <is>
           <t>produtos ou serviços de farmácia</t>
         </is>
       </c>
-      <c r="E63" s="176" t="inlineStr">
+      <c r="E63" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3387,7 +3390,7 @@
           <t>Quero ouvir a Ondas Verdes no celular. Baixe grátis o aplicativo e ouça Ondas Verdes também no celular. Natural é confiar, é fazer tudo cada vez melhor. Com carinho, amizade e cuidado. É natural viver</t>
         </is>
       </c>
-      <c r="G63" s="176" t="inlineStr">
+      <c r="G63" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Farmopatia__produtos_ou_servicos_de_farmacia__11-03-2026_15-45-35__ad1.mp3</t>
         </is>
@@ -3431,27 +3434,27 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="176" t="inlineStr">
+      <c r="A65" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:45:51</t>
         </is>
       </c>
-      <c r="B65" s="176" t="inlineStr">
+      <c r="B65" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C65" s="176" t="inlineStr">
+      <c r="C65" s="192" t="inlineStr">
         <is>
           <t>Farmopatia</t>
         </is>
       </c>
-      <c r="D65" s="176" t="inlineStr">
+      <c r="D65" s="192" t="inlineStr">
         <is>
           <t>Produtos de saúde</t>
         </is>
       </c>
-      <c r="E65" s="176" t="inlineStr">
+      <c r="E65" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3461,34 +3464,34 @@
           <t>É natural viver bem a cada dia. Viva com mais saúde, farmopatia. Farmopatia, quarenta anos ao seu lado. Viva bem com alegria, farmopatia. Rua Pará, 771 no centro. Pone o ato 1735313300. zero. Mega ofe</t>
         </is>
       </c>
-      <c r="G65" s="176" t="inlineStr">
+      <c r="G65" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Farmopatia__Produtos_de_saude__11-03-2026_15-45-51__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="176" t="inlineStr">
+      <c r="A66" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:45:51</t>
         </is>
       </c>
-      <c r="B66" s="176" t="inlineStr">
+      <c r="B66" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C66" s="176" t="inlineStr">
+      <c r="C66" s="192" t="inlineStr">
         <is>
           <t>Antunes</t>
         </is>
       </c>
-      <c r="D66" s="176" t="inlineStr">
+      <c r="D66" s="192" t="inlineStr">
         <is>
           <t>Produtos em geral</t>
         </is>
       </c>
-      <c r="E66" s="176" t="inlineStr">
+      <c r="E66" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3498,34 +3501,34 @@
           <t>É natural viver bem a cada dia. Viva com mais saúde, farmopatia. Farmopatia, quarenta anos ao seu lado. Viva bem com alegria, farmopatia. Rua Pará, 771 no centro. Pone o ato 1735313300. zero. Mega ofe</t>
         </is>
       </c>
-      <c r="G66" s="176" t="inlineStr">
+      <c r="G66" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Antunes__Produtos_em_geral__11-03-2026_15-45-51__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="176" t="inlineStr">
+      <c r="A67" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:46:25</t>
         </is>
       </c>
-      <c r="B67" s="176" t="inlineStr">
+      <c r="B67" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C67" s="176" t="inlineStr">
+      <c r="C67" s="192" t="inlineStr">
         <is>
           <t>Atunes Mais</t>
         </is>
       </c>
-      <c r="D67" s="176" t="inlineStr">
+      <c r="D67" s="192" t="inlineStr">
         <is>
           <t>Carnes e ofertas do Clube do Precinho</t>
         </is>
       </c>
-      <c r="E67" s="176" t="inlineStr">
+      <c r="E67" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3535,34 +3538,34 @@
           <t>Cote, quinze e quarenta e nove o quilo. Bisteca suína, treze e noventa e nove o quilo. Linguiça suína, perdigão, quatorze e noventa e nove o quilo. Tem também as ofertas do Clube do Precinho. Paleta o</t>
         </is>
       </c>
-      <c r="G67" s="176" t="inlineStr">
+      <c r="G67" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Atunes_Mais__Carnes_e_ofertas_do_Clube_do_Precinho__11-03-2026_15-46-25.mp3</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="176" t="inlineStr">
+      <c r="A68" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:46:41</t>
         </is>
       </c>
-      <c r="B68" s="176" t="inlineStr">
+      <c r="B68" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C68" s="176" t="inlineStr">
+      <c r="C68" s="192" t="inlineStr">
         <is>
           <t>Atunes Mais</t>
         </is>
       </c>
-      <c r="D68" s="176" t="inlineStr">
+      <c r="D68" s="192" t="inlineStr">
         <is>
           <t>ofertas</t>
         </is>
       </c>
-      <c r="E68" s="176" t="inlineStr">
+      <c r="E68" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3572,34 +3575,34 @@
           <t>quarenta e quatro e oitenta e cinco. Ofertas válidas somente hoje no Atunes Mais. Dia vinte de março no Clube de Tênis Catanduva, dois super shows. Tem um moço na abertura. E pela primeira vez na regi</t>
         </is>
       </c>
-      <c r="G68" s="176" t="inlineStr">
+      <c r="G68" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Atunes_Mais__ofertas__11-03-2026_15-46-41__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="176" t="inlineStr">
+      <c r="A69" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:46:41</t>
         </is>
       </c>
-      <c r="B69" s="176" t="inlineStr">
+      <c r="B69" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C69" s="176" t="inlineStr">
+      <c r="C69" s="192" t="inlineStr">
         <is>
           <t>Clube de Tênis Catanduva</t>
         </is>
       </c>
-      <c r="D69" s="176" t="inlineStr">
+      <c r="D69" s="192" t="inlineStr">
         <is>
           <t>shows</t>
         </is>
       </c>
-      <c r="E69" s="176" t="inlineStr">
+      <c r="E69" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3609,34 +3612,34 @@
           <t>quarenta e quatro e oitenta e cinco. Ofertas válidas somente hoje no Atunes Mais. Dia vinte de março no Clube de Tênis Catanduva, dois super shows. Tem um moço na abertura. E pela primeira vez na regi</t>
         </is>
       </c>
-      <c r="G69" s="176" t="inlineStr">
+      <c r="G69" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Clube_de_Tenis_Catanduva__shows__11-03-2026_15-46-41__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="176" t="inlineStr">
+      <c r="A70" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:46:58</t>
         </is>
       </c>
-      <c r="B70" s="176" t="inlineStr">
+      <c r="B70" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C70" s="176" t="inlineStr">
+      <c r="C70" s="192" t="inlineStr">
         <is>
           <t>Clube de Tênis Catanduva</t>
         </is>
       </c>
-      <c r="D70" s="176" t="inlineStr">
+      <c r="D70" s="192" t="inlineStr">
         <is>
           <t>Evento com Open Bar e área VIP</t>
         </is>
       </c>
-      <c r="E70" s="176" t="inlineStr">
+      <c r="E70" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3646,34 +3649,34 @@
           <t>E em palco trezentos e sessenta. Mesas Open Pool de Open Bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br. Seu Moço e Traia Velha, dia vinte de março, no Clube</t>
         </is>
       </c>
-      <c r="G70" s="176" t="inlineStr">
+      <c r="G70" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Clube_de_Tenis_Catanduva__Evento_com_Open_Bar_e_area_VIP__11-03-2026_15-46-58__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="176" t="inlineStr">
+      <c r="A71" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:46:58</t>
         </is>
       </c>
-      <c r="B71" s="176" t="inlineStr">
+      <c r="B71" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C71" s="176" t="inlineStr">
+      <c r="C71" s="192" t="inlineStr">
         <is>
           <t>querodoisingressos.com.br</t>
         </is>
       </c>
-      <c r="D71" s="176" t="inlineStr">
+      <c r="D71" s="192" t="inlineStr">
         <is>
           <t>Ingressos para eventos</t>
         </is>
       </c>
-      <c r="E71" s="176" t="inlineStr">
+      <c r="E71" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3683,34 +3686,34 @@
           <t>E em palco trezentos e sessenta. Mesas Open Pool de Open Bar e convites para área VIP, a venda na Secretaria do Clube ou querodoisingressos.com.br. Seu Moço e Traia Velha, dia vinte de março, no Clube</t>
         </is>
       </c>
-      <c r="G71" s="176" t="inlineStr">
+      <c r="G71" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__querodoisingressos_com_br__Ingressos_para_eventos__11-03-2026_15-46-58__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="176" t="inlineStr">
+      <c r="A72" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:49:27</t>
         </is>
       </c>
-      <c r="B72" s="176" t="inlineStr">
+      <c r="B72" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C72" s="176" t="inlineStr">
+      <c r="C72" s="192" t="inlineStr">
         <is>
           <t>Band FM</t>
         </is>
       </c>
-      <c r="D72" s="176" t="inlineStr">
+      <c r="D72" s="192" t="inlineStr">
         <is>
           <t>Rádio/Estação de Rádio</t>
         </is>
       </c>
-      <c r="E72" s="176" t="inlineStr">
+      <c r="E72" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3720,34 +3723,34 @@
           <t>O áudio, quando a ficha caiu, fiquei desesperado, tava conectado, no blanco do carro A boca errada falou tudo que o ouvido certo não sabia Quando eu voltei pro carro, ela não tava no cabinei Toca toda</t>
         </is>
       </c>
-      <c r="G72" s="176" t="inlineStr">
+      <c r="G72" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Band_FM__Radio_Estacao_de_Radio__11-03-2026_15-49-27.mp3</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="176" t="inlineStr">
+      <c r="A73" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:59:14</t>
         </is>
       </c>
-      <c r="B73" s="176" t="inlineStr">
+      <c r="B73" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C73" s="176" t="inlineStr">
+      <c r="C73" s="192" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="D73" s="176" t="inlineStr">
+      <c r="D73" s="192" t="inlineStr">
         <is>
           <t>burgers</t>
         </is>
       </c>
-      <c r="E73" s="176" t="inlineStr">
+      <c r="E73" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3757,34 +3760,34 @@
           <t>Black Eyed Peas Ainda ouvimos o Jota Quest, Post Malone, The Weeknd, Jack Johnson e uma clássica com o Rafa Só no BK Você garante dois burgers que valem cada</t>
         </is>
       </c>
-      <c r="G73" s="176" t="inlineStr">
+      <c r="G73" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__BK__burgers__11-03-2026_15-59-14.mp3</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="176" t="inlineStr">
+      <c r="A74" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 15:59:32</t>
         </is>
       </c>
-      <c r="B74" s="176" t="inlineStr">
+      <c r="B74" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C74" s="176" t="inlineStr">
+      <c r="C74" s="192" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="D74" s="176" t="inlineStr">
+      <c r="D74" s="192" t="inlineStr">
         <is>
           <t>hambúrgueres</t>
         </is>
       </c>
-      <c r="E74" s="176" t="inlineStr">
+      <c r="E74" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3794,34 +3797,34 @@
           <t xml:space="preserve">com o Rafa. Só no BK, você garante dois hambúrgueres que valem cada mordida, com porções generosas, grelhadas no fogo e com ingredientes frescos, a partir de vinte e cinco e noventa. Cole no BK Drive </t>
         </is>
       </c>
-      <c r="G74" s="176" t="inlineStr">
+      <c r="G74" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__BK__hamburgueres__11-03-2026_15-59-32.mp3</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="176" t="inlineStr">
+      <c r="A75" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:00:08</t>
         </is>
       </c>
-      <c r="B75" s="176" t="inlineStr">
+      <c r="B75" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C75" s="176" t="inlineStr">
+      <c r="C75" s="192" t="inlineStr">
         <is>
           <t>Casa dos Construtores</t>
         </is>
       </c>
-      <c r="D75" s="176" t="inlineStr">
+      <c r="D75" s="192" t="inlineStr">
         <is>
           <t>espaços e casas</t>
         </is>
       </c>
-      <c r="E75" s="176" t="inlineStr">
+      <c r="E75" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3831,34 +3834,34 @@
           <t>O verdadeiro luxo não está no que se compra, mas em como se vive. O tempo bem vivido é feito de escolhas, de detalhes que permanecem, de casas que acolhem, de memórias que resistem. Há 65 anos, criamo</t>
         </is>
       </c>
-      <c r="G75" s="176" t="inlineStr">
+      <c r="G75" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Casa_dos_Construtores__espacos_e_casas__11-03-2026_16-00-08.mp3</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="176" t="inlineStr">
+      <c r="A76" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:00:26</t>
         </is>
       </c>
-      <c r="B76" s="176" t="inlineStr">
+      <c r="B76" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C76" s="176" t="inlineStr">
+      <c r="C76" s="192" t="inlineStr">
         <is>
           <t>Casa dos Construtores</t>
         </is>
       </c>
-      <c r="D76" s="176" t="inlineStr">
+      <c r="D76" s="192" t="inlineStr">
         <is>
           <t>serviços de construção ou decoração</t>
         </is>
       </c>
-      <c r="E76" s="176" t="inlineStr">
+      <c r="E76" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3868,34 +3871,34 @@
           <t>Criamos espaços para que cada instante não apenas passe, mas fique. Casa dos Construtores, o melhor tempo na sua casa.</t>
         </is>
       </c>
-      <c r="G76" s="176" t="inlineStr">
+      <c r="G76" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Casa_dos_Construtores__servicos_de_construcao_ou_decoracao__11-03-2026_16-00-26.mp3</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="176" t="inlineStr">
+      <c r="A77" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:01:02</t>
         </is>
       </c>
-      <c r="B77" s="176" t="inlineStr">
+      <c r="B77" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C77" s="176" t="inlineStr">
+      <c r="C77" s="192" t="inlineStr">
         <is>
           <t>Caravelas</t>
         </is>
       </c>
-      <c r="D77" s="176" t="inlineStr">
+      <c r="D77" s="192" t="inlineStr">
         <is>
           <t>produto não especificado</t>
         </is>
       </c>
-      <c r="E77" s="176" t="inlineStr">
+      <c r="E77" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3905,34 +3908,34 @@
           <t>Caravelas, pelo sabor do novo</t>
         </is>
       </c>
-      <c r="G77" s="176" t="inlineStr">
+      <c r="G77" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Caravelas__produto_nao_especificado__11-03-2026_16-01-02.mp3</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="176" t="inlineStr">
+      <c r="A78" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:01:39</t>
         </is>
       </c>
-      <c r="B78" s="176" t="inlineStr">
+      <c r="B78" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C78" s="176" t="inlineStr">
+      <c r="C78" s="192" t="inlineStr">
         <is>
           <t>Unifipa</t>
         </is>
       </c>
-      <c r="D78" s="176" t="inlineStr">
+      <c r="D78" s="192" t="inlineStr">
         <is>
           <t>Vestibular continuado 2026</t>
         </is>
       </c>
-      <c r="E78" s="176" t="inlineStr">
+      <c r="E78" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -3942,7 +3945,7 @@
           <t>futuro acontecer. Participe do vestibular continuado dois mil e vinte e seis da Unifipa Catanduva. São onze opções de cursos de graduação na instituição que tem mais de cinquenta e cinco anos de tradi</t>
         </is>
       </c>
-      <c r="G78" s="176" t="inlineStr">
+      <c r="G78" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Unifipa__Vestibular_continuado_2026__11-03-2026_16-01-39__ad1.mp3</t>
         </is>
@@ -3986,27 +3989,27 @@
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="176" t="inlineStr">
+      <c r="A80" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:01:56</t>
         </is>
       </c>
-      <c r="B80" s="176" t="inlineStr">
+      <c r="B80" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C80" s="176" t="inlineStr">
+      <c r="C80" s="192" t="inlineStr">
         <is>
           <t>Unifipa</t>
         </is>
       </c>
-      <c r="D80" s="176" t="inlineStr">
+      <c r="D80" s="192" t="inlineStr">
         <is>
           <t>provas online</t>
         </is>
       </c>
-      <c r="E80" s="176" t="inlineStr">
+      <c r="E80" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4016,34 +4019,34 @@
           <t>e provas online em Unifipa ponto</t>
         </is>
       </c>
-      <c r="G80" s="176" t="inlineStr">
+      <c r="G80" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Unifipa__provas_online__11-03-2026_16-01-56.mp3</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="176" t="inlineStr">
+      <c r="A81" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:02:33</t>
         </is>
       </c>
-      <c r="B81" s="176" t="inlineStr">
+      <c r="B81" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C81" s="176" t="inlineStr">
+      <c r="C81" s="192" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="D81" s="176" t="inlineStr">
+      <c r="D81" s="192" t="inlineStr">
         <is>
           <t>Internet</t>
         </is>
       </c>
-      <c r="E81" s="176" t="inlineStr">
+      <c r="E81" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4053,7 +4056,7 @@
           <t>Vem express, procurando a conexão perfeita? Então pare de procurar. A melhor internet da região é Netflix. O melhor suporte técnico é Netflix. A maior velocidade pra você voar navegando, com certeza é</t>
         </is>
       </c>
-      <c r="G81" s="176" t="inlineStr">
+      <c r="G81" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Netflix__Internet__11-03-2026_16-02-33__ad1.mp3</t>
         </is>
@@ -4097,27 +4100,27 @@
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="176" t="inlineStr">
+      <c r="A83" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:02:51</t>
         </is>
       </c>
-      <c r="B83" s="176" t="inlineStr">
+      <c r="B83" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C83" s="176" t="inlineStr">
+      <c r="C83" s="192" t="inlineStr">
         <is>
           <t>Netflex</t>
         </is>
       </c>
-      <c r="D83" s="176" t="inlineStr">
+      <c r="D83" s="192" t="inlineStr">
         <is>
           <t>Internet</t>
         </is>
       </c>
-      <c r="E83" s="176" t="inlineStr">
+      <c r="E83" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4127,34 +4130,34 @@
           <t>Venha você também para a ultra velocidade. Ligue agora ou mande um zap 17 315 1000 ou acesse netflexbr.com. Mega ofertas na Quarta Animal do Antunes Mais. Qualidade e preço baixo é aqui. Pelé de peito</t>
         </is>
       </c>
-      <c r="G83" s="176" t="inlineStr">
+      <c r="G83" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Netflex__Internet__11-03-2026_16-02-51__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="176" t="inlineStr">
+      <c r="A84" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:02:51</t>
         </is>
       </c>
-      <c r="B84" s="176" t="inlineStr">
+      <c r="B84" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C84" s="176" t="inlineStr">
+      <c r="C84" s="192" t="inlineStr">
         <is>
           <t>Antunes Mais</t>
         </is>
       </c>
-      <c r="D84" s="176" t="inlineStr">
+      <c r="D84" s="192" t="inlineStr">
         <is>
           <t>Produtos alimentícios</t>
         </is>
       </c>
-      <c r="E84" s="176" t="inlineStr">
+      <c r="E84" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4164,34 +4167,34 @@
           <t>Venha você também para a ultra velocidade. Ligue agora ou mande um zap 17 315 1000 ou acesse netflexbr.com. Mega ofertas na Quarta Animal do Antunes Mais. Qualidade e preço baixo é aqui. Pelé de peito</t>
         </is>
       </c>
-      <c r="G84" s="176" t="inlineStr">
+      <c r="G84" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Antunes_Mais__Produtos_alimenticios__11-03-2026_16-02-51__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="176" t="inlineStr">
+      <c r="A85" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:03:09</t>
         </is>
       </c>
-      <c r="B85" s="176" t="inlineStr">
+      <c r="B85" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C85" s="176" t="inlineStr">
+      <c r="C85" s="192" t="inlineStr">
         <is>
           <t>Atunes Mais</t>
         </is>
       </c>
-      <c r="D85" s="176" t="inlineStr">
+      <c r="D85" s="192" t="inlineStr">
         <is>
           <t>carnes (bisteca suína, linguiça suína, paleta ou ponta de peito bovina, alcatra com maminha)</t>
         </is>
       </c>
-      <c r="E85" s="176" t="inlineStr">
+      <c r="E85" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4201,34 +4204,34 @@
           <t>nove o quilo, bisteca suína, treze e noventa e nove o quilo, linguiça suína, perdigão, quatorze e noventa e nove o quilo. Tem também as ofertas do Clube do Precinho, paleta ou ponta de peito bovina se</t>
         </is>
       </c>
-      <c r="G85" s="176" t="inlineStr">
+      <c r="G85" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Atunes_Mais__carnes__bisteca_suina__linguica_suina__paleta_ou_ponta_de_pe__11-03-2026_16-03-09.mp3</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="176" t="inlineStr">
+      <c r="A86" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:04:03</t>
         </is>
       </c>
-      <c r="B86" s="176" t="inlineStr">
+      <c r="B86" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C86" s="176" t="inlineStr">
+      <c r="C86" s="192" t="inlineStr">
         <is>
           <t>Jovem Pan</t>
         </is>
       </c>
-      <c r="D86" s="176" t="inlineStr">
+      <c r="D86" s="192" t="inlineStr">
         <is>
           <t>campanha contra o crime</t>
         </is>
       </c>
-      <c r="E86" s="176" t="inlineStr">
+      <c r="E86" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4238,34 +4241,34 @@
           <t>Chega! Era por volta de umas seis da manhã, né? Eu desci do ônibus pra fazer meu trajeto pra ir pra empresa. Eu tava andando na rua, né? Assim, aí um cara tava vindo também, só que na direção contrári</t>
         </is>
       </c>
-      <c r="G86" s="176" t="inlineStr">
+      <c r="G86" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Jovem_Pan__campanha_contra_o_crime__11-03-2026_16-04-03.mp3</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="176" t="inlineStr">
+      <c r="A87" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:04:07</t>
         </is>
       </c>
-      <c r="B87" s="176" t="inlineStr">
+      <c r="B87" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C87" s="176" t="inlineStr">
+      <c r="C87" s="192" t="inlineStr">
         <is>
           <t>Unifipa</t>
         </is>
       </c>
-      <c r="D87" s="176" t="inlineStr">
+      <c r="D87" s="192" t="inlineStr">
         <is>
           <t>Cursos e Ensino</t>
         </is>
       </c>
-      <c r="E87" s="176" t="inlineStr">
+      <c r="E87" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4275,34 +4278,34 @@
           <t>E é sinônimo de excelência em ensino, com nota máxima na avaliação do MEC. Venha ser Unifipa. Inscrições e provas online em unifipa.com.br barra vestibular. Unifipa, referência que transforma vidas. P</t>
         </is>
       </c>
-      <c r="G87" s="176" t="inlineStr">
+      <c r="G87" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Unifipa__Cursos_e_Ensino__11-03-2026_16-04-07__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="176" t="inlineStr">
+      <c r="A88" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:04:07</t>
         </is>
       </c>
-      <c r="B88" s="176" t="inlineStr">
+      <c r="B88" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C88" s="176" t="inlineStr">
+      <c r="C88" s="192" t="inlineStr">
         <is>
           <t>Prestimonte</t>
         </is>
       </c>
-      <c r="D88" s="176" t="inlineStr">
+      <c r="D88" s="192" t="inlineStr">
         <is>
           <t>Serralheria e Fachadas</t>
         </is>
       </c>
-      <c r="E88" s="176" t="inlineStr">
+      <c r="E88" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4312,34 +4315,34 @@
           <t>E é sinônimo de excelência em ensino, com nota máxima na avaliação do MEC. Venha ser Unifipa. Inscrições e provas online em unifipa.com.br barra vestibular. Unifipa, referência que transforma vidas. P</t>
         </is>
       </c>
-      <c r="G88" s="176" t="inlineStr">
+      <c r="G88" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Prestimonte__Serralheria_e_Fachadas__11-03-2026_16-04-07__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="176" t="inlineStr">
+      <c r="A89" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:04:23</t>
         </is>
       </c>
-      <c r="B89" s="176" t="inlineStr">
+      <c r="B89" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C89" s="176" t="inlineStr">
+      <c r="C89" s="192" t="inlineStr">
         <is>
           <t>Prestimonte</t>
         </is>
       </c>
-      <c r="D89" s="176" t="inlineStr">
+      <c r="D89" s="192" t="inlineStr">
         <is>
           <t>fachadas de comércio e indústria, serralheria, portão, cobertura metálica e corrimão de aço inox</t>
         </is>
       </c>
-      <c r="E89" s="176" t="inlineStr">
+      <c r="E89" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4349,34 +4352,34 @@
           <t>Quem entende? Prestimonte, há muitos anos no mercado fazendo fachadas de comércio e indústria. Serralheria em geral, portão, cobertura metálica e corrimão de aço inox. Fale com a gente. Prestimonte, R</t>
         </is>
       </c>
-      <c r="G89" s="176" t="inlineStr">
+      <c r="G89" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Prestimonte__fachadas_de_comercio_e_industria__serralheria__portao__cober__11-03-2026_16-04-23.mp3</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="176" t="inlineStr">
+      <c r="A90" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:04:40</t>
         </is>
       </c>
-      <c r="B90" s="176" t="inlineStr">
+      <c r="B90" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C90" s="176" t="inlineStr">
+      <c r="C90" s="192" t="inlineStr">
         <is>
           <t>Cotuca</t>
         </is>
       </c>
-      <c r="D90" s="176" t="inlineStr">
+      <c r="D90" s="192" t="inlineStr">
         <is>
           <t>materiais de construção e serviços de reparo</t>
         </is>
       </c>
-      <c r="E90" s="176" t="inlineStr">
+      <c r="E90" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4386,34 +4389,34 @@
           <t>Telefone 3522-7961 ou 99744-7961. Prestemonte, qualidade e segurança pra sua obra. Pra você que está construindo ou reformando a Cotuca, comércio tubos, cataluva, tem tubos a banco, reparos pra tornei</t>
         </is>
       </c>
-      <c r="G90" s="176" t="inlineStr">
+      <c r="G90" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Cotuca__materiais_de_construcao_e_servicos_de_reparo__11-03-2026_16-04-40.mp3</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="176" t="inlineStr">
+      <c r="A91" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:04:56</t>
         </is>
       </c>
-      <c r="B91" s="176" t="inlineStr">
+      <c r="B91" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C91" s="176" t="inlineStr">
+      <c r="C91" s="192" t="inlineStr">
         <is>
           <t>Cotuca</t>
         </is>
       </c>
-      <c r="D91" s="176" t="inlineStr">
+      <c r="D91" s="192" t="inlineStr">
         <is>
           <t>Materiais para irrigação e construção</t>
         </is>
       </c>
-      <c r="E91" s="176" t="inlineStr">
+      <c r="E91" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4423,34 +4426,34 @@
           <t>A nova tem tubos a banco, reparos pra torneiras e vaula hidra, tudo pra irrigação e caixa d'água. Cotuca, Rua Fredo Ortega, setenta e sete, telefone três cinco dois cinco zero zero dois zero, atendend</t>
         </is>
       </c>
-      <c r="G91" s="176" t="inlineStr">
+      <c r="G91" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Cotuca__Materiais_para_irrigacao_e_construcao__11-03-2026_16-04-56__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="176" t="inlineStr">
+      <c r="A92" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:04:57</t>
         </is>
       </c>
-      <c r="B92" s="176" t="inlineStr">
+      <c r="B92" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C92" s="176" t="inlineStr">
+      <c r="C92" s="192" t="inlineStr">
         <is>
           <t>Quinze Auto Center São Francisco</t>
         </is>
       </c>
-      <c r="D92" s="176" t="inlineStr">
+      <c r="D92" s="192" t="inlineStr">
         <is>
           <t>Reparação de veículos</t>
         </is>
       </c>
-      <c r="E92" s="176" t="inlineStr">
+      <c r="E92" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4460,34 +4463,34 @@
           <t>A nova tem tubos a banco, reparos pra torneiras e vaula hidra, tudo pra irrigação e caixa d'água. Cotuca, Rua Fredo Ortega, setenta e sete, telefone três cinco dois cinco zero zero dois zero, atendend</t>
         </is>
       </c>
-      <c r="G92" s="176" t="inlineStr">
+      <c r="G92" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Quinze_Auto_Center_Sao_Francisco__Reparacao_de_veiculos__11-03-2026_16-04-57__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="176" t="inlineStr">
+      <c r="A93" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:05:15</t>
         </is>
       </c>
-      <c r="B93" s="176" t="inlineStr">
+      <c r="B93" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C93" s="176" t="inlineStr">
+      <c r="C93" s="192" t="inlineStr">
         <is>
           <t>Quinze Auto Center São Francisco</t>
         </is>
       </c>
-      <c r="D93" s="176" t="inlineStr">
+      <c r="D93" s="192" t="inlineStr">
         <is>
           <t>serviços de reparação de veículos</t>
         </is>
       </c>
-      <c r="E93" s="176" t="inlineStr">
+      <c r="E93" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4497,34 +4500,34 @@
           <t xml:space="preserve">O Tuca, construindo com você. E atenção, agora também material para qualquer tipo de irrigação, vai lá. Quinze Auto Center São Francisco, maior centro de reparação de veículos, nacionais, impostados, </t>
         </is>
       </c>
-      <c r="G93" s="176" t="inlineStr">
+      <c r="G93" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Quinze_Auto_Center_Sao_Francisco__servicos_de_reparacao_de_veiculos__11-03-2026_16-05-15.mp3</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="176" t="inlineStr">
+      <c r="A94" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:05:29</t>
         </is>
       </c>
-      <c r="B94" s="176" t="inlineStr">
+      <c r="B94" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C94" s="176" t="inlineStr">
+      <c r="C94" s="192" t="inlineStr">
         <is>
           <t>15 Auto Center São Francisco</t>
         </is>
       </c>
-      <c r="D94" s="176" t="inlineStr">
+      <c r="D94" s="192" t="inlineStr">
         <is>
           <t>serviços de mecânica</t>
         </is>
       </c>
-      <c r="E94" s="176" t="inlineStr">
+      <c r="E94" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4534,34 +4537,34 @@
           <t>Um orçamento sem compromisso, suspensão, parte elétrica, ar-condicionado, injeção eletrônica, troca de óleo e filtros, serviço de mecânica em geral. Seu carro deu problema? Não leve em qualquer lugar.</t>
         </is>
       </c>
-      <c r="G94" s="176" t="inlineStr">
+      <c r="G94" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__15_Auto_Center_Sao_Francisco__servicos_de_mecanica__11-03-2026_16-05-29.mp3</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="176" t="inlineStr">
+      <c r="A95" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:05:46</t>
         </is>
       </c>
-      <c r="B95" s="176" t="inlineStr">
+      <c r="B95" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C95" s="176" t="inlineStr">
+      <c r="C95" s="192" t="inlineStr">
         <is>
           <t>Auto Center</t>
         </is>
       </c>
-      <c r="D95" s="176" t="inlineStr">
+      <c r="D95" s="192" t="inlineStr">
         <is>
           <t>seguros</t>
         </is>
       </c>
-      <c r="E95" s="176" t="inlineStr">
+      <c r="E95" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4571,34 +4574,34 @@
           <t>Rone, três, cinco, dois, três, quatro, oito, meia, meia, quinze Auto Center, São Francisco. Para nós é o seguros da sua família, está em primeiro lugar, Eléctrica Araújo. A maior variedade com os meno</t>
         </is>
       </c>
-      <c r="G95" s="176" t="inlineStr">
+      <c r="G95" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Auto_Center__seguros__11-03-2026_16-05-46__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="176" t="inlineStr">
+      <c r="A96" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:05:46</t>
         </is>
       </c>
-      <c r="B96" s="176" t="inlineStr">
+      <c r="B96" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C96" s="176" t="inlineStr">
+      <c r="C96" s="192" t="inlineStr">
         <is>
           <t>Eléctrica Araújo</t>
         </is>
       </c>
-      <c r="D96" s="176" t="inlineStr">
+      <c r="D96" s="192" t="inlineStr">
         <is>
           <t>produtos elétricos</t>
         </is>
       </c>
-      <c r="E96" s="176" t="inlineStr">
+      <c r="E96" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4608,7 +4611,7 @@
           <t>Rone, três, cinco, dois, três, quatro, oito, meia, meia, quinze Auto Center, São Francisco. Para nós é o seguros da sua família, está em primeiro lugar, Eléctrica Araújo. A maior variedade com os meno</t>
         </is>
       </c>
-      <c r="G96" s="176" t="inlineStr">
+      <c r="G96" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Electrica_Araujo__produtos_eletricos__11-03-2026_16-05-46__ad2.mp3</t>
         </is>
@@ -4652,27 +4655,27 @@
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="176" t="inlineStr">
+      <c r="A98" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:06:19</t>
         </is>
       </c>
-      <c r="B98" s="176" t="inlineStr">
+      <c r="B98" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C98" s="176" t="inlineStr">
+      <c r="C98" s="192" t="inlineStr">
         <is>
           <t>Berin Life</t>
         </is>
       </c>
-      <c r="D98" s="176" t="inlineStr">
+      <c r="D98" s="192" t="inlineStr">
         <is>
           <t>suplemento/saúde</t>
         </is>
       </c>
-      <c r="E98" s="176" t="inlineStr">
+      <c r="E98" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4682,7 +4685,7 @@
           <t>A veja o teu anjo estupro de berinjela. Vida com mais qualidade, é vida com Berin Life. Saúde é com Berin Life. Berin Life, está à venda nas melhores farmácias e casas de produtos naturais, pertinho d</t>
         </is>
       </c>
-      <c r="G98" s="176" t="inlineStr">
+      <c r="G98" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Berin_Life__suplemento_saude__11-03-2026_16-06-19.mp3</t>
         </is>
@@ -4726,27 +4729,27 @@
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="176" t="inlineStr">
+      <c r="A100" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:08:15</t>
         </is>
       </c>
-      <c r="B100" s="176" t="inlineStr">
+      <c r="B100" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C100" s="176" t="inlineStr">
+      <c r="C100" s="192" t="inlineStr">
         <is>
           <t>Traia Veia</t>
         </is>
       </c>
-      <c r="D100" s="176" t="inlineStr">
+      <c r="D100" s="192" t="inlineStr">
         <is>
           <t>Show no Clube de Tênis de Catanduva</t>
         </is>
       </c>
-      <c r="E100" s="176" t="inlineStr">
+      <c r="E100" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4756,34 +4759,34 @@
           <t xml:space="preserve">lá de Embaúba, ela e toda a família, toda a região ligada na Ondas Verdes tá chegando aí, ó, sucesso de Traia Veia. Traia Veia estará agora no Clube de Tênis de Catanduva, dia 20 de março, e você é o </t>
         </is>
       </c>
-      <c r="G100" s="176" t="inlineStr">
+      <c r="G100" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Traia_Veia__Show_no_Clube_de_Tenis_de_Catanduva__11-03-2026_16-08-15.mp3</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="176" t="inlineStr">
+      <c r="A101" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:11:27</t>
         </is>
       </c>
-      <c r="B101" s="176" t="inlineStr">
+      <c r="B101" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C101" s="176" t="inlineStr">
+      <c r="C101" s="192" t="inlineStr">
         <is>
           <t>Cicred</t>
         </is>
       </c>
-      <c r="D101" s="176" t="inlineStr">
+      <c r="D101" s="192" t="inlineStr">
         <is>
           <t>Cartão Black</t>
         </is>
       </c>
-      <c r="E101" s="176" t="inlineStr">
+      <c r="E101" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4793,34 +4796,34 @@
           <t>Busca o boy town Comprei um raio loucão, enchi ela de som Salvei das menina na caçamba com sabão Comprei um raio loucão, enchi ela de som Se a vida tem dois lados, eu vou viver só um lado bom Alô gere</t>
         </is>
       </c>
-      <c r="G101" s="176" t="inlineStr">
+      <c r="G101" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Cicred__Cartao_Black__11-03-2026_16-11-27.mp3</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="176" t="inlineStr">
+      <c r="A102" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:11:45</t>
         </is>
       </c>
-      <c r="B102" s="176" t="inlineStr">
+      <c r="B102" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C102" s="176" t="inlineStr">
+      <c r="C102" s="192" t="inlineStr">
         <is>
           <t>Cicred</t>
         </is>
       </c>
-      <c r="D102" s="176" t="inlineStr">
+      <c r="D102" s="192" t="inlineStr">
         <is>
           <t>Cartão Black</t>
         </is>
       </c>
-      <c r="E102" s="176" t="inlineStr">
+      <c r="E102" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4830,34 +4833,34 @@
           <t>Eu vou viver só lá do bairro Alô, gerente da Cicred Aumenta aí o limite do cartão black Que eu vou acertar ele na mão das piriguete Passa combo de black, passa combo de red Passa combo de jack Alô, ge</t>
         </is>
       </c>
-      <c r="G102" s="176" t="inlineStr">
+      <c r="G102" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Cicred__Cartao_Black__11-03-2026_16-11-45.mp3</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="176" t="inlineStr">
+      <c r="A103" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:12:02</t>
         </is>
       </c>
-      <c r="B103" s="176" t="inlineStr">
+      <c r="B103" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C103" s="176" t="inlineStr">
+      <c r="C103" s="192" t="inlineStr">
         <is>
           <t>Cicred</t>
         </is>
       </c>
-      <c r="D103" s="176" t="inlineStr">
+      <c r="D103" s="192" t="inlineStr">
         <is>
           <t>Cartão Black</t>
         </is>
       </c>
-      <c r="E103" s="176" t="inlineStr">
+      <c r="E103" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4867,34 +4870,34 @@
           <t>Cicred, aumenta aí o limite do cartão black Que eu vou sentar, ele na mão das pirigate Passa o combo de black, passa o combo de red E passa o combo de jet Alô, gerente da Cicred Band FM, gerente da Ci</t>
         </is>
       </c>
-      <c r="G103" s="176" t="inlineStr">
+      <c r="G103" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Cicred__Cartao_Black__11-03-2026_16-12-02.mp3</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="176" t="inlineStr">
+      <c r="A104" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:12:20</t>
         </is>
       </c>
-      <c r="B104" s="176" t="inlineStr">
+      <c r="B104" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C104" s="176" t="inlineStr">
+      <c r="C104" s="192" t="inlineStr">
         <is>
           <t>Nagacela</t>
         </is>
       </c>
-      <c r="D104" s="176" t="inlineStr">
+      <c r="D104" s="192" t="inlineStr">
         <is>
           <t>Poupança Premiada</t>
         </is>
       </c>
-      <c r="E104" s="176" t="inlineStr">
+      <c r="E104" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4904,34 +4907,34 @@
           <t>Logo aqui no Toca Todas com Bruno e Barreto, Paula Fernandes, teve também o Ale Vieira com o Kleber e Cauã e o Foguinho. 4 e 12, ótima tarde pra você. Não saia daí, já já tem muito mais músicas aqui n</t>
         </is>
       </c>
-      <c r="G104" s="176" t="inlineStr">
+      <c r="G104" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Nagacela__Poupanca_Premiada__11-03-2026_16-12-20.mp3</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="176" t="inlineStr">
+      <c r="A105" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:12:38</t>
         </is>
       </c>
-      <c r="B105" s="176" t="inlineStr">
+      <c r="B105" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C105" s="176" t="inlineStr">
+      <c r="C105" s="192" t="inlineStr">
         <is>
           <t>Cicrede</t>
         </is>
       </c>
-      <c r="D105" s="176" t="inlineStr">
+      <c r="D105" s="192" t="inlineStr">
         <is>
           <t>Poupança Premiada</t>
         </is>
       </c>
-      <c r="E105" s="176" t="inlineStr">
+      <c r="E105" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4941,34 +4944,34 @@
           <t>Aqui é a Nacastela, é hora de sonhar alto, a poupança premiada Cicrede tá aí! Se crede, poupa ou se é premiada, pra fazer tudo o que você sonhava, tem milhões em prêmios toda semana. São mais de 600 g</t>
         </is>
       </c>
-      <c r="G105" s="176" t="inlineStr">
+      <c r="G105" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Cicrede__Poupanca_Premiada__11-03-2026_16-12-38.mp3</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="176" t="inlineStr">
+      <c r="A106" s="192" t="inlineStr">
         <is>
           <t>11/03/2026 16:12:56</t>
         </is>
       </c>
-      <c r="B106" s="176" t="inlineStr">
+      <c r="B106" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C106" s="176" t="inlineStr">
+      <c r="C106" s="192" t="inlineStr">
         <is>
           <t>Poupa Bem das Credito</t>
         </is>
       </c>
-      <c r="D106" s="176" t="inlineStr">
+      <c r="D106" s="192" t="inlineStr">
         <is>
           <t>Crédito</t>
         </is>
       </c>
-      <c r="E106" s="176" t="inlineStr">
+      <c r="E106" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -4978,7 +4981,7 @@
           <t>5 milhões em prêmios em dinheiro. Poupa o nosso crédito e concorra. Poupa o nosso crédito e concorra. Vamos começar o vinculado, título e capitalização da moradia de incentivo. Emitido, vinculado e ca</t>
         </is>
       </c>
-      <c r="G106" s="176" t="inlineStr">
+      <c r="G106" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Poupa_Bem_das_Credito__Credito__11-03-2026_16-12-56__ad1.mp3</t>
         </is>
@@ -5059,27 +5062,27 @@
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="176" t="inlineStr">
+      <c r="A109" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:04:48</t>
         </is>
       </c>
-      <c r="B109" s="176" t="inlineStr">
+      <c r="B109" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C109" s="176" t="inlineStr">
+      <c r="C109" s="192" t="inlineStr">
         <is>
           <t>Ótica Fabrilein</t>
         </is>
       </c>
-      <c r="D109" s="176" t="inlineStr">
+      <c r="D109" s="192" t="inlineStr">
         <is>
           <t>Lentes multifocais digitais Noblen</t>
         </is>
       </c>
-      <c r="E109" s="176" t="inlineStr">
+      <c r="E109" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5089,34 +5092,34 @@
           <t>Quando o assunto é visão, a ótica Fabrilein é referência. Atendimento diferenciado com profissionais preparados pra orientar você com atenção e confiança. As lentes são produzidas com alta tecnologia,</t>
         </is>
       </c>
-      <c r="G109" s="176" t="inlineStr">
+      <c r="G109" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Otica_Fabrilein__Lentes_multifocais_digitais_Noblen__12-03-2026_09-04-47.mp3</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="176" t="inlineStr">
+      <c r="A110" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:04:52</t>
         </is>
       </c>
-      <c r="B110" s="176" t="inlineStr">
+      <c r="B110" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C110" s="176" t="inlineStr">
+      <c r="C110" s="192" t="inlineStr">
         <is>
           <t>Óticas FabriLem</t>
         </is>
       </c>
-      <c r="D110" s="176" t="inlineStr">
+      <c r="D110" s="192" t="inlineStr">
         <is>
           <t>lentes multifocais digitais Noblen e lentes de visão simples</t>
         </is>
       </c>
-      <c r="E110" s="176" t="inlineStr">
+      <c r="E110" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5126,7 +5129,7 @@
           <t>do precisão e conforto para o dia a dia e tem promoção especial. Na compra do primeiro par de lentes multifocais digitais Noblen com antirreflexo, o segundo par é grátis. E mais, lentes de visão simpl</t>
         </is>
       </c>
-      <c r="G110" s="176" t="inlineStr">
+      <c r="G110" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Oticas_FabriLem__lentes_multifocais_digitais_Noblen_e_lentes_de_visao_simples__12-03-2026_09-04-52__ad1.mp3</t>
         </is>
@@ -5170,27 +5173,27 @@
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="176" t="inlineStr">
+      <c r="A112" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:05:08</t>
         </is>
       </c>
-      <c r="B112" s="176" t="inlineStr">
+      <c r="B112" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C112" s="176" t="inlineStr">
+      <c r="C112" s="192" t="inlineStr">
         <is>
           <t>Óticas Fabrilem</t>
         </is>
       </c>
-      <c r="D112" s="176" t="inlineStr">
+      <c r="D112" s="192" t="inlineStr">
         <is>
           <t>lentes</t>
         </is>
       </c>
-      <c r="E112" s="176" t="inlineStr">
+      <c r="E112" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5200,34 +5203,34 @@
           <t>em até dez vezes de dezoito e noventa. Visite a loja na Rua Brasil Esquina com a Cuiabá em Catanduva. Óticas Fabrilem, a fábrica da sua lente. Amaral Centro Automotivo Multimarcas agradece a todos o c</t>
         </is>
       </c>
-      <c r="G112" s="176" t="inlineStr">
+      <c r="G112" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Oticas_Fabrilem__lentes__12-03-2026_09-05-08__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="176" t="inlineStr">
+      <c r="A113" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:05:08</t>
         </is>
       </c>
-      <c r="B113" s="176" t="inlineStr">
+      <c r="B113" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C113" s="176" t="inlineStr">
+      <c r="C113" s="192" t="inlineStr">
         <is>
           <t>Amaral Centro Automotivo Multimarcas</t>
         </is>
       </c>
-      <c r="D113" s="176" t="inlineStr">
+      <c r="D113" s="192" t="inlineStr">
         <is>
           <t>serviços automotivos</t>
         </is>
       </c>
-      <c r="E113" s="176" t="inlineStr">
+      <c r="E113" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5237,34 +5240,34 @@
           <t>em até dez vezes de dezoito e noventa. Visite a loja na Rua Brasil Esquina com a Cuiabá em Catanduva. Óticas Fabrilem, a fábrica da sua lente. Amaral Centro Automotivo Multimarcas agradece a todos o c</t>
         </is>
       </c>
-      <c r="G113" s="176" t="inlineStr">
+      <c r="G113" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Amaral_Centro_Automotivo_Multimarcas__servicos_automotivos__12-03-2026_09-05-08__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="176" t="inlineStr">
+      <c r="A114" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:05:13</t>
         </is>
       </c>
-      <c r="B114" s="176" t="inlineStr">
+      <c r="B114" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C114" s="176" t="inlineStr">
+      <c r="C114" s="192" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D114" s="176" t="inlineStr">
+      <c r="D114" s="192" t="inlineStr">
         <is>
           <t>Produtos alimentícios (frango, peito, arroz, café, batata, Amaciente P)</t>
         </is>
       </c>
-      <c r="E114" s="176" t="inlineStr">
+      <c r="E114" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5274,34 +5277,34 @@
           <t>Onde? No Max. Frango a passarinho lar, um quilo oito e noventa e sete. Peito com osso, dez e noventa e sete o quilo. Arroz do tripar, cinco quilos, onze e noventa e nove. Café Macali, quinhentos grama</t>
         </is>
       </c>
-      <c r="G114" s="176" t="inlineStr">
+      <c r="G114" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Max__Produtos_alimenticios__frango__peito__arroz__cafe__batata__A__12-03-2026_09-05-13__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="176" t="inlineStr">
+      <c r="A115" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:05:13</t>
         </is>
       </c>
-      <c r="B115" s="176" t="inlineStr">
+      <c r="B115" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C115" s="176" t="inlineStr">
+      <c r="C115" s="192" t="inlineStr">
         <is>
           <t>Tacarejo</t>
         </is>
       </c>
-      <c r="D115" s="176" t="inlineStr">
+      <c r="D115" s="192" t="inlineStr">
         <is>
           <t>Páscoa</t>
         </is>
       </c>
-      <c r="E115" s="176" t="inlineStr">
+      <c r="E115" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5311,34 +5314,34 @@
           <t>Onde? No Max. Frango a passarinho lar, um quilo oito e noventa e sete. Peito com osso, dez e noventa e sete o quilo. Arroz do tripar, cinco quilos, onze e noventa e nove. Café Macali, quinhentos grama</t>
         </is>
       </c>
-      <c r="G115" s="176" t="inlineStr">
+      <c r="G115" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Tacarejo__Pascoa__12-03-2026_09-05-13__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="176" t="inlineStr">
+      <c r="A116" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:05:13</t>
         </is>
       </c>
-      <c r="B116" s="176" t="inlineStr">
+      <c r="B116" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C116" s="176" t="inlineStr">
+      <c r="C116" s="192" t="inlineStr">
         <is>
           <t>Pan</t>
         </is>
       </c>
-      <c r="D116" s="176" t="inlineStr">
+      <c r="D116" s="192" t="inlineStr">
         <is>
           <t>Lojas</t>
         </is>
       </c>
-      <c r="E116" s="176" t="inlineStr">
+      <c r="E116" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5348,34 +5351,34 @@
           <t>Onde? No Max. Frango a passarinho lar, um quilo oito e noventa e sete. Peito com osso, dez e noventa e sete o quilo. Arroz do tripar, cinco quilos, onze e noventa e nove. Café Macali, quinhentos grama</t>
         </is>
       </c>
-      <c r="G116" s="176" t="inlineStr">
+      <c r="G116" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Pan__Lojas__12-03-2026_09-05-13__ad3.mp3</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="176" t="inlineStr">
+      <c r="A117" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:05:31</t>
         </is>
       </c>
-      <c r="B117" s="176" t="inlineStr">
+      <c r="B117" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C117" s="176" t="inlineStr">
+      <c r="C117" s="192" t="inlineStr">
         <is>
           <t>Bazar Chique</t>
         </is>
       </c>
-      <c r="D117" s="176" t="inlineStr">
+      <c r="D117" s="192" t="inlineStr">
         <is>
           <t>Roupas, acessórios, calçados, óticas</t>
         </is>
       </c>
-      <c r="E117" s="176" t="inlineStr">
+      <c r="E117" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5385,34 +5388,34 @@
           <t>Não, não pode. Acione o WhatsApp da Planca. 1735232001 As melhores lojas de Catanduva, reunidas em um único lugar com até 60% off. Você já sabe de qual evento estamos falando? Bazar chique, é claro. R</t>
         </is>
       </c>
-      <c r="G117" s="176" t="inlineStr">
+      <c r="G117" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Bazar_Chique__Roupas__acessorios__calcados__oticas__12-03-2026_09-05-30.mp3</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="176" t="inlineStr">
+      <c r="A118" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:05:41</t>
         </is>
       </c>
-      <c r="B118" s="176" t="inlineStr">
+      <c r="B118" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C118" s="176" t="inlineStr">
+      <c r="C118" s="192" t="inlineStr">
         <is>
           <t>Loja de vestidos de noiva</t>
         </is>
       </c>
-      <c r="D118" s="176" t="inlineStr">
+      <c r="D118" s="192" t="inlineStr">
         <is>
           <t>Vestido de noiva</t>
         </is>
       </c>
-      <c r="E118" s="176" t="inlineStr">
+      <c r="E118" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5422,34 +5425,34 @@
           <t>e pintura, parcerias com grandes seguradoras, bateu, amassou, amarao, consertou, Rua Martinópolis, o telefone 30459137. Você que vai casar, pare um instante. Imagine encontrar um vestido de noiva mara</t>
         </is>
       </c>
-      <c r="G118" s="176" t="inlineStr">
+      <c r="G118" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Loja_de_vestidos_de_noiva__Vestido_de_noiva__12-03-2026_09-05-41__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="176" t="inlineStr">
+      <c r="A119" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:05:41</t>
         </is>
       </c>
-      <c r="B119" s="176" t="inlineStr">
+      <c r="B119" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C119" s="176" t="inlineStr">
+      <c r="C119" s="192" t="inlineStr">
         <is>
           <t>Oficina de consertos</t>
         </is>
       </c>
-      <c r="D119" s="176" t="inlineStr">
+      <c r="D119" s="192" t="inlineStr">
         <is>
           <t>Serviços de conserto de veículos</t>
         </is>
       </c>
-      <c r="E119" s="176" t="inlineStr">
+      <c r="E119" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5459,34 +5462,34 @@
           <t>e pintura, parcerias com grandes seguradoras, bateu, amassou, amarao, consertou, Rua Martinópolis, o telefone 30459137. Você que vai casar, pare um instante. Imagine encontrar um vestido de noiva mara</t>
         </is>
       </c>
-      <c r="G119" s="176" t="inlineStr">
+      <c r="G119" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Oficina_de_consertos__Servicos_de_conserto_de_veiculos__12-03-2026_09-05-41__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="176" t="inlineStr">
+      <c r="A120" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:05:58</t>
         </is>
       </c>
-      <c r="B120" s="176" t="inlineStr">
+      <c r="B120" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C120" s="176" t="inlineStr">
+      <c r="C120" s="192" t="inlineStr">
         <is>
           <t>Projeto Corujas do Bem</t>
         </is>
       </c>
-      <c r="D120" s="176" t="inlineStr">
+      <c r="D120" s="192" t="inlineStr">
         <is>
           <t>Vestidos de noiva</t>
         </is>
       </c>
-      <c r="E120" s="176" t="inlineStr">
+      <c r="E120" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5496,34 +5499,34 @@
           <t>você que vai casar pare um instante imagine encontrar um vestido de noiva maravilhoso por apenas duzentos reais sim duzentos reais no dia vinte e oito de março sábado a partir das dez horas da manhã a</t>
         </is>
       </c>
-      <c r="G120" s="176" t="inlineStr">
+      <c r="G120" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Projeto_Corujas_do_Bem__Vestidos_de_noiva__12-03-2026_09-05-58.mp3</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="176" t="inlineStr">
+      <c r="A121" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:06:14</t>
         </is>
       </c>
-      <c r="B121" s="176" t="inlineStr">
+      <c r="B121" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C121" s="176" t="inlineStr">
+      <c r="C121" s="192" t="inlineStr">
         <is>
           <t>Projeto Corujas do Bem</t>
         </is>
       </c>
-      <c r="D121" s="176" t="inlineStr">
+      <c r="D121" s="192" t="inlineStr">
         <is>
           <t>Bazar de vestidos de noiva</t>
         </is>
       </c>
-      <c r="E121" s="176" t="inlineStr">
+      <c r="E121" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5533,34 +5536,34 @@
           <t>Oito de março, sábado, a partir das dez horas da manhã, acontece o grande bazar de vestidos de noiva em prol do projeto Corujas do Bem. Serão mais de oitenta vestidos de noiva. Lindos, esperando você.</t>
         </is>
       </c>
-      <c r="G121" s="176" t="inlineStr">
+      <c r="G121" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Projeto_Corujas_do_Bem__Bazar_de_vestidos_de_noiva__12-03-2026_09-06-14.mp3</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="176" t="inlineStr">
+      <c r="A122" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:06:25</t>
         </is>
       </c>
-      <c r="B122" s="176" t="inlineStr">
+      <c r="B122" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C122" s="176" t="inlineStr">
+      <c r="C122" s="192" t="inlineStr">
         <is>
           <t>Paz Previne</t>
         </is>
       </c>
-      <c r="D122" s="176" t="inlineStr">
+      <c r="D122" s="192" t="inlineStr">
         <is>
           <t>serviços de saúde</t>
         </is>
       </c>
-      <c r="E122" s="176" t="inlineStr">
+      <c r="E122" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5570,34 +5573,34 @@
           <t>da saúde, além de serviços de excelência e confiança. E contando em breve com o novo prédio do Paz Previne, com maior capacidade de atendimento e novos profissionais e atividades para o corpo e a ment</t>
         </is>
       </c>
-      <c r="G122" s="176" t="inlineStr">
+      <c r="G122" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Paz_Previne__servicos_de_saude__12-03-2026_09-06-25.mp3</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="176" t="inlineStr">
+      <c r="A123" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:06:31</t>
         </is>
       </c>
-      <c r="B123" s="176" t="inlineStr">
+      <c r="B123" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C123" s="176" t="inlineStr">
+      <c r="C123" s="192" t="inlineStr">
         <is>
           <t>Nagastela</t>
         </is>
       </c>
-      <c r="D123" s="176" t="inlineStr">
+      <c r="D123" s="192" t="inlineStr">
         <is>
           <t>Poupança Premiada</t>
         </is>
       </c>
-      <c r="E123" s="176" t="inlineStr">
+      <c r="E123" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5607,34 +5610,34 @@
           <t xml:space="preserve">e trinta e três sábado dia vinte e oito a partir das dez da manhã. Informações WhatsApp dezessete nove dois zero zero dois cinco oito zero cinco. Aqui é a Nagastela, é hora de sonhar alto. A poupança </t>
         </is>
       </c>
-      <c r="G123" s="176" t="inlineStr">
+      <c r="G123" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Nagastela__Poupanca_Premiada__12-03-2026_09-06-31.mp3</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="176" t="inlineStr">
+      <c r="A124" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:06:44</t>
         </is>
       </c>
-      <c r="B124" s="176" t="inlineStr">
+      <c r="B124" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C124" s="176" t="inlineStr">
+      <c r="C124" s="192" t="inlineStr">
         <is>
           <t>São Geraldo Tintas</t>
         </is>
       </c>
-      <c r="D124" s="176" t="inlineStr">
+      <c r="D124" s="192" t="inlineStr">
         <is>
           <t>tintas</t>
         </is>
       </c>
-      <c r="E124" s="176" t="inlineStr">
+      <c r="E124" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5644,34 +5647,34 @@
           <t>Paz, saúde ao seu alcance. Jovem Fã. É tinta, São Geraldo Tintas. Pinte o que quiser nas cores que vieram a sua imaginação. É tinta, São Geraldo Tintas. Pra imóveis, automóveis, acessórios, qualidade,</t>
         </is>
       </c>
-      <c r="G124" s="176" t="inlineStr">
+      <c r="G124" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Sao_Geraldo_Tintas__tintas__12-03-2026_09-06-44.mp3</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="176" t="inlineStr">
+      <c r="A125" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:06:47</t>
         </is>
       </c>
-      <c r="B125" s="176" t="inlineStr">
+      <c r="B125" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C125" s="176" t="inlineStr">
+      <c r="C125" s="192" t="inlineStr">
         <is>
           <t>Poupos e Noci Crede</t>
         </is>
       </c>
-      <c r="D125" s="176" t="inlineStr">
+      <c r="D125" s="192" t="inlineStr">
         <is>
           <t>Sorteio e prêmios</t>
         </is>
       </c>
-      <c r="E125" s="176" t="inlineStr">
+      <c r="E125" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5681,34 +5684,34 @@
           <t>O Pino se Crede tá aí! O Pino se Crede, Poupos é premiada E pra fazer tudo o que você sonhava Tem milhões em prêmios toda semana São mais de 600 ganhadores 5 milhões em prêmios em dinheiro Poupo e Noc</t>
         </is>
       </c>
-      <c r="G125" s="176" t="inlineStr">
+      <c r="G125" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Poupos_e_Noci_Crede__Sorteio_e_premios__12-03-2026_09-06-47.mp3</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="176" t="inlineStr">
+      <c r="A126" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:07:01</t>
         </is>
       </c>
-      <c r="B126" s="176" t="inlineStr">
+      <c r="B126" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C126" s="176" t="inlineStr">
+      <c r="C126" s="192" t="inlineStr">
         <is>
           <t>São Geraldo Tintas</t>
         </is>
       </c>
-      <c r="D126" s="176" t="inlineStr">
+      <c r="D126" s="192" t="inlineStr">
         <is>
           <t>tintas</t>
         </is>
       </c>
-      <c r="E126" s="176" t="inlineStr">
+      <c r="E126" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5718,34 +5721,34 @@
           <t>pra imóveis, automóveis, acessórios, qualidade, preço bom. É tinta, é São Geraldo Tintas. Em Catanduva, na sete de setembro sessenta e dois e José Nelson Machado mil duzentos e treze. Olá, eu sou o do</t>
         </is>
       </c>
-      <c r="G126" s="176" t="inlineStr">
+      <c r="G126" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Sao_Geraldo_Tintas__tintas__12-03-2026_09-07-01__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="176" t="inlineStr">
+      <c r="A127" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:07:01</t>
         </is>
       </c>
-      <c r="B127" s="176" t="inlineStr">
+      <c r="B127" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C127" s="176" t="inlineStr">
+      <c r="C127" s="192" t="inlineStr">
         <is>
           <t>Oralfai Catanduva</t>
         </is>
       </c>
-      <c r="D127" s="176" t="inlineStr">
+      <c r="D127" s="192" t="inlineStr">
         <is>
           <t>tratamentos odontológicos</t>
         </is>
       </c>
-      <c r="E127" s="176" t="inlineStr">
+      <c r="E127" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5755,34 +5758,34 @@
           <t>pra imóveis, automóveis, acessórios, qualidade, preço bom. É tinta, é São Geraldo Tintas. Em Catanduva, na sete de setembro sessenta e dois e José Nelson Machado mil duzentos e treze. Olá, eu sou o do</t>
         </is>
       </c>
-      <c r="G127" s="176" t="inlineStr">
+      <c r="G127" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Oralfai_Catanduva__tratamentos_odontologicos__12-03-2026_09-07-01__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="176" t="inlineStr">
+      <c r="A128" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:07:38</t>
         </is>
       </c>
-      <c r="B128" s="176" t="inlineStr">
+      <c r="B128" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C128" s="176" t="inlineStr">
+      <c r="C128" s="192" t="inlineStr">
         <is>
           <t>Oral Pai Catanduva</t>
         </is>
       </c>
-      <c r="D128" s="176" t="inlineStr">
+      <c r="D128" s="192" t="inlineStr">
         <is>
           <t>serviços odontológicos</t>
         </is>
       </c>
-      <c r="E128" s="176" t="inlineStr">
+      <c r="E128" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5792,34 +5795,34 @@
           <t>Oral Pai Catanduva para voltar a sorrir. Oral Pai Catanduva, Rua Minas Gerais, 586. Acesse oralfaicatanduva.com.br ou siga no Instagram, arroba Oral Pai Catanduva. Se liga já de volta! Essa é a número</t>
         </is>
       </c>
-      <c r="G128" s="176" t="inlineStr">
+      <c r="G128" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Oral_Pai_Catanduva__servicos_odontologicos__12-03-2026_09-07-38.mp3</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="176" t="inlineStr">
+      <c r="A129" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:12:18</t>
         </is>
       </c>
-      <c r="B129" s="176" t="inlineStr">
+      <c r="B129" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C129" s="176" t="inlineStr">
+      <c r="C129" s="192" t="inlineStr">
         <is>
           <t>supermercado</t>
         </is>
       </c>
-      <c r="D129" s="176" t="inlineStr">
+      <c r="D129" s="192" t="inlineStr">
         <is>
           <t>supermercado</t>
         </is>
       </c>
-      <c r="E129" s="176" t="inlineStr">
+      <c r="E129" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5829,34 +5832,34 @@
           <t>Comprou e foi ao caixa 7, tudo pronto e nada acontecia E um silêncio após a pergunta, de que forma que ela pagaria De repente o serviço de som, anuncia o seguinte recado Estamos completando hoje, 7 an</t>
         </is>
       </c>
-      <c r="G129" s="176" t="inlineStr">
+      <c r="G129" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__supermercado__supermercado__12-03-2026_09-12-17.mp3</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="176" t="inlineStr">
+      <c r="A130" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:12:34</t>
         </is>
       </c>
-      <c r="B130" s="176" t="inlineStr">
+      <c r="B130" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C130" s="176" t="inlineStr">
+      <c r="C130" s="192" t="inlineStr">
         <is>
           <t>supermercado</t>
         </is>
       </c>
-      <c r="D130" s="176" t="inlineStr">
+      <c r="D130" s="192" t="inlineStr">
         <is>
           <t>produtos do supermercado</t>
         </is>
       </c>
-      <c r="E130" s="176" t="inlineStr">
+      <c r="E130" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5866,34 +5869,34 @@
           <t>Serviço de som, anuncia o seguinte recado Estamos completando hoje, sete anos de supermercado E como é nosso aniversário, um cliente vamos premiar Quem estiver no caixa sete, não precisa sua conta pag</t>
         </is>
       </c>
-      <c r="G130" s="176" t="inlineStr">
+      <c r="G130" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__supermercado__produtos_do_supermercado__12-03-2026_09-12-34.mp3</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="176" t="inlineStr">
+      <c r="A131" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:19:26</t>
         </is>
       </c>
-      <c r="B131" s="176" t="inlineStr">
+      <c r="B131" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C131" s="176" t="inlineStr">
+      <c r="C131" s="192" t="inlineStr">
         <is>
           <t>Grupo Moreschi</t>
         </is>
       </c>
-      <c r="D131" s="176" t="inlineStr">
+      <c r="D131" s="192" t="inlineStr">
         <is>
           <t>Bisteca Suína, Costela Bovina Ripa, Costel Duro Bovino</t>
         </is>
       </c>
-      <c r="E131" s="176" t="inlineStr">
+      <c r="E131" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5903,34 +5906,34 @@
           <t>E aí Não saia daí, já já tem muito mais músicas aqui na Band FM Band FM Confira as ofertas do Grupo Moreschi Bisteca Suína, 14,99 o quilo Costela Bovina Ripa, quilo 21,99 Costel Duro Bovino, quilo 36,</t>
         </is>
       </c>
-      <c r="G131" s="176" t="inlineStr">
+      <c r="G131" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Grupo_Moreschi__Bisteca_Suina__Costela_Bovina_Ripa__Costel_Duro_Bovino__12-03-2026_09-19-26.mp3</t>
         </is>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="176" t="inlineStr">
+      <c r="A132" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:20:56</t>
         </is>
       </c>
-      <c r="B132" s="176" t="inlineStr">
+      <c r="B132" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C132" s="176" t="inlineStr">
+      <c r="C132" s="192" t="inlineStr">
         <is>
           <t>Beto Salgados</t>
         </is>
       </c>
-      <c r="D132" s="176" t="inlineStr">
+      <c r="D132" s="192" t="inlineStr">
         <is>
           <t>salgados</t>
         </is>
       </c>
-      <c r="E132" s="176" t="inlineStr">
+      <c r="E132" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5940,34 +5943,34 @@
           <t xml:space="preserve">Agora também, na Avenida Benedito Zancaner, 1481, ao lado do Proença Supermercados. Só tintas, tudo em tintas. Oi gente, aqui quem tá falando é o Leizinho da Turma do Pagode. É bem melhor, é Band FM. </t>
         </is>
       </c>
-      <c r="G132" s="176" t="inlineStr">
+      <c r="G132" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Beto_Salgados__salgados__12-03-2026_09-20-56.mp3</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="176" t="inlineStr">
+      <c r="A133" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:22:25</t>
         </is>
       </c>
-      <c r="B133" s="176" t="inlineStr">
+      <c r="B133" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C133" s="176" t="inlineStr">
+      <c r="C133" s="192" t="inlineStr">
         <is>
           <t>Autoposto Campeão</t>
         </is>
       </c>
-      <c r="D133" s="176" t="inlineStr">
+      <c r="D133" s="192" t="inlineStr">
         <is>
           <t>serviço de embelezamento automotivo</t>
         </is>
       </c>
-      <c r="E133" s="176" t="inlineStr">
+      <c r="E133" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -5977,34 +5980,34 @@
           <t>E pra deixar o seu carro ainda mais lindo, confira o estúdio de embelezamento automotivo. Transforme o seu veículo em um verdadeiro campeão nas ruas. Autoposto Campeão, onde a qualidade é campeã e voc</t>
         </is>
       </c>
-      <c r="G133" s="176" t="inlineStr">
+      <c r="G133" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Autoposto_Campeao__servico_de_embelezamento_automotivo__12-03-2026_09-22-25.mp3</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="176" t="inlineStr">
+      <c r="A134" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:26:19</t>
         </is>
       </c>
-      <c r="B134" s="176" t="inlineStr">
+      <c r="B134" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C134" s="176" t="inlineStr">
+      <c r="C134" s="192" t="inlineStr">
         <is>
           <t>Vive empreendimentos</t>
         </is>
       </c>
-      <c r="D134" s="176" t="inlineStr">
+      <c r="D134" s="192" t="inlineStr">
         <is>
           <t>Imóveis no Boulevard Baivive</t>
         </is>
       </c>
-      <c r="E134" s="176" t="inlineStr">
+      <c r="E134" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6014,34 +6017,34 @@
           <t>do tempo Jovem Pan. Jovem Pan Brasil Você está ouvindo Manhã Pan Catanduva Oferecimento Doutor Alex Baraldo Portes, otorrino laringologista RQE 64202 Vive empreendimentos Unifipa Catanduva Doutor Cris</t>
         </is>
       </c>
-      <c r="G134" s="176" t="inlineStr">
+      <c r="G134" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Vive_empreendimentos__Imoveis_no_Boulevard_Baivive__12-03-2026_09-26-19__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="176" t="inlineStr">
+      <c r="A135" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:26:19</t>
         </is>
       </c>
-      <c r="B135" s="176" t="inlineStr">
+      <c r="B135" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C135" s="176" t="inlineStr">
+      <c r="C135" s="192" t="inlineStr">
         <is>
           <t>GA Proteção Veicular</t>
         </is>
       </c>
-      <c r="D135" s="176" t="inlineStr">
+      <c r="D135" s="192" t="inlineStr">
         <is>
           <t>Proteção veicular</t>
         </is>
       </c>
-      <c r="E135" s="176" t="inlineStr">
+      <c r="E135" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6051,34 +6054,34 @@
           <t>do tempo Jovem Pan. Jovem Pan Brasil Você está ouvindo Manhã Pan Catanduva Oferecimento Doutor Alex Baraldo Portes, otorrino laringologista RQE 64202 Vive empreendimentos Unifipa Catanduva Doutor Cris</t>
         </is>
       </c>
-      <c r="G135" s="176" t="inlineStr">
+      <c r="G135" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__GA_Protecao_Veicular__Protecao_veicular__12-03-2026_09-26-19__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="176" t="inlineStr">
+      <c r="A136" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:26:37</t>
         </is>
       </c>
-      <c r="B136" s="176" t="inlineStr">
+      <c r="B136" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C136" s="176" t="inlineStr">
+      <c r="C136" s="192" t="inlineStr">
         <is>
           <t>Tecnodin</t>
         </is>
       </c>
-      <c r="D136" s="176" t="inlineStr">
+      <c r="D136" s="192" t="inlineStr">
         <is>
           <t>aparelhos de fitness</t>
         </is>
       </c>
-      <c r="E136" s="176" t="inlineStr">
+      <c r="E136" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6088,34 +6091,34 @@
           <t>Unifipa Catanduva, doutor Cristiano Herrera e GA Proteção Veicular. No Boulevard Baivive, cada detalhe é pensado para elevar o bem-estar dos futuros moradores. A Academia do Empreendimento será equipa</t>
         </is>
       </c>
-      <c r="G136" s="176" t="inlineStr">
+      <c r="G136" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Tecnodin__aparelhos_de_fitness__12-03-2026_09-26-37__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="176" t="inlineStr">
+      <c r="A137" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:26:37</t>
         </is>
       </c>
-      <c r="B137" s="176" t="inlineStr">
+      <c r="B137" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C137" s="176" t="inlineStr">
+      <c r="C137" s="192" t="inlineStr">
         <is>
           <t>Boulevard by Divi</t>
         </is>
       </c>
-      <c r="D137" s="176" t="inlineStr">
+      <c r="D137" s="192" t="inlineStr">
         <is>
           <t>imóvel (Boulevard Baivive)</t>
         </is>
       </c>
-      <c r="E137" s="176" t="inlineStr">
+      <c r="E137" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6125,34 +6128,34 @@
           <t>Unifipa Catanduva, doutor Cristiano Herrera e GA Proteção Veicular. No Boulevard Baivive, cada detalhe é pensado para elevar o bem-estar dos futuros moradores. A Academia do Empreendimento será equipa</t>
         </is>
       </c>
-      <c r="G137" s="176" t="inlineStr">
+      <c r="G137" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Boulevard_by_Divi__imovel__Boulevard_Baivive__12-03-2026_09-26-37__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="176" t="inlineStr">
+      <c r="A138" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:27:11</t>
         </is>
       </c>
-      <c r="B138" s="176" t="inlineStr">
+      <c r="B138" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C138" s="176" t="inlineStr">
+      <c r="C138" s="192" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D138" s="176" t="inlineStr">
+      <c r="D138" s="192" t="inlineStr">
         <is>
           <t>Açude (frango, peito com osso, arroz, café)</t>
         </is>
       </c>
-      <c r="E138" s="176" t="inlineStr">
+      <c r="E138" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6162,34 +6165,34 @@
           <t xml:space="preserve">Se nos fugir e ouvir a voz, ser desconhecido, eu sei. Onda Zedis. O jogo de esquinho de Páscoa já está liberado. Com preço baixo, então, não tem discussão. Vem aproveitar as melhores ofertas de açude </t>
         </is>
       </c>
-      <c r="G138" s="176" t="inlineStr">
+      <c r="G138" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Max__Acude__frango__peito_com_osso__arroz__cafe__12-03-2026_09-27-11.mp3</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="176" t="inlineStr">
+      <c r="A139" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:27:13</t>
         </is>
       </c>
-      <c r="B139" s="176" t="inlineStr">
+      <c r="B139" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C139" s="176" t="inlineStr">
+      <c r="C139" s="192" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D139" s="176" t="inlineStr">
+      <c r="D139" s="192" t="inlineStr">
         <is>
           <t>Produtos de açougue e outros</t>
         </is>
       </c>
-      <c r="E139" s="176" t="inlineStr">
+      <c r="E139" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6199,34 +6202,34 @@
           <t xml:space="preserve">11 24 00. O que você quer de Páscoa, Chapari Barado? Com preço baixo, então, não tem discussão. Vem aproveitar as melhores ofertas de açougue no Max. Frango a passarinho lar, 1,98 kg. Peito com osso, </t>
         </is>
       </c>
-      <c r="G139" s="176" t="inlineStr">
+      <c r="G139" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Max__Produtos_de_acougue_e_outros__12-03-2026_09-27-13.mp3</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="176" t="inlineStr">
+      <c r="A140" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:27:27</t>
         </is>
       </c>
-      <c r="B140" s="176" t="inlineStr">
+      <c r="B140" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C140" s="176" t="inlineStr">
+      <c r="C140" s="192" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D140" s="176" t="inlineStr">
+      <c r="D140" s="192" t="inlineStr">
         <is>
           <t>Produtos de açougue e outros</t>
         </is>
       </c>
-      <c r="E140" s="176" t="inlineStr">
+      <c r="E140" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6236,34 +6239,34 @@
           <t>O Baixitão não tem discussão. Vem aproveitar as melhores ofertas de açougue no Max. Frango a passarinho lar, 1,987. Peito com osso, 10,97 o quilo. Arroz do tripar, 5,1199. Café Macali, 500 gramas, 19,</t>
         </is>
       </c>
-      <c r="G140" s="176" t="inlineStr">
+      <c r="G140" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Max__Produtos_de_acougue_e_outros__12-03-2026_09-27-27.mp3</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="176" t="inlineStr">
+      <c r="A141" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:27:31</t>
         </is>
       </c>
-      <c r="B141" s="176" t="inlineStr">
+      <c r="B141" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C141" s="176" t="inlineStr">
+      <c r="C141" s="192" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D141" s="176" t="inlineStr">
+      <c r="D141" s="192" t="inlineStr">
         <is>
           <t>Páscoa</t>
         </is>
       </c>
-      <c r="E141" s="176" t="inlineStr">
+      <c r="E141" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6273,34 +6276,34 @@
           <t xml:space="preserve">Macali, quinhentos gramas, dezenove e noventa e oito. Batata, dois quilos a partir de dezenove e noventa. Amaciente P, dois litros, sete e quarenta e nove. A maior páscoa do atacarejo é no Max. Jovem </t>
         </is>
       </c>
-      <c r="G141" s="176" t="inlineStr">
+      <c r="G141" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Max__Pascoa__12-03-2026_09-27-31__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="176" t="inlineStr">
+      <c r="A142" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:27:31</t>
         </is>
       </c>
-      <c r="B142" s="176" t="inlineStr">
+      <c r="B142" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C142" s="176" t="inlineStr">
+      <c r="C142" s="192" t="inlineStr">
         <is>
           <t>Drogaria Economia</t>
         </is>
       </c>
-      <c r="D142" s="176" t="inlineStr">
+      <c r="D142" s="192" t="inlineStr">
         <is>
           <t>Medicamento</t>
         </is>
       </c>
-      <c r="E142" s="176" t="inlineStr">
+      <c r="E142" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6310,34 +6313,34 @@
           <t xml:space="preserve">Macali, quinhentos gramas, dezenove e noventa e oito. Batata, dois quilos a partir de dezenove e noventa. Amaciente P, dois litros, sete e quarenta e nove. A maior páscoa do atacarejo é no Max. Jovem </t>
         </is>
       </c>
-      <c r="G142" s="176" t="inlineStr">
+      <c r="G142" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Drogaria_Economia__Medicamento__12-03-2026_09-27-31__ad2.mp3</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="176" t="inlineStr">
+      <c r="A143" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:27:44</t>
         </is>
       </c>
-      <c r="B143" s="176" t="inlineStr">
+      <c r="B143" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C143" s="176" t="inlineStr">
+      <c r="C143" s="192" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="D143" s="176" t="inlineStr">
+      <c r="D143" s="192" t="inlineStr">
         <is>
           <t>Páscoa do atacarejo</t>
         </is>
       </c>
-      <c r="E143" s="176" t="inlineStr">
+      <c r="E143" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6347,7 +6350,7 @@
           <t>A partir de dezenove e noventa, a massa e ente P dois litros sete e quarenta e nove. A maior páscoa do atacarejo é do Max. Festa de São José, no bairro da Serrinha. Sábado, dia vinte e um. A partir da</t>
         </is>
       </c>
-      <c r="G143" s="176" t="inlineStr">
+      <c r="G143" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Max__Pascoa_do_atacarejo__12-03-2026_09-27-44__ad1.mp3</t>
         </is>
@@ -6428,27 +6431,27 @@
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="176" t="inlineStr">
+      <c r="A146" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:28:17</t>
         </is>
       </c>
-      <c r="B146" s="176" t="inlineStr">
+      <c r="B146" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C146" s="176" t="inlineStr">
+      <c r="C146" s="192" t="inlineStr">
         <is>
           <t>Clube de Tênis Catanduva</t>
         </is>
       </c>
-      <c r="D146" s="176" t="inlineStr">
+      <c r="D146" s="192" t="inlineStr">
         <is>
           <t>Shows e área VIP</t>
         </is>
       </c>
-      <c r="E146" s="176" t="inlineStr">
+      <c r="E146" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6458,34 +6461,34 @@
           <t>Serrinha, realização, membros da capela da Serrinha. Dia vinte de março, no Clube de Tênis Catanduva, dois super shows. Seu Moço, na abertura. E pela primeira vez na região, Praia Velha. Você só vai a</t>
         </is>
       </c>
-      <c r="G146" s="176" t="inlineStr">
+      <c r="G146" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Clube_de_Tenis_Catanduva__Shows_e_area_VIP__12-03-2026_09-28-17.mp3</t>
         </is>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="176" t="inlineStr">
+      <c r="A147" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:28:34</t>
         </is>
       </c>
-      <c r="B147" s="176" t="inlineStr">
+      <c r="B147" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C147" s="176" t="inlineStr">
+      <c r="C147" s="192" t="inlineStr">
         <is>
           <t>Clube de Tênis Catanduva</t>
         </is>
       </c>
-      <c r="D147" s="176" t="inlineStr">
+      <c r="D147" s="192" t="inlineStr">
         <is>
           <t>Ingressos para evento</t>
         </is>
       </c>
-      <c r="E147" s="176" t="inlineStr">
+      <c r="E147" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6495,34 +6498,34 @@
           <t>em palco trezentos e sessenta convites para a área VIP por oitenta reais a venda na Secretaria do Clube ou quero dois ingressos ponto com ponto BR. Seu moço e trai a velha. Dia vinte de março no Clube</t>
         </is>
       </c>
-      <c r="G147" s="176" t="inlineStr">
+      <c r="G147" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Clube_de_Tenis_Catanduva__Ingressos_para_evento__12-03-2026_09-28-34__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="176" t="inlineStr">
+      <c r="A148" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:28:34</t>
         </is>
       </c>
-      <c r="B148" s="176" t="inlineStr">
+      <c r="B148" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C148" s="176" t="inlineStr">
+      <c r="C148" s="192" t="inlineStr">
         <is>
           <t>Antunes</t>
         </is>
       </c>
-      <c r="D148" s="176" t="inlineStr">
+      <c r="D148" s="192" t="inlineStr">
         <is>
           <t>Ofertas no fim de semana do consumidor</t>
         </is>
       </c>
-      <c r="E148" s="176" t="inlineStr">
+      <c r="E148" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6532,7 +6535,7 @@
           <t>em palco trezentos e sessenta convites para a área VIP por oitenta reais a venda na Secretaria do Clube ou quero dois ingressos ponto com ponto BR. Seu moço e trai a velha. Dia vinte de março no Clube</t>
         </is>
       </c>
-      <c r="G148" s="176" t="inlineStr">
+      <c r="G148" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Antunes__Ofertas_no_fim_de_semana_do_consumidor__12-03-2026_09-28-34__ad2.mp3</t>
         </is>
@@ -6576,27 +6579,27 @@
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="176" t="inlineStr">
+      <c r="A150" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:28:44</t>
         </is>
       </c>
-      <c r="B150" s="176" t="inlineStr">
+      <c r="B150" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C150" s="176" t="inlineStr">
+      <c r="C150" s="192" t="inlineStr">
         <is>
           <t>Usina Nardini</t>
         </is>
       </c>
-      <c r="D150" s="176" t="inlineStr">
+      <c r="D150" s="192" t="inlineStr">
         <is>
           <t>Leilão de equipamentos agrícolas</t>
         </is>
       </c>
-      <c r="E150" s="176" t="inlineStr">
+      <c r="E150" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6606,34 +6609,34 @@
           <t xml:space="preserve">Jovem Pan. Jovem Pan. Jovem Pan. Jovem Pan. Jovem Pan. Jovem Pan. Atenção, atenção. Sensacional leilão online da usina Nardini, cidades de vista alegre do alto, São Paulo e Aporé, Goiás. São diversos </t>
         </is>
       </c>
-      <c r="G150" s="176" t="inlineStr">
+      <c r="G150" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Usina_Nardini__Leilao_de_equipamentos_agricolas__12-03-2026_09-28-44.mp3</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="176" t="inlineStr">
+      <c r="A151" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:28:50</t>
         </is>
       </c>
-      <c r="B151" s="176" t="inlineStr">
+      <c r="B151" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C151" s="176" t="inlineStr">
+      <c r="C151" s="192" t="inlineStr">
         <is>
           <t>Antunes Mais</t>
         </is>
       </c>
-      <c r="D151" s="176" t="inlineStr">
+      <c r="D151" s="192" t="inlineStr">
         <is>
           <t>Produtos alimentícios e de limpeza</t>
         </is>
       </c>
-      <c r="E151" s="176" t="inlineStr">
+      <c r="E151" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6643,34 +6646,34 @@
           <t>Seu moço e praia velha, dia vinte de março, no Clube de Tênis Catanduva. Fim de semana do consumidor no Antunes Mais, confira as ofertas do Clube do Precinho. Alcatra com maminha, bovina, bife, quilo,</t>
         </is>
       </c>
-      <c r="G151" s="176" t="inlineStr">
+      <c r="G151" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Antunes_Mais__Produtos_alimenticios_e_de_limpeza__12-03-2026_09-28-50.mp3</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="176" t="inlineStr">
+      <c r="A152" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:29:07</t>
         </is>
       </c>
-      <c r="B152" s="176" t="inlineStr">
+      <c r="B152" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C152" s="176" t="inlineStr">
+      <c r="C152" s="192" t="inlineStr">
         <is>
           <t>Supermercado</t>
         </is>
       </c>
-      <c r="D152" s="176" t="inlineStr">
+      <c r="D152" s="192" t="inlineStr">
         <is>
           <t>Bisteca suína, milho verde, amaciante para roupas Baby Soft, papel higiênico personal VIP</t>
         </is>
       </c>
-      <c r="E152" s="176" t="inlineStr">
+      <c r="E152" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6680,7 +6683,7 @@
           <t>e noventa e oito, bisteca suína, quatorze e noventa e nove o quilo, milho verde, bandeja, cinco e noventa e nove, amaciante para roupas Baby Soft, dois litros, seis e noventa e nove, papel higiênico p</t>
         </is>
       </c>
-      <c r="G152" s="176" t="inlineStr">
+      <c r="G152" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Supermercado__Bisteca_suina__milho_verde__amaciante_para_roupas_Baby_Soft___12-03-2026_09-29-07.mp3</t>
         </is>
@@ -6761,27 +6764,27 @@
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="176" t="inlineStr">
+      <c r="A155" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:42:02</t>
         </is>
       </c>
-      <c r="B155" s="176" t="inlineStr">
+      <c r="B155" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C155" s="176" t="inlineStr">
+      <c r="C155" s="192" t="inlineStr">
         <is>
           <t>Cressol</t>
         </is>
       </c>
-      <c r="D155" s="176" t="inlineStr">
+      <c r="D155" s="192" t="inlineStr">
         <is>
           <t>Investimento com promoção Cooperar é Ganhar</t>
         </is>
       </c>
-      <c r="E155" s="176" t="inlineStr">
+      <c r="E155" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6791,34 +6794,34 @@
           <t>Já já tem muito mais músicas aqui na Band FM! Band FM! Oi, eu sou o cantor Daniel. E quando o assunto é investimento, não dá pra contar com a sorte, né? Mas se a sorte te ajudar, você ainda pode ganha</t>
         </is>
       </c>
-      <c r="G155" s="176" t="inlineStr">
+      <c r="G155" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Cressol__Investimento_com_promocao_Cooperar_e_Ganhar__12-03-2026_09-42-02.mp3</t>
         </is>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="176" t="inlineStr">
+      <c r="A156" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:42:20</t>
         </is>
       </c>
-      <c r="B156" s="176" t="inlineStr">
+      <c r="B156" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C156" s="176" t="inlineStr">
+      <c r="C156" s="192" t="inlineStr">
         <is>
           <t>Cressol</t>
         </is>
       </c>
-      <c r="D156" s="176" t="inlineStr">
+      <c r="D156" s="192" t="inlineStr">
         <is>
           <t>Serviços de investimento</t>
         </is>
       </c>
-      <c r="E156" s="176" t="inlineStr">
+      <c r="E156" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6828,34 +6831,34 @@
           <t>Operar é ganhar. Invista com a Cressol. Gele números da sorte e concorra. Você vai mudar de vida. Pode acreditar. Porque na Cressol, operar é ganhar. Certificado de autorização SPAME. Número 04047374-</t>
         </is>
       </c>
-      <c r="G156" s="176" t="inlineStr">
+      <c r="G156" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Cressol__Servicos_de_investimento__12-03-2026_09-42-20.mp3</t>
         </is>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="176" t="inlineStr">
+      <c r="A157" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 09:42:37</t>
         </is>
       </c>
-      <c r="B157" s="176" t="inlineStr">
+      <c r="B157" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C157" s="176" t="inlineStr">
+      <c r="C157" s="192" t="inlineStr">
         <is>
           <t>Energiza</t>
         </is>
       </c>
-      <c r="D157" s="176" t="inlineStr">
+      <c r="D157" s="192" t="inlineStr">
         <is>
           <t>Serviços de energia</t>
         </is>
       </c>
-      <c r="E157" s="176" t="inlineStr">
+      <c r="E157" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -6865,7 +6868,7 @@
           <t>sete, três, sete, quatro, dois, vinte e seis. Energiza apresenta Michel tem luz. Fala moçada, hoje a participação é do Milton e ele quer informações importantes, hein? Bora ver o que é. Pelo aí, quais</t>
         </is>
       </c>
-      <c r="G157" s="176" t="inlineStr">
+      <c r="G157" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Energiza__Servicos_de_energia__12-03-2026_09-42-37.mp3</t>
         </is>
@@ -6983,27 +6986,27 @@
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="176" t="inlineStr">
+      <c r="A161" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 10:11:30</t>
         </is>
       </c>
-      <c r="B161" s="176" t="inlineStr">
+      <c r="B161" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C161" s="176" t="inlineStr">
+      <c r="C161" s="192" t="inlineStr">
         <is>
           <t>Gigante Max Atacadista</t>
         </is>
       </c>
-      <c r="D161" s="176" t="inlineStr">
+      <c r="D161" s="192" t="inlineStr">
         <is>
           <t>Páscoa</t>
         </is>
       </c>
-      <c r="E161" s="176" t="inlineStr">
+      <c r="E161" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -7013,34 +7016,34 @@
           <t>Muito mais barato, tem muita qualidade e tá lá todo o pessoal do Max esperando por você de Catanduva e região. Se anotou aí, hein? A maior Páscoa do maior atacarejo do Brasil é no Gigante Max Atacadis</t>
         </is>
       </c>
-      <c r="G161" s="176" t="inlineStr">
+      <c r="G161" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Gigante_Max_Atacadista__Pascoa__12-03-2026_10-11-30__ad1.mp3</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="A162" s="176" t="inlineStr">
+      <c r="A162" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 10:11:30</t>
         </is>
       </c>
-      <c r="B162" s="176" t="inlineStr">
+      <c r="B162" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C162" s="176" t="inlineStr">
+      <c r="C162" s="192" t="inlineStr">
         <is>
           <t>Doutor Alex Baraldo Portes</t>
         </is>
       </c>
-      <c r="D162" s="176" t="inlineStr">
+      <c r="D162" s="192" t="inlineStr">
         <is>
           <t>Serviços de Otorrino Laringologista</t>
         </is>
       </c>
-      <c r="E162" s="176" t="inlineStr">
+      <c r="E162" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -7050,7 +7053,7 @@
           <t>Muito mais barato, tem muita qualidade e tá lá todo o pessoal do Max esperando por você de Catanduva e região. Se anotou aí, hein? A maior Páscoa do maior atacarejo do Brasil é no Gigante Max Atacadis</t>
         </is>
       </c>
-      <c r="G162" s="176" t="inlineStr">
+      <c r="G162" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Doutor_Alex_Baraldo_Portes__Servicos_de_Otorrino_Laringologista__12-03-2026_10-11-30__ad2.mp3</t>
         </is>
@@ -7131,27 +7134,27 @@
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="176" t="inlineStr">
+      <c r="A165" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 10:48:38</t>
         </is>
       </c>
-      <c r="B165" s="176" t="inlineStr">
+      <c r="B165" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C165" s="176" t="inlineStr">
+      <c r="C165" s="192" t="inlineStr">
         <is>
           <t>Pavate</t>
         </is>
       </c>
-      <c r="D165" s="176" t="inlineStr">
+      <c r="D165" s="192" t="inlineStr">
         <is>
           <t>parabrisas e acessórios</t>
         </is>
       </c>
-      <c r="E165" s="176" t="inlineStr">
+      <c r="E165" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -7161,7 +7164,7 @@
           <t>Ondas Verdes Ondas Verdes Ondas Verdes Ondas Verdes Quero ouvir a Ondas Verdes no celular Baixe grátis o aplicativo E ouça Ondas Verdes também no celular Pavate O rei do parabrisa Duas lojas em Catand</t>
         </is>
       </c>
-      <c r="G165" s="176" t="inlineStr">
+      <c r="G165" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Pavate__parabrisas_e_acessorios__12-03-2026_10-48-38.mp3</t>
         </is>
@@ -7242,27 +7245,27 @@
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="176" t="inlineStr">
+      <c r="A168" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 11:18:41</t>
         </is>
       </c>
-      <c r="B168" s="176" t="inlineStr">
+      <c r="B168" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C168" s="176" t="inlineStr">
+      <c r="C168" s="192" t="inlineStr">
         <is>
           <t>Casa dos Construtores</t>
         </is>
       </c>
-      <c r="D168" s="176" t="inlineStr">
+      <c r="D168" s="192" t="inlineStr">
         <is>
           <t>tempo na sua casa</t>
         </is>
       </c>
-      <c r="E168" s="176" t="inlineStr">
+      <c r="E168" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -7272,34 +7275,34 @@
           <t>instante, não apenas passe, mas fique. Casa dos Construtores, o melhor tempo na sua casa.</t>
         </is>
       </c>
-      <c r="G168" s="176" t="inlineStr">
+      <c r="G168" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Casa_dos_Construtores__tempo_na_sua_casa__12-03-2026_11-18-41.mp3</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="176" t="inlineStr">
+      <c r="A169" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 11:34:50</t>
         </is>
       </c>
-      <c r="B169" s="176" t="inlineStr">
+      <c r="B169" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C169" s="176" t="inlineStr">
+      <c r="C169" s="192" t="inlineStr">
         <is>
           <t>Elétrica Araújo</t>
         </is>
       </c>
-      <c r="D169" s="176" t="inlineStr">
+      <c r="D169" s="192" t="inlineStr">
         <is>
           <t>Material elétrico</t>
         </is>
       </c>
-      <c r="E169" s="176" t="inlineStr">
+      <c r="E169" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -7309,7 +7312,7 @@
           <t xml:space="preserve">Vêneto, a tranquilidade da Itália em Pindorama. Para nossas figuras é de sua família, está em primeiro lugar, Elétrica Araújo. Material elétrico, ilustres para o seu lar. Rua Pernambuco 440. Elétrica </t>
         </is>
       </c>
-      <c r="G169" s="176" t="inlineStr">
+      <c r="G169" s="192" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Eletrica_Araujo__Material_eletrico__12-03-2026_11-34-50.mp3</t>
         </is>
@@ -7390,27 +7393,27 @@
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="A172" s="176" t="inlineStr">
+      <c r="A172" s="192" t="inlineStr">
         <is>
           <t>12/03/2026 11:49:53</t>
         </is>
       </c>
-      <c r="B172" s="176" t="inlineStr">
+      <c r="B172" s="192" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C172" s="176" t="inlineStr">
+      <c r="C172" s="192" t="inlineStr">
         <is>
           <t>Band FM</t>
         </is>
       </c>
-      <c r="D172" s="176" t="inlineStr">
+      <c r="D172" s="192" t="inlineStr">
         <is>
           <t>Rádio/Estação de Rádio</t>
         </is>
       </c>
-      <c r="E172" s="176" t="inlineStr">
+      <c r="E172" s="192" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
@@ -7420,7 +7423,7 @@
           <t>Não pode ter ciúme, não pode ter ciúme E quando eu pago a conta do quarto, cê vai secando seu cabelo molhado Na Band FM, quem ama não esquece</t>
         </is>
       </c>
-      <c r="G172" s="176" t="inlineStr">
+      <c r="G172" s="192" t="inlineStr">
         <is>
           <t>Band_FM__Band_FM__Radio_Estacao_de_Radio__12-03-2026_11-49-53.mp3</t>
         </is>
@@ -8015,6 +8018,43 @@
       <c r="G188" s="192" t="inlineStr">
         <is>
           <t>Jovem_Pan__Vene_Express__prato_de_executivos__12-03-2026_13-54-09.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="193" t="inlineStr">
+        <is>
+          <t>12/03/2026 14:05:43</t>
+        </is>
+      </c>
+      <c r="B189" s="193" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C189" s="193" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D189" s="193" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E189" s="193" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="F189" s="112" t="inlineStr">
+        <is>
+          <t>Semi-reboques, transbordos, caminhões, implementos agrícolas, entre outros. Leilão, dia 25 de março de 2026, às 11h30. Cadastre-se e agende sua visita. www.leilãoonline.net Acesse www.leilãoonline.net</t>
+        </is>
+      </c>
+      <c r="G189" s="193" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Desconhecido__12-03-2026_14-05-43.mp3</t>
         </is>
       </c>
     </row>
@@ -8071,11 +8111,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12/03/2026 13:54:09</t>
+          <t>12/03/2026 14:05:43</t>
         </is>
       </c>
     </row>

--- a/radio_capture/relatorio_anuncios.xlsx
+++ b/radio_capture/relatorio_anuncios.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -686,6 +686,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1053,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5025,27 +5028,27 @@
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="191" t="inlineStr">
+      <c r="A108" s="193" t="inlineStr">
         <is>
           <t>11/03/2026 16:13:13</t>
         </is>
       </c>
-      <c r="B108" s="191" t="inlineStr">
+      <c r="B108" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C108" s="191" t="inlineStr">
+      <c r="C108" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D108" s="191" t="inlineStr">
+      <c r="D108" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E108" s="191" t="inlineStr">
+      <c r="E108" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -5055,7 +5058,7 @@
           <t>Imagina encontrar um vestido de noiva maravilhoso por apenas 200 reais. Sim, 200 reais. No dia 28 de março, sábado, a partir das 10 horas da manhã, acontece o grande bazar de vestidos de noiva em prol</t>
         </is>
       </c>
-      <c r="G108" s="191" t="inlineStr">
+      <c r="G108" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__11-03-2026_16-13-13.mp3</t>
         </is>
@@ -6875,27 +6878,27 @@
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="191" t="inlineStr">
+      <c r="A158" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 10:09:20</t>
         </is>
       </c>
-      <c r="B158" s="191" t="inlineStr">
+      <c r="B158" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C158" s="191" t="inlineStr">
+      <c r="C158" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D158" s="191" t="inlineStr">
+      <c r="D158" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E158" s="191" t="inlineStr">
+      <c r="E158" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -6905,34 +6908,34 @@
           <t>Ela gosta demais do chapeludo Não saia daí! Já já tem muito mais músicas aqui na Band FM! Você que vai casar, pare um instante Imagine encontrar um vestido de noiva maravilhoso por apenas 200 reais Si</t>
         </is>
       </c>
-      <c r="G158" s="191" t="inlineStr">
+      <c r="G158" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_10-09-20.mp3</t>
         </is>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="191" t="inlineStr">
+      <c r="A159" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 10:09:38</t>
         </is>
       </c>
-      <c r="B159" s="191" t="inlineStr">
+      <c r="B159" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C159" s="191" t="inlineStr">
+      <c r="C159" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D159" s="191" t="inlineStr">
+      <c r="D159" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E159" s="191" t="inlineStr">
+      <c r="E159" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -6942,34 +6945,34 @@
           <t>Você que vai casar, pare um instante. Imagine encontrar um vestido de noiva maravilhoso por apenas 200 reais. Sim, 200 reais. No dia 28 de março, sábado, a partir das 10 horas da manhã, acontece o gra</t>
         </is>
       </c>
-      <c r="G159" s="191" t="inlineStr">
+      <c r="G159" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_10-09-38.mp3</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="191" t="inlineStr">
+      <c r="A160" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 10:09:42</t>
         </is>
       </c>
-      <c r="B160" s="191" t="inlineStr">
+      <c r="B160" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C160" s="191" t="inlineStr">
+      <c r="C160" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D160" s="191" t="inlineStr">
+      <c r="D160" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E160" s="191" t="inlineStr">
+      <c r="E160" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -6979,7 +6982,7 @@
           <t>Especialidades, caixa com 220 gramas, R$ 13,99. Batata congelada, pacote 2 kg, a partir de R$ 19,90. Amaciante P, fragrâncias 2 litros, R$ 7,49. É, aqui no Max Atacadista é preço baixo todo dia. E a m</t>
         </is>
       </c>
-      <c r="G160" s="191" t="inlineStr">
+      <c r="G160" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan__Desconhecido__12-03-2026_10-09-42.mp3</t>
         </is>
@@ -7060,27 +7063,27 @@
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="191" t="inlineStr">
+      <c r="A163" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 10:33:05</t>
         </is>
       </c>
-      <c r="B163" s="191" t="inlineStr">
+      <c r="B163" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C163" s="191" t="inlineStr">
+      <c r="C163" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D163" s="191" t="inlineStr">
+      <c r="D163" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E163" s="191" t="inlineStr">
+      <c r="E163" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7090,34 +7093,34 @@
           <t xml:space="preserve">Clube de Tênis Catanduva, dois super shows, seu moço na abertura e pela primeira vez na região, traia, veia. Você só vai achar lembrança boa. E em palco 360. E o sinal abria. Convites para a área VIP </t>
         </is>
       </c>
-      <c r="G163" s="191" t="inlineStr">
+      <c r="G163" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_10-33-05.mp3</t>
         </is>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="191" t="inlineStr">
+      <c r="A164" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 10:33:23</t>
         </is>
       </c>
-      <c r="B164" s="191" t="inlineStr">
+      <c r="B164" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C164" s="191" t="inlineStr">
+      <c r="C164" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D164" s="191" t="inlineStr">
+      <c r="D164" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E164" s="191" t="inlineStr">
+      <c r="E164" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7127,7 +7130,7 @@
           <t>Se não havia... Convites para a área VIP por R$ 80,00 A venda na Secretaria do Clube Ou querodoisingressos.com.br Entra dentro do meu peito Seu moço e traia a veia Dia 20 de Março, no Clube de Tênis C</t>
         </is>
       </c>
-      <c r="G164" s="191" t="inlineStr">
+      <c r="G164" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_10-33-23.mp3</t>
         </is>
@@ -7171,27 +7174,27 @@
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="191" t="inlineStr">
+      <c r="A166" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 10:59:13</t>
         </is>
       </c>
-      <c r="B166" s="191" t="inlineStr">
+      <c r="B166" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C166" s="191" t="inlineStr">
+      <c r="C166" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D166" s="191" t="inlineStr">
+      <c r="D166" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E166" s="191" t="inlineStr">
+      <c r="E166" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7201,34 +7204,34 @@
           <t>Aquele sabor delicio! League da Band! 0850 1313 Band FM Você que vai casar, pare um instante. Imagine encontrar um vestido de noiva maravilhoso por apenas 200 reais. Sim, 200 reais. No dia 28 de março</t>
         </is>
       </c>
-      <c r="G166" s="191" t="inlineStr">
+      <c r="G166" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_10-59-13.mp3</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="191" t="inlineStr">
+      <c r="A167" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 10:59:31</t>
         </is>
       </c>
-      <c r="B167" s="191" t="inlineStr">
+      <c r="B167" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C167" s="191" t="inlineStr">
+      <c r="C167" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D167" s="191" t="inlineStr">
+      <c r="D167" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E167" s="191" t="inlineStr">
+      <c r="E167" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7238,7 +7241,7 @@
           <t>Por apenas 200 reais. Sim, 200 reais. No dia 28 de março, sábado, a partir das 10 horas da manhã, acontece o grande bazar de vestidos de noiva em prol do projeto Corujas do Bem. Serão mais de 80 vesti</t>
         </is>
       </c>
-      <c r="G167" s="191" t="inlineStr">
+      <c r="G167" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_10-59-30.mp3</t>
         </is>
@@ -7319,27 +7322,27 @@
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="191" t="inlineStr">
+      <c r="A170" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 11:39:54</t>
         </is>
       </c>
-      <c r="B170" s="191" t="inlineStr">
+      <c r="B170" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C170" s="191" t="inlineStr">
+      <c r="C170" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D170" s="191" t="inlineStr">
+      <c r="D170" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E170" s="191" t="inlineStr">
+      <c r="E170" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7349,34 +7352,34 @@
           <t>da casa, aquele sabor deliciosos. Toda hora, toda hora, toda hora. Band FM. E aí, quer economizar? Vem conferir a oferta do dia na loja da Band FM. lojabandfm.com.br Você encontra de tudo. Promoção de</t>
         </is>
       </c>
-      <c r="G170" s="191" t="inlineStr">
+      <c r="G170" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_11-39-53.mp3</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="191" t="inlineStr">
+      <c r="A171" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 11:40:11</t>
         </is>
       </c>
-      <c r="B171" s="191" t="inlineStr">
+      <c r="B171" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C171" s="191" t="inlineStr">
+      <c r="C171" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D171" s="191" t="inlineStr">
+      <c r="D171" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E171" s="191" t="inlineStr">
+      <c r="E171" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7386,7 +7389,7 @@
           <t>Desde pães de queijo a carnes, por apenas 8 parcelas, de R$ 56,13, sem juros! E você ainda encontra cupons de desconto e o site todo com até 12 vezes sem juros! Você curtiu, né? Loja bandfm.com.br, co</t>
         </is>
       </c>
-      <c r="G171" s="191" t="inlineStr">
+      <c r="G171" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_11-40-11.mp3</t>
         </is>
@@ -7430,27 +7433,27 @@
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="191" t="inlineStr">
+      <c r="A173" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 11:50:13</t>
         </is>
       </c>
-      <c r="B173" s="191" t="inlineStr">
+      <c r="B173" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C173" s="191" t="inlineStr">
+      <c r="C173" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D173" s="191" t="inlineStr">
+      <c r="D173" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E173" s="191" t="inlineStr">
+      <c r="E173" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7460,34 +7463,34 @@
           <t>Vai achar lembrança boa E em palco 360 E o sinal abria Convites para a área VIP por 80 reais A venda na secretaria do clube Ou querodoisingressos.com.br Seu moço e traia a veia Dia 20 de março no club</t>
         </is>
       </c>
-      <c r="G173" s="191" t="inlineStr">
+      <c r="G173" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Desconhecido__12-03-2026_11-50-13.mp3</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="191" t="inlineStr">
+      <c r="A174" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:14:14</t>
         </is>
       </c>
-      <c r="B174" s="191" t="inlineStr">
+      <c r="B174" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C174" s="191" t="inlineStr">
+      <c r="C174" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D174" s="191" t="inlineStr">
+      <c r="D174" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E174" s="191" t="inlineStr">
+      <c r="E174" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7497,34 +7500,34 @@
           <t>Muito pouco. Olha só, confira as ofertas e você vai entender o que eu estou falando. Hoje, quinta-feira, olha só, no Max, tem frango a passarinho lar com 1kg, apenas R$ 8,97. Feito com osso, só R$ 10,</t>
         </is>
       </c>
-      <c r="G174" s="191" t="inlineStr">
+      <c r="G174" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Desconhecido__12-03-2026_12-14-14.mp3</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="A175" s="191" t="inlineStr">
+      <c r="A175" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:15:03</t>
         </is>
       </c>
-      <c r="B175" s="191" t="inlineStr">
+      <c r="B175" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C175" s="191" t="inlineStr">
+      <c r="C175" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D175" s="191" t="inlineStr">
+      <c r="D175" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E175" s="191" t="inlineStr">
+      <c r="E175" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7534,34 +7537,34 @@
           <t xml:space="preserve">Aqui na Ondas Verdes, a FM da gente. Continue ligado! Ondas Verdes! 99777 9270 Fale com a Onda! WhatsApp! Ondas Verdes! Atenção! Quer comer bem de verdade? Vem pro restaurante Vila Brasil! Comida boa </t>
         </is>
       </c>
-      <c r="G175" s="191" t="inlineStr">
+      <c r="G175" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Desconhecido__12-03-2026_12-15-03.mp3</t>
         </is>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="191" t="inlineStr">
+      <c r="A176" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:15:36</t>
         </is>
       </c>
-      <c r="B176" s="191" t="inlineStr">
+      <c r="B176" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C176" s="191" t="inlineStr">
+      <c r="C176" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D176" s="191" t="inlineStr">
+      <c r="D176" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E176" s="191" t="inlineStr">
+      <c r="E176" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7571,34 +7574,34 @@
           <t xml:space="preserve">Itagrande, vinte e dois reais. Fazemos entrega pelo telefone três cinco dois cinco oitenta e um cinquenta, Rua Brasil mil e novecentos. Temos também espetinho de quarta a sábado, a partir das dezoito </t>
         </is>
       </c>
-      <c r="G176" s="191" t="inlineStr">
+      <c r="G176" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Desconhecido__12-03-2026_12-15-36.mp3</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="191" t="inlineStr">
+      <c r="A177" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:20:33</t>
         </is>
       </c>
-      <c r="B177" s="191" t="inlineStr">
+      <c r="B177" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C177" s="191" t="inlineStr">
+      <c r="C177" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D177" s="191" t="inlineStr">
+      <c r="D177" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E177" s="191" t="inlineStr">
+      <c r="E177" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7608,34 +7611,34 @@
           <t>R$ 450,00 ML, R$ 3,59. Macarrão Basilar, 400 gramas, R$ 2,99. Refrigerante Piquenique Pet, sabores 2 litros, R$ 3,99. Sabonete Francis, 85 gramas, fragrâncias, só R$ 1,99. Ofertas válidas até o dia 12</t>
         </is>
       </c>
-      <c r="G177" s="191" t="inlineStr">
+      <c r="G177" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_12-20-33.mp3</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="A178" s="191" t="inlineStr">
+      <c r="A178" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:52:56</t>
         </is>
       </c>
-      <c r="B178" s="191" t="inlineStr">
+      <c r="B178" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C178" s="191" t="inlineStr">
+      <c r="C178" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D178" s="191" t="inlineStr">
+      <c r="D178" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E178" s="191" t="inlineStr">
+      <c r="E178" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7645,34 +7648,34 @@
           <t xml:space="preserve">A qualidade do couro é muito gostosa, né Dede? É muito boa. Eu provei a 70 graus, pé fosco de metal, é assim ideal pra casa, escritório, você quer um momentinho ali, você quer almoçar, quer descansar </t>
         </is>
       </c>
-      <c r="G178" s="191" t="inlineStr">
+      <c r="G178" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan__Desconhecido__12-03-2026_12-52-56.mp3</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
-      <c r="A179" s="191" t="inlineStr">
+      <c r="A179" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:54:45</t>
         </is>
       </c>
-      <c r="B179" s="191" t="inlineStr">
+      <c r="B179" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C179" s="191" t="inlineStr">
+      <c r="C179" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D179" s="191" t="inlineStr">
+      <c r="D179" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E179" s="191" t="inlineStr">
+      <c r="E179" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7682,34 +7685,34 @@
           <t>... de 15 mil reais. Pode pesquisar, não vai ter ninguém que vai ter esse preço que a gente vai ofertar aqui. Dividido, hein? Dividido até em 10 vezes, 10 de 699 reais. Tá dando sofá. 600 mil um sofá,</t>
         </is>
       </c>
-      <c r="G179" s="191" t="inlineStr">
+      <c r="G179" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan__Desconhecido__12-03-2026_12-54-45.mp3</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="191" t="inlineStr">
+      <c r="A180" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:55:21</t>
         </is>
       </c>
-      <c r="B180" s="191" t="inlineStr">
+      <c r="B180" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C180" s="191" t="inlineStr">
+      <c r="C180" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D180" s="191" t="inlineStr">
+      <c r="D180" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E180" s="191" t="inlineStr">
+      <c r="E180" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7719,34 +7722,34 @@
           <t>Esteve aqui já. É, ele dois, um sofá livre, mas que vira cama, largura um metro e oitenta para apartamentos compactos, estúdios, pé de madeira, costura invertida, um linho grosso de qualidade, para am</t>
         </is>
       </c>
-      <c r="G180" s="191" t="inlineStr">
+      <c r="G180" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan__Desconhecido__12-03-2026_12-55-21.mp3</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="191" t="inlineStr">
+      <c r="A181" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:55:39</t>
         </is>
       </c>
-      <c r="B181" s="191" t="inlineStr">
+      <c r="B181" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C181" s="191" t="inlineStr">
+      <c r="C181" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D181" s="191" t="inlineStr">
+      <c r="D181" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E181" s="191" t="inlineStr">
+      <c r="E181" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7756,34 +7759,34 @@
           <t>Resolve, apartamento menor, né? É um produto bonito, não é nada, olha o design, acessível, pronto entrega no site, em todas as lojas, preço de mercado, 3 mil reais de mercado, na Openbox, 10 de 169,99</t>
         </is>
       </c>
-      <c r="G181" s="191" t="inlineStr">
+      <c r="G181" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan__Desconhecido__12-03-2026_12-55-39.mp3</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="191" t="inlineStr">
+      <c r="A182" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:56:48</t>
         </is>
       </c>
-      <c r="B182" s="191" t="inlineStr">
+      <c r="B182" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C182" s="191" t="inlineStr">
+      <c r="C182" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D182" s="191" t="inlineStr">
+      <c r="D182" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E182" s="191" t="inlineStr">
+      <c r="E182" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7793,34 +7796,34 @@
           <t xml:space="preserve">Não tem também nenhuma concorrência, é um produto exclusivo nosso. 10 de R$ 169,99, 10 parcelas, se pagar no Pix ainda tem mais 7. Esqueci, Emilio, mais 7%. Todos esses produtos anunciados aqui, quem </t>
         </is>
       </c>
-      <c r="G182" s="191" t="inlineStr">
+      <c r="G182" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan__Desconhecido__12-03-2026_12-56-48.mp3</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="191" t="inlineStr">
+      <c r="A183" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:57:19</t>
         </is>
       </c>
-      <c r="B183" s="191" t="inlineStr">
+      <c r="B183" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C183" s="191" t="inlineStr">
+      <c r="C183" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D183" s="191" t="inlineStr">
+      <c r="D183" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E183" s="191" t="inlineStr">
+      <c r="E183" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7830,34 +7833,34 @@
           <t>É, a sua Alexa é tudo de bom, é tudo de mais. Corre que acaba Casas Bahia. A sua chance de aproveitar essa oferta é impedível e dura pouco. Batedeira Planetária Filco pela metade do preço, só R$ 24,90</t>
         </is>
       </c>
-      <c r="G183" s="191" t="inlineStr">
+      <c r="G183" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_12-57-19.mp3</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="191" t="inlineStr">
+      <c r="A184" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 12:58:04</t>
         </is>
       </c>
-      <c r="B184" s="191" t="inlineStr">
+      <c r="B184" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan</t>
         </is>
       </c>
-      <c r="C184" s="191" t="inlineStr">
+      <c r="C184" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D184" s="191" t="inlineStr">
+      <c r="D184" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E184" s="191" t="inlineStr">
+      <c r="E184" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7867,34 +7870,34 @@
           <t>Ó, custa... no mercado... Acaba rapidinho. É, acaba rapidinho. Você vai fazer R$ 179,99, é isso mesmo? É, no mercado em torno de R$ 500,00. R$ 500,00. Pode ver, hein? Tem lá, tem no mercado livre, Qui</t>
         </is>
       </c>
-      <c r="G184" s="191" t="inlineStr">
+      <c r="G184" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan__Desconhecido__12-03-2026_12-58-04.mp3</t>
         </is>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="191" t="inlineStr">
+      <c r="A185" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 13:01:36</t>
         </is>
       </c>
-      <c r="B185" s="191" t="inlineStr">
+      <c r="B185" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C185" s="191" t="inlineStr">
+      <c r="C185" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D185" s="191" t="inlineStr">
+      <c r="D185" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E185" s="191" t="inlineStr">
+      <c r="E185" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7904,34 +7907,34 @@
           <t>e está à venda nas melhores farmácias e casas de produtos naturais pertinho de você. Fim de semana do consumidor no Antunes Mais. Arroz seleto tipo 1, pacote 5 quilos, R$ 12,99. Feijão carioca seleto,</t>
         </is>
       </c>
-      <c r="G185" s="191" t="inlineStr">
+      <c r="G185" s="193" t="inlineStr">
         <is>
           <t>Ondas_Verdes__Desconhecido__12-03-2026_13-01-36.mp3</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
-      <c r="A186" s="191" t="inlineStr">
+      <c r="A186" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 13:25:32</t>
         </is>
       </c>
-      <c r="B186" s="191" t="inlineStr">
+      <c r="B186" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C186" s="191" t="inlineStr">
+      <c r="C186" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D186" s="191" t="inlineStr">
+      <c r="D186" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E186" s="191" t="inlineStr">
+      <c r="E186" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7941,34 +7944,34 @@
           <t>É ganhar, invista com a Cressol, gere números da sorte e concorra. Você vai mudar de vida, pode acreditar, porque na Cressol, operar é ganhar. Certificado de autorização SPAME, número 0404737421. Você</t>
         </is>
       </c>
-      <c r="G186" s="191" t="inlineStr">
+      <c r="G186" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_13-25-32.mp3</t>
         </is>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
-      <c r="A187" s="191" t="inlineStr">
+      <c r="A187" s="193" t="inlineStr">
         <is>
           <t>12/03/2026 13:25:50</t>
         </is>
       </c>
-      <c r="B187" s="191" t="inlineStr">
+      <c r="B187" s="193" t="inlineStr">
         <is>
           <t>Band_FM</t>
         </is>
       </c>
-      <c r="C187" s="191" t="inlineStr">
+      <c r="C187" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D187" s="191" t="inlineStr">
+      <c r="D187" s="193" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E187" s="191" t="inlineStr">
+      <c r="E187" s="193" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
@@ -7978,7 +7981,7 @@
           <t>Você que vai casar, pare um instante. Imagine encontrar um vestido de noiva maravilhoso por apenas 200 reais. Sim, 200 reais. No dia 28 de março, sábado, a partir das 10 horas da manhã, acontece o gra</t>
         </is>
       </c>
-      <c r="G187" s="191" t="inlineStr">
+      <c r="G187" s="193" t="inlineStr">
         <is>
           <t>Band_FM__Desconhecido__12-03-2026_13-25-50.mp3</t>
         </is>
@@ -8055,6 +8058,43 @@
       <c r="G189" s="193" t="inlineStr">
         <is>
           <t>Jovem_Pan__Desconhecido__12-03-2026_14-05-43.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="194" t="inlineStr">
+        <is>
+          <t>12/03/2026 14:10:16</t>
+        </is>
+      </c>
+      <c r="B190" s="194" t="inlineStr">
+        <is>
+          <t>Jovem_Pan</t>
+        </is>
+      </c>
+      <c r="C190" s="194" t="inlineStr">
+        <is>
+          <t>Unifipa Catanduva</t>
+        </is>
+      </c>
+      <c r="D190" s="194" t="inlineStr">
+        <is>
+          <t>Cursos de graduação</t>
+        </is>
+      </c>
+      <c r="E190" s="194" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>dois, mil e um. Na Unifipa Catanduva, nossa missão é formar para crescer e ensinar para ser grande. Acreditamos que o verdadeiro crescimento começa com formação sólida, humana e conectada ao mundo rea</t>
+        </is>
+      </c>
+      <c r="G190" s="194" t="inlineStr">
+        <is>
+          <t>Jovem_Pan__Unifipa_Catanduva__Cursos_de_graduacao__12-03-2026_14-10-16.mp3</t>
         </is>
       </c>
     </row>
@@ -8111,11 +8151,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12/03/2026 14:05:43</t>
+          <t>12/03/2026 14:10:16</t>
         </is>
       </c>
     </row>

--- a/radio_capture/relatorio_anuncios.xlsx
+++ b/radio_capture/relatorio_anuncios.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,25 +122,55 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -508,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -520,7 +550,7 @@
     <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Data/Hora</t>
@@ -548,7 +578,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Transcrição (resumo)</t>
+          <t>Trecho do Anúncio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -558,335 +588,705 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>18/03/2026 15:11:29</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 09:42:25</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>Rede Móveis</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Rede Móveis Casa Vende</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__Rede_Moveis__20-03-2026_09-42-24__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>20/03/2026 09:42:25</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>JS Consórcios</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Grupo JS Consórcios</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Band_FM__JS_Consorcios__20-03-2026_09-42-25__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 09:42:25</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Cressol Gele</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>números da sorte</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Cressol Gele números da sorte</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__Cressol_Gele__numeros_da_sorte__20-03-2026_09-42-25__ad3.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>20/03/2026 09:43:12</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Cressol</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>promoção, prêmios, investimento</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Invista com a Cressol, gere números da sorte e concorra</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Band_FM__Cressol__promocao__premios__investimento__20-03-2026_09-43-12__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>20/03/2026 09:43:12</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>internet, suporte técnico, velocidade</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>A melhor internet da região é Netflix</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Band_FM__Netflix__internet__suporte_tecnico__velocidade__20-03-2026_09-43-12__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:03:19</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Grupo Moresc</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>refrigerante, sorvete, creme, piquenique, pet, vestidos de noiva</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Ofertas válidas até o dia vinte e três, nas lojas do Grupo Moresc</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__Grupo_Moresc__refrigerante__sorvete__creme__piquenique__pet__vestidos_de_n__20-03-2026_10-03-19.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:04:07</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Dicopel</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>formas para ovos, bombons de acetato e silicone, embalagens, envelopes, caixa para ovos, papéis decorados, chocolates confeitos, linha completa de doces</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>A sua Páscoa é mais gostosa na Dicopel</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__Dicopel__formas_para_ovos__bombons_de_acetato_e_silicone__embalagens___20-03-2026_10-04-07.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:04:48</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Top Frios</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>produtos exclusivos</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Produtos exclusivos, os menores preços, conforto pra você comprar e ainda, claro, estacionamento próprio. Top Frios é demais. Entregamos em domicílio. WhatsApp 997459897 ou 35239820. Top Frios, Rua 15</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Top_Frios__produtos_exclusivos__18-03-2026_15-11-29.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>18/03/2026 15:11:46</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Desconhecido__20-03-2026_10-04-48.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:04:54</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>La Juma</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>apartamento, Ilhas Gregas, Rua Sergipe, três dormitórios, suíte, salas, cozinha</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Apartamento no edifício Ilhas Gregas</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__La_Juma__apartamento__Ilhas_Gregas__Rua_Sergipe__tres_dormitorios__su__20-03-2026_10-04-54.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:32:47</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Sicredi</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>poupança premiada</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Sicredi, poucos, é premiada</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__Sicredi__poupanca_premiada__20-03-2026_10-32-47.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:33:35</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Padre Albino Saúde</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>serviços de saúde, profissionais de saúde</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>No Padre Albino Saúde</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__Padre_Albino_Saude__servicos_de_saude__profissionais_de_saude__20-03-2026_10-33-35__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:33:35</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Paz Previme</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>serviços de saúde, profissionais de saúde</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>contando em breve com o novo prédio do Paz Previme</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__Paz_Previme__servicos_de_saude__profissionais_de_saude__20-03-2026_10-33-35__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:34:23</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Rede Móveis Casa Verde</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>produtos selecionados</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>ofertas especiais pra renovar a sua casa</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__Rede_Moveis_Casa_Verde__produtos_selecionados__20-03-2026_10-34-23__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:34:23</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Cressol</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>investimento, prêmios</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Invista com a Cressol Gere números da sorte e concorra</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>Band_FM__Cressol__investimento__premios__20-03-2026_10-34-23__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:36:36</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>vestido de noiva</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 98, 20, top frios, rua 15 de novembro, 1306, com estacionamento próprio. Você que vai casar, pare um instante. Imagine encontrar um vestido de noiva, maravilhoso, por apenas 200 reais. Sim, 2</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Desconhecido__vestido_de_noiva__18-03-2026_15-11-46.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>18/03/2026 15:12:02</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Ferreira Decorações</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>tapete, cortinas</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Ferreira Decorações, uma verdadeira festa</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Ferreira_Decoracoes__tapete__cortinas__20-03-2026_10-36-36.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:53:39</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>bazar de vestidos de noiva</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Maravilhoso, por apenas duzentos reais. Sim, duzentos reais. No dia vinte e oito de março, sábado, a partir das dez horas da manhã, acontece o grande bazar de vestidos de noiva em prol do projeto Coru</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Desconhecido__bazar_de_vestidos_de_noiva__18-03-2026_15-12-02.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>18/03/2026 15:12:19</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Vance Brasil</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>ofertas, cerveja Romarinho, Antártica, Escoa, Brama</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Romarinho, Antártica, Escoa e Brama, dois e quarenta e nove</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Vance_Brasil__ofertas__cerveja_Romarinho__Antartica__Escoa__Brama__20-03-2026_10-53-39.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:55:13</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Messias Doces</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>ovos de Páscoa</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Serão mais de oitenta vestidos de noiva, lindos, esperando você. Rua São Paulo, mil e trinta e três, sábado, dia vinte e oito, a partir das dez da manhã. Informações WhatsApp, dezessete, nove dois, ze</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Messias_Doces__ovos_de_Pascoa__18-03-2026_15-12-19.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>18/03/2026 15:13:58</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Empório São Pedro</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>bacalhau selecionado, azeites especiais, azeitonas e grão de bico premium</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empório São Pedro, bacalhau selecionado, azeites especiais, azeitonas e grão de </t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Emporio_Sao_Pedro__bacalhau_selecionado__azeites_especiais__azeitonas_e_grao_de__20-03-2026_10-55-13__ad1.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:55:13</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>Ondas_Verdes</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Polo São Pedro</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>bacalhau de qualidade</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>de Catanduva. Bacalhau de qualidade, com procedência e aquele cuidado especial. Venha garantir o seu, na Rua São Paulo, cinquenta e quatro. Em Polo São Pedro, tradição que dá sabor a sua mesa. Canecão</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Polo_Sao_Pedro__bacalhau_de_qualidade__18-03-2026_15-13-58__ad1.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>18/03/2026 15:13:58</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>carro ou caminhonete</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>de Catanduva. Bacalhau de qualidade, com procedência e aquele cuidado especial. Venha garantir o seu, na Rua São Paulo, cinquenta e quatro. Em Polo São Pedro, tradição que dá sabor a sua mesa. Canecão</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>Ondas_Verdes__Desconhecido__carro_ou_caminhonete__18-03-2026_15-13-58__ad2.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>18/03/2026 15:14:45</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Band_FM</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Magazine Luiza</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>iPhone</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>É isso mesmo, ó. Vem comprar o seu iPhone aqui no Magazine Luiza em 21 vezes sem juros. Temos também o Galaxy S25, 256 GB por apenas 3.999. Também, Maurício, em 21 vezes sem juros no cartão do Magazin</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Band_FM__Magazine_Luiza__iPhone__18-03-2026_15-14-45.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>18/03/2026 15:15:51</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Band_FM</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Magazine Luiza</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>cartão</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Hein, Maurício? Em 21 vezes sem juros no cartão do Magazine Luiza. Temos Motorola também na promoção aqui, Motorola, Edge 60, Fusio, 256 gigas, por apenas 299 ou 21 pagamentos sem juros no cartão do M</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>Band_FM__Magazine_Luiza__cartao__18-03-2026_15-15-51__ad1.mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>18/03/2026 15:15:51</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Band_FM</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Edge 60, Fusio</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Hein, Maurício? Em 21 vezes sem juros no cartão do Magazine Luiza. Temos Motorola também na promoção aqui, Motorola, Edge 60, Fusio, 256 gigas, por apenas 299 ou 21 pagamentos sem juros no cartão do M</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>Band_FM__Motorola__Edge_60__Fusio__18-03-2026_15-15-51__ad2.mp3</t>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Óticas Fabrilene</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>lentes multifocais digitais Noblem com antirreflexo, lentes de visão simples com antirreflexo e filtro de luz azul</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Na compra do primeiro par de lentes multifocais digitais Noblem com antirreflexo</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>Ondas_Verdes__Oticas_Fabrilene__lentes_multifocais_digitais_Noblem_com_antirreflexo__lentes___20-03-2026_10-55-13__ad2.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>20/03/2026 10:56:39</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Band_FM</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Grupo Moresc</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>carne bovina, suína, frango, arroz, banana, leite</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>A 100 bovino, quilo 32,99. Mistéca suína, 14,99 o quilo.</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>Band_FM__Grupo_Moresc__carne_bovina__suina__frango__arroz__banana__leite__20-03-2026_10-56-39.mp3</t>
         </is>
       </c>
     </row>
@@ -924,30 +1324,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ondas_Verdes</t>
+          <t>Band_FM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18/03/2026 15:13:58</t>
+          <t>20/03/2026 10:56:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Band_FM</t>
+          <t>Ondas_Verdes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18/03/2026 15:15:51</t>
+          <t>20/03/2026 10:55:13</t>
         </is>
       </c>
     </row>
